--- a/structured_bills_detailed.xlsx
+++ b/structured_bills_detailed.xlsx
@@ -434,22 +434,22 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Invoice Number</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Total Price</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>GSTIN</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Invoice Number</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Total Price</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -469,7 +469,11 @@
           <t>M. A. STONEX</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>tal</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -493,26 +497,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SHED  29-30, SAMAYSAAR BUNGLOW, NR NANDINI 3 VIP ROAD SURAT, Surat,  395007, Gujarat</t>
+          <t>SHED</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>SPS-2073</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SPS-2073</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>20/03/2026</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>2360</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -536,15 +540,15 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>950</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>24ARMPK8698R1ZH</t>
         </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>950</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -560,7 +564,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>co OPiutTigons</t>
+          <t>HNO.1/938/2, BLOCK NO.1 SIDI MAHOLLA, KISHOR BHAVAN,B/H JIVA BHARTI TIMALIYAVAD,NANPURA,</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -568,19 +572,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>30/06/2025</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>24ARMPK8698R1ZH</t>
         </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>30/06/2025</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>2065</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -596,7 +600,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SHED</t>
+          <t>S.T. LOKHANDWALA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -605,15 +609,15 @@
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>05-04-25</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="F6" t="n">
         <v>318247</v>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>SHED  GSTIN :- 24RrAanY ** Ledger (MID:  7933G1zY 375] ** Brom Ol=Gz=cOeomucmol—O2—2026  S.T.LOKHAND SURAT WALA  Balance B/f JVAC Yogesh Shah Huf 05-04-25 104 PRCHAI1  USTVGT J BO leone 0}. 00  92704-25905)  24-04-25 20-05-25 04-06-2 16-06-25 04-07-25  PRCHA1 PRCHAL PRCHA1 PRCHA1 PRCHA1 PRCHA1 AXISBA  78088.00  -00  moO? 00  00 00 9624800 (27444 .00  31708.00 41921.00 DAUGS A - OO 78086 .00 4336.00 MALATE) — OW 33692 .00  a Sfx  ee) 1  11-07-25 8 1g=&lt;07-25 PRCHA1 1 ao PRCHA1 0 23S-25@1369 PRCHAL 07-08-25 PRCHA1 28=08-—25 PRCHA1 08-09-25 ameo” PRCHAL  Vee NO0&gt;25 PRCHA1 | 08-10-25 @m53"  PRCHA1 | PaO AS) 2 AXISBA i} 01-11-2 PRCHA1  0411-25 qe PRCHA1 AQ-1i—Z2s) PRCHA1 LASTISZS PRCHA1 25-11-2 PRCHA1 25-11-2 PRCHAL 12-12-2 PRCHA1 are — 23-12-2 07-01-2  40412.00 42696.00 DEZei _ Ol 74506.00  6726.00 w2a78" 00 5385-00 mie225.-.00 25002700 99508.00 C (3970200 138610.00 30695.00 169305.00 41739000 210695.00 230773.00 131279.00 137685.00 145237.00 178926.00 186154.00  99494.00  ZAMS SrA O10 261411.00 Z2UVNGZ33 Ol 284620.00 306435.00 318247.00 CR PB  Bs6243..00[cR PB  PRCHA1L PRCHA1 PRCHA1 PRCHA1  25634930 5113825 .00</t>
@@ -638,10 +642,10 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
+      <c r="F7" t="n">
         <v>397763</v>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>S.T. LOKHANDWALA 771/72, TOWER ROAD SURAT - 395003 MSME : UDYAM-GJ-22-0140455 Ph 9428456552 / 9879577652 / 9924452786, Gujarat - 395003 Contact :0261-2434942 E-Mail :stlokhandwala@yahoo.co.in Yogesh Natwarlal Shah (HUF) Ledger Account  29-30, Samaysaar Bunglow, Nr. Nandini 3, VIP Road, Surat-395007,  01 Apr 25 To 31 Mar 26  Page 1 [Date | Particulars Vch Type|Vch Ref.| Vch No. Debit Credit  Balance a4, \ 05 Apr 25|Cr Sales GST Sales GS STU25-26/0104 149,170.00 49,170.00 Dr  pa)  NN SS sc om mo  20 May 25CrSalesGST |) [Sales GST] sTU25-261057) 41,930.00 53,851.00 Dr 04 Jun 25 STUDS. 260744 | 24,237.00 78,088.00 Dr| [TiJa25|Or BANKOFINGIA (| Reson [+585 |__| 7009800 32.00.0004 fiavazslor SaesesT Sees csr] «atl (@RO| =| oara.00 or  fievuas|er Saesest [Sees cst] iad gaarica| | _#2.07.00 br oeauges|r SaescsT—(saescst] _(swsaay Asisrooo| ‘| 59,267.00 be  vAugzafor Seesest (Ses cst] _—‘(sveraned aezpeoo| |_74.482.00 psauy2e|or SaescsT sass Gsif___‘useree am00900| | 99.44.0001 sSep2efor SaesGoT [Ses st] usar BOEEECO| | 169.291.0001  oe oazslor saesosT «Sees St] _—_—iuscmtfanove0] | 230,788.00  01 Nov 2o\Ciiecles Gomi MMM. l[Saesasti\ |) s715-262334 §16)406.00[ | 4,37\671.00 Dr  10 Nov 25 STUDS 26 74 @aiege00)) 1,78,912.00 Dr  25 Nov 25|Cr Sales GST STU25-26263% 18,885.00 AAR Sia 2,05,025.00 Dr Bi Cr Sales GST STL25-261263'| 45/456.00 iia 2,20,181.00 Dr  Carried Over 3,97,763.00 |1,77,582.00  continued...</t>
@@ -654,18 +658,14 @@
           <t>IMG_20260516_160021.jpg</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>RNS RE AN</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="n">
+      <c r="F8" t="n">
         <v>397763</v>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Pose | Parcs ‘(ver Type| Ven Ref verNo.[ | Debt] Grea] atone  Brought Forward 3,97,763.00 |1,77,582.00 RNS RE AN) Sales GS sruns26cead 44216.00| | 2,61,397.00 Dr  or Sasser sae  lor Seles GST [Sales Geter eee.00| «| 2,70.221.00 Dr er Sees GsT [Sales est|_(swasarf eaas.co| | 2,04 606.00 or orSaesGsT |saesest|  [rusaranl Mgeta0o) | 2.10,200.00 or  mM isaeervoo 77 se2c0  nga i a a EE]  23 Dec 25 07 Jan 26 09 Jan 26 16 Jan 26  — (o6) O 0) ra) N a</t>
@@ -678,11 +678,7 @@
           <t>IMG_20260516_160145.jpg</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ST TAX INVOICE</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Yogesh Natwarlal Shah (HUF)</t>
@@ -690,21 +686,21 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Dated</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>25-26/0104</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>16245.4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Dated</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>25-26/0104</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>16245.4</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -718,22 +714,18 @@
           <t>IMG_20260516_160208.jpg</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>TAX INVOICE</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>s Order No.</t>
+          <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="n">
+      <c r="F10" t="n">
         <v>2924.18</v>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>TAX INVOICE(Page 2) (ORIGINAL FOR RECIPIENT) Fi Dated S.T.Lo LA Invoice No. ley S ee row — asda erms of Payment 72 TAN SURAG ~ 395003 Delivery Note SME :u -GJ-22-0140455 189 ,5278  Ph 9428456552 / oa7Sa7 7662 19924452786 5138,5189,5: Ose eerrese GSTIN/UIN: 24ABIFS7716GA1ZD Reference No. &amp; Date.  State Name : Gujarat, Code : 24 Contact : 0261-2434942  E-Mail : stlokhandwala@yahoo.co.in Buyers Order No. Dated Consignee (Ship to) Dispatch Doc No. Delivery Note Date Yogesh Natwarlal Shah (HUF) scApr-25 29-30, Samaysaar Bunglow, Dispatched through Destination Nr. Nandini 3, VIP Road, Surat-395007, Y ; GSTIN/UIN : 24AAAHY 7933612 ‘Terms of Delivery State Name : Gujarat, Code : 24  Buyer (Bill to)  Yogesh Natwarlal Shah (HUF) 29-30, Samaysaar Bunglow,  Nr. Nandini 3, VIP Road,  Surat-395007, GSTIN/UIN : 2ZA4AAAHY 7933G1ZY  State Name s Gujarat, Code : 24 Place of Supply: Gujarat  Description of Goods HSN/SAC GST Quantity a ic Rate  ; ROUNDING OFF (S) 0.42  Amount  | Total | | | | | | ).00  | Saar Chargeable (in words) EVs OE |INR Nineteen Thousand One Hundred Seventy Only  Taxable [| cast [| sesmutest |) tom Value |" Ratei| amount | Rate | Amount | Tax amount Total: fe 2aSe4 GIN \ [It 40a. oa ANG | 1,462.09 2,924.18  Tax Amount (in words): INR Two Thousand Nine Hundred Twenty Four and Eighteen paise Only | Company's Bank Details |  Declaration _ Bank Name : BANK OF INDIA 1(1) Any query will not be except after 15th days. ‘Ale-No. + 270120110000049  (2) Interest @ 21% will be charged on over due bill. Branch &amp; IFS Code: Clock Tower &amp; BKID0002701  for 6.7. LOKHANDWALA pect ac “ag  Authorised Signatory 2:  SUBJECT TO SURAT JURISDICTION  This is a Computer Generated Invoice</t>
@@ -756,15 +748,15 @@
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>10625</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
-        <v>10625</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -788,19 +780,19 @@
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>25-26/0305</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>8677.059999999999</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>25-26/0305</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>8677.059999999999</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -814,25 +806,21 @@
           <t>IMG_20260516_160337.jpg</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ao  TAX INVOICE  f S.T, LOKHANDWALA</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>49440</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="n">
-        <v>49440</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -856,15 +844,15 @@
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>20540</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="n">
-        <v>20540</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -878,25 +866,21 @@
           <t>IMG_20260516_160433.jpg</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>TAX INVOICE</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>5295</v>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="n">
-        <v>5295</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -910,11 +894,7 @@
           <t>IMG_20260516_160519.jpg</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>OU F  BOOAL PAYBIGUSD JBINGWOD</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -942,15 +922,15 @@
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>5700</v>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="n">
-        <v>5700</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -964,25 +944,25 @@
           <t>IMG_20260516_160630.jpg</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>TAX INVOICE</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>. SURAT JURISDICTION his ts a-Computer Generated</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>25-26/121</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>25-26/121</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>4129</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1020,19 +1000,19 @@
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>07-05-2075</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>13750</v>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>07-05-2075</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>246225</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1046,21 +1026,21 @@
           <t>IMG_20260516_160752.jpg</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>TAX INMOIGE DAD</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SURAT JURISDICTION ims ts a Computer Generated</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>71600</v>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="n">
-        <v>71600</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1074,21 +1054,21 @@
           <t>IMG_20260516_160810.jpg</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>JUSL G</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>testiatsitioial</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>33247</v>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="n">
-        <v>33247</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1102,21 +1082,21 @@
           <t>IMG_20260516_160832.jpg</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>TAX INVOICE</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SURAT JURISDICTION This is a Computer Generated</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>30695</v>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="n">
-        <v>30695</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1132,7 +1112,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S.T. LOKHANDWALA</t>
+          <t>LOKWANESIG</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1140,15 +1120,15 @@
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>35076</v>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="n">
-        <v>35076</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1164,7 +1144,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TOWER ROAD SURAI</t>
+          <t>TOWER ROAD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1172,19 +1152,19 @@
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>25-26/2102</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>26268</v>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>25-26/2102</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>26268</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1208,15 +1188,15 @@
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>17127.59</v>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="n">
-        <v>46107.5</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1230,25 +1210,21 @@
           <t>IMG_20260516_160913.jpg</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>AIL A</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>5550</v>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="n">
-        <v>5550</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1262,25 +1238,21 @@
           <t>IMG_20260516_160922.jpg</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ARSENE</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>6400</v>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="n">
-        <v>6400</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1294,25 +1266,21 @@
           <t>IMG_20260516_160944.jpg</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>TAX INVOICE</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>28550</v>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="n">
-        <v>28550</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1336,15 +1304,15 @@
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>6125</v>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="n">
-        <v>6125</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1368,19 +1336,19 @@
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>25-26/2490</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>6125</v>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>25-26/2490</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>7228</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1394,25 +1362,21 @@
           <t>IMG_20260516_161016.jpg</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>LOKNANDIE</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>16012</v>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="n">
-        <v>16012</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1432,15 +1396,15 @@
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>15940.09</v>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="n">
-        <v>15940.09</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1464,15 +1428,15 @@
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>12844</v>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="n">
-        <v>12844</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1488,7 +1452,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>S.T. LOKHANDWALA</t>
+          <t>TAX INVOI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1498,10 +1462,10 @@
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="n">
+      <c r="F35" t="n">
         <v>241216</v>
       </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>y  ont i TAX INVOI “Bittern oe PENT) iain. O74 1D, TOWE Nvoice No Dated | Nile, SURAT - ee S1r2z (32-Dec-25 | YNltst es= : UDYAM-GJ-22-0140455 Bee ee Bae Mode/Terms of Payment | h w : , SS TIN Ez 'Reference No. &amp; Date. \Other References . 1ZD ETE a State Name : Gujarat, Code : 24 |Buyer’s Order No. |Dated Loniact : 0264-2434942 “SS Me E-Mail : Stlokhandwala@yahoo.co.in | Dispatch Doc No. Delivery Note Date Consignee (Shipta). Be 12-Dec-25 Wg Yogesh Nanna saline (HUF) | Dispatched through iPestination 29-30, Samaysaar Bunglow, " , ; ue Sunset vie Road, Terms of Delivery at , SSTIN;GUIN &gt; 2SAAANY7S33612Y | State Name : Gujarat, Code : 24 | Buyer (Bill to) Yogesh Natwarlal Shah (HUF) 29-30, Samaysaar Bunglow, Nr. Nandini 3, VIP Road, Suret-205007, GSTIN/UIN : 24AAAHY7933GiZY State Name : Gujarat, Code : 24 Place of Supply: Gujarat ! WN Description of Goods HSN/SAC GST Quantity Rate | per | Amount No. Rate | fs 7 'Piy Wood 8’x4’xi8mm 4412 | 18%) 2NCS 2,080.00 |Nos'| 4,166.86 2'Ply Wood 8’x4’x12mm 4412 18%) (NOS 1,632.00 |NOs | 9,792.00 3 Ply Wood 8’x4’x8mm ‘AAD i 48%! 3NCS | 1,376.00 'NOS 4,122.06 4 Freight ‘996712 18%] 1 times 1,500.00 times | VEL 5 Dewalt Angle Grinder 4" 850W DW801 820790, 18 % 2NOS 3,300.00 INOS | 6,600.00 6 Wall Cutter 4” 82075000 18%| 5NOS 120.00 [NOS | Gu 7 Core Cutter Pana 48mm (82075000. i 48 % j 4nCcS | 330.00 iNOS 1,920.00 74MM | | | | a | 8 Adopter Pin 853610 | 18% 2 NOS 60.00 NOS | 120.00 9/Fevicoal Skg (3506 | 18%) ttn, 1,650.00 tin 1,850.00 {0 Jumbura 8” 82075000 | 18% 3NOS 140.00 INOS 420.00 11 Araldite 450grm 3506 18 % 2NOS 550.00 INOS | 1,100.00 {2|Heatex 500gm 3506 18%| 2NOS/ = 290.00 Nos. 580.00 13 Tape 3 Mts 19017 18% 6 NOS | 170.00 |NOS | 1,020.00 4 Plastic Wrapping Roll 39269099 18%| 4.470 Kg 220.00 Kg) 983.40 15 HSS Bit 2.9 82075000 18%| ~ 3NOS | 35.00 NOS | 105.00 16'S S Screw 13x8 73181500 18 % |1,000 NOS 0.85 INOS | 850.00 e | |) 34,928.40 | SGST | 3,143.56 CGST 3,143.56 ROUNDING OFF (S) | | 0.48 | ee OU LAN | Total CCA 1 SALA / 241,216.00 | Amount Chargeahle (in words) FROE INR Forty One Thousand Two Hundred Sixteen Only | Taxable | CGST | _ SGST/UTGST | Total | Value | Rate Amount | Rate, Amount Tax Amount bi Le ad | UE Lh OHMS et ae aL i ath 4 ———_—-34,928.40 9% | 3. 443,561. 2%. —__3,143.56 | 6,287.42, Total: 34,928.4 3,143.56 3,143.56 6,287.12 | | i LU OS hdd Ta |Tax Amount (in words): {NK Six {housand {wo Hundred Eighty Seven ana Iweive paise Oniy | Company's Bank Details | ‘Declaration Bank Name : BANK OF INDIA | | (1) Any query will not be except after 15th days. Alc No. : 278120110000049 Ee Interest @ 21% will be charged on over due bill. Branch &amp; IFS Cade; Clock Tower &amp; BKID0002701 |Customer’s Seal and Sj nature for S.T. LOKHANDWALA { g VASTERESIAL Sa SKA | ‘i  | } 5  ) Shwe Oigitatyy | I" |  Aathorised Signatory |  SUBJECT TO SURAT JURISDICTION  This is a Computer Generated Invoice</t>
@@ -1516,7 +1480,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>S.T. LOKHANDWALA</t>
+          <t>24ABIFS7716A1ZD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1526,17 +1490,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>SURAT</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>14258</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>SURAT</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="n">
-        <v>14258</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1560,19 +1524,19 @@
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>25-26/2977</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>6385</v>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>24ABIFS7716A1ZD</t>
         </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>25-26/2977</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>6385</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1598,17 +1562,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>18487</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="n">
-        <v>18487</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1627,20 +1591,24 @@
           <t>S.T. LOKHANDWALA</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ry SUBJECT TO SURAT JURISDICTION This is a Computer Generated</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>09-01-2026</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>10010</v>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>09-01-2026</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>41801.8</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1664,19 +1632,19 @@
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>25-26/3222</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>15251</v>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>25-26/3222</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>45251</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1690,26 +1658,22 @@
           <t>IMG_20260516_161328.jpg</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>SHED</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>01-04-2029</t>
         </is>
       </c>
-      <c r="G41" t="n">
+      <c r="F41" t="n">
         <v>27681</v>
       </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>SHED  GSTIN :- 9, * ke Ledger  AAAHY7933612zy MID:1375] ** Prom 01-04-2029 t° 31-03-2026  ASHIRWAD PA SHOP NO Loe  AAGAM SHOPPING CE NTER, NEAR AGARWAL SCHOOL, VES  U, SURAT. SURAT  01-04-25 01-04=2550 02-04-255mg5 07-04-25 272 08-04-25 322 09-04-25 357 15-04-25 608 05-05-25 1401 25-06-25) Zone Pin 2767 02-07-25 2784 07-07-25 2878 l= (e253 22-07-25 3249 02-08-25 3499 06-08-25 3568 26-08-25 3938 16-09-25) Savi 9-00-2519 419 94-09-25 15316 06-1 0—255538 18-10-25 1 15-11-2 56069 27-11-25 13-12-25  29-01-26 31-01-2 6g89md9 03-02-26 9061"  Balance B/f Discount &amp; Commission  JVAC PRCHA1L PRCHAL PRCHA1 PRCHA1 PRCHA1 PRCHA1 PRCHA1 PRCHAL PRCHA1 PRCHA1 ACMAST PRCHAL PRCHA1 PRCHA1L PRCHA1 PRCHA1L PRCHAL PRCHA1 PRCHA1L AXISBA PRCHA1 PRCHA1 PRCHA1L PRCHA1 PRCHAL1 PRCHA1L PRCHAL PRCHA1 PRCHA1 PRCHAL PRCHA1 PRCHAL PRCHA1 PRCHA1 PRCHA1 PRCHA1 PRCHA1 PRCHA1 PRCHA1  PRCHAI1  12630.00  -12265.00  1615.00 420.00 770.00  1600.00  1250 .O© 450.00  1050.00  2500.00  12754.00 CR 10250.00 CR JD 10330.00 CR PB 10730.00 CR PB 10830.00 CR PB 11330.00 CR PB 11880.00 CR PB 12630.00 CR PB 13080.00 CR PB PB 14640.00 CR PB 15240.00 CR PB 2610.00 CR BP 4225.00 CR PB 4645.00 CR PB 5415.00 CR PB O15. OO)} CR jee 8265.00 CR PB 8715.00 CR PB 9765.00 CR PB 12265.00 CR PB r BP 3500.00 CR PB 3900.00 CR PB 5500.00,)CR PB 6000.00 CR PB 6650.00 CR PB 7650).00)CR PB PB PLS LO 00) CREB 11640.00 CR PB LAri90) 0.0 CREB 15280.00 CR PB 15440.00 CR PB 17916.00.CR PB 18916.00 CR PB 22966.00 CR PB 24311200 CR PB 26251\100) CR’ PB 2OS 1) OONCR EB  27681.00 CR, PB</t>
@@ -1728,19 +1692,19 @@
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>01/04/2025</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>42630</v>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>01/04/2025</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>42630</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1754,26 +1718,22 @@
           <t>IMG_20260516_161500.jpg</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>ASHIRWAD PAINTS</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>01/04/2025</t>
         </is>
       </c>
-      <c r="G43" t="n">
+      <c r="F43" t="n">
         <v>52636</v>
       </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>yO | LUOe  NI 2 AON Tove a  ASHIRWAD PAINTS Ledger From : 01/04/2025 SHED To —_: 13/02/2026 Date : t ____ SHESHD 23/12/2025 __ Nae Book ; Wy Debit Credit Balance W7449"SALEGST - VESU $8 1.00000 F 7,650.00 DR «7483"'SALEGST - VESU SB 10,510.0 ; pees a, (2,860.00 510.00 DR AN2i2025 «@@7494" SALEGST - VESU SB “1,000.00 11,510.00 DR CASHV- atet 26/ 6/2/2025 RRR ALECST - VESU SB 130.00 11,640.00 DR 02/01/2026 7866" SALEGST - VESU SB 3.15000 14.790.00 DR CASHV- 10/01/2026 8142" SALEGST - VeSU SB 490.00 15,280.00 DR CASHV- ps 12/01/2026 @8273"SALEGST - VESU SB 9160.00 15,44000DR § CASHV- 16/01/2026 8360"SALEGST - VESU SB ©2)476'00° 17,916.00 DR CASHV- 19/01/2026 @8507@SALEGST - VESU SB 1,000.00 18,916.00 DR CASHV- 21/01/2026 @8603)/SALEGST - VESU SB 4,050.00 22,966.00 DR CASHV- 27/01/2026 8853) SALEGST - VESU SB 1,345.00 24,311.00 DR CASHV- 29/01/2026 9§8900"SALEGST - VESU SB 1,940.00 26,251.00 DR CASHV- 31/01/2026 8974" SALEGST - VESU SB 780.00 27,031.00 DR CASHV- 03/02/2026 9061" SALEGST - VESU SB 9650.00 27,681.00 DR CASHV- 05/02/2026 @21449SALEGST - VESU SB 960.00, porratooroR CASHV- uaa _ iw During the Period 17,491.00 42,386.00 Rs. 52,636.00 R</t>
@@ -1786,21 +1746,17 @@
           <t>IMG_20260516_161531.jpg</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>GUJARAT</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>4000.02</v>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="n">
-        <v>4000.02</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1816,7 +1772,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ASHIRWAD PAINTS  OPPING WORLD</t>
+          <t>ASHIRWAD PAINTS OPPING WORLD, NEAR-</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1824,19 +1780,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>41/27/25</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>41/27/25</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>516</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1850,25 +1806,21 @@
           <t>IMG_20260516_161557.jpg</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>TAX INVOICE</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>13/12/2025</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>25</v>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>13/12/2025</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>41250</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1884,7 +1836,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BN  ASHIRWAD PAINTS</t>
+          <t>ASHIRWAD PAINTS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1892,19 +1844,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>500.01</v>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>15/12/2025</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>500.01</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1928,19 +1880,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>16/12/2025</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>650.01</v>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>16/12/2025</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>650.01</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -1978,15 +1930,15 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>2820.02</v>
+      </c>
+      <c r="G50" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="n">
-        <v>2820.02</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2002,19 +1954,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ASHIRWAD PAINTS</t>
+          <t>ASHIRWAD PAINTS: AAGAM SHOPPING WORLD, NEAR- AGRAWAL SCHOOL, VESU</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>1000.02</v>
+      </c>
+      <c r="G51" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="n">
-        <v>1000.02</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2038,19 +1990,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>26/12/2025</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>130.01</v>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>26/12/2025</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>130.01</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2064,21 +2016,17 @@
           <t>IMG_20260516_161757.jpg</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>SHOP NO</t>
-        </is>
-      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="n">
+        <v>4500.01</v>
+      </c>
+      <c r="G53" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="n">
-        <v>4500.01</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2094,23 +2042,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ASHIRWAD PAINTS  LD NEAR</t>
+          <t>ASHIRWAD PAINTS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>40/01/2026</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>415.25</v>
+      </c>
+      <c r="G54" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>40/01/2026</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>415.25</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2124,26 +2072,22 @@
           <t>IMG_20260516_161829.jpg</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>SHOP NO D</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>42/01/2026</t>
         </is>
       </c>
-      <c r="G55" t="n">
+      <c r="F55" t="n">
         <v>460</v>
       </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>SHOP NO D-4 AAGAM  /HaH  ee a M/s SHED |  29-30 SAMAYSAAR BUNGLOW ae Di 42/01/2026 NR NANDINI 3 VIP ROAD SURAT 395007. al , oe Contact 2); RANCHOD BHAI GST No. :24AAAHY7933G6 1ZY PAN No. {AAAHY7933G__ Mobile Z 4 ee Rate Disc% Disc% GST% KJ GLOSS ENAMEL BROWN 3208 ‘|’ fh, Pes 460.00 15.25 18.00 500 ML a wrth we 1 0.500 (ees ONE HUNDRED SIXTY ONLY | GST Total Rs. | TAXABLE Rs. ) Nah S5 589 CESTHi RS. 42.20 SGST Rs. 42.20 Total Rs. 159\99 460.00 | |Terms &amp; Conditions : », For ASHIRWAD PAINTS 5 1.Subject to SURAT Jurisdiction Wa 2 NNT GR BANK DETAILS:- KOTAK MAHINDRA BANK(PIPLOD BRANCH) | tL : A/C bye: 3812805412 |FSC-KKBK0000877 UPI-7878368000@KOTAK mh ane Received By : Authorised. Pa ch  INBHGST1HHWST  Shree Ganeshay Namah  SHOPPING WORLD, NEAR- AGRAWAL SC  Received Mob No :  _-  Sy  ~  Origina ASHIRWAD PAINTS  HOOL, VESU ,  Surat GUJARAT 24 395007 Phones :(O ) 8140942000  PAN No. : AGDPV7018G  ABV: “4142126, 4:27PM</t>
@@ -2156,25 +2100,21 @@
           <t>IMG_20260516_161856.jpg</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>MARS IR SP</t>
-        </is>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>46/01/2026</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>2476.01</v>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>46/01/2026</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>4000</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2194,15 +2134,15 @@
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G57" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="n">
-        <v>1000</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2216,25 +2156,21 @@
           <t>IMG_20260516_161927.jpg</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>ASSHIRWAD PAINTS SHOP NO D</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr">
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1/21/26</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>952.4</v>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1/21/26</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>4050</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2248,29 +2184,25 @@
           <t>IMG_20260516_161941.jpg</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>ASHIRWAD PAINTS</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1/29/26</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1940.01</v>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1/29/26</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>1940.01</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2294,19 +2226,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>31/01/2026</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>780</v>
+      </c>
+      <c r="G60" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>31/01/2026</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>780</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2320,29 +2252,25 @@
           <t>IMG_20260516_162022.jpg</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>ASHIRWAD PAINTS</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>650.01</v>
+      </c>
+      <c r="G61" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>03/02/2026</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>650.01</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2356,29 +2284,25 @@
           <t>IMG_20260516_162042.jpg</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>ASHIRWAD PAINTS  SHOP NO D</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>05/02/2026</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>50.85</v>
+      </c>
+      <c r="G62" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>05/02/2026</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>60.01</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2402,19 +2326,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>27/01/2026</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1345</v>
+      </c>
+      <c r="G63" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>27/01/2026</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>1345</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2428,29 +2352,25 @@
           <t>IMG_20260516_162230.jpg</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>ASHIRWAD PAINTS</t>
-        </is>
-      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>02/04/2025</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>18</v>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>02/04/2025</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>80</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2474,19 +2394,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>07/04/2025</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>370.47</v>
+      </c>
+      <c r="G65" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>07/04/2025</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>400</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2502,7 +2422,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>wriygina  ASHIRWAD PAINTS Factory</t>
+          <t>ASHIRWAD PAINTS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2510,19 +2430,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>08/04/2025</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>100.06</v>
+      </c>
+      <c r="G66" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>08/04/2025</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>100.06</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2546,19 +2466,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>09/04/2025</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>448.92</v>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>09/04/2025</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>500</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2574,23 +2494,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ASHIRWAD PAINTS  SHOP NO D</t>
+          <t>ASHIRWAD PAINTS SHOP</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr">
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>15/04/2025</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>523.8200000000001</v>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>15/04/2025</t>
-        </is>
-      </c>
-      <c r="G68" t="n">
-        <v>550</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2604,29 +2524,25 @@
           <t>IMG_20260516_162415.jpg</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>SHOP NO D</t>
-        </is>
-      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>05/05/2025</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>750.02</v>
+      </c>
+      <c r="G69" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>05/05/2025</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>750.02</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2642,7 +2558,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Office,</t>
+          <t>ASHIRWAD PAINTS G-4, DEVANG SHOPPING CENTER NERA SARGAM SHOPPING PARLE POINT ~MSME -</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2650,19 +2566,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>25/06/2025</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>450</v>
+      </c>
+      <c r="G70" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>25/06/2025</t>
-        </is>
-      </c>
-      <c r="G70" t="n">
-        <v>450</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2678,7 +2594,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ASHIRWAD PAINTS  .</t>
+          <t>ASHIRWAD PAINTS .</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2686,19 +2602,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>300</v>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>02/07/2025</t>
-        </is>
-      </c>
-      <c r="G71" t="n">
-        <v>310</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -2722,19 +2638,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G72" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>02/07/2025</t>
-        </is>
-      </c>
-      <c r="G72" t="n">
-        <v>1250</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -2750,23 +2666,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ASHIRWAD PAINTS Office</t>
+          <t>ASHIRWAD PAINTS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr">
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>07/07/2025</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>600</v>
+      </c>
+      <c r="G73" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>07/07/2025</t>
-        </is>
-      </c>
-      <c r="G73" t="n">
-        <v>600</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -2782,7 +2698,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>ASHIRWADL PAINTS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2790,19 +2706,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>22/07/2025</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>4615</v>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>22/07/2025</t>
-        </is>
-      </c>
-      <c r="G74" t="n">
-        <v>4615</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -2818,7 +2734,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ts Factory</t>
+          <t>ASHIRY.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2826,19 +2742,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>02/08/2025</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>420.01</v>
+      </c>
+      <c r="G75" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>02/08/2025</t>
-        </is>
-      </c>
-      <c r="G75" t="n">
-        <v>420.01</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -2854,7 +2770,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Orightial Office</t>
+          <t>ASHIRWAD PAINTS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2863,15 +2779,15 @@
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>06/08/2025</t>
         </is>
       </c>
-      <c r="G76" t="n">
+      <c r="F76" t="n">
         <v>652.54</v>
       </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>Orightial Office Address: ASHIRWAD PAINTS Factory Address:  G-4, DEVANG SHOPPING CENTER NERA SARGAM SHOPPING  PARLE POINT - MSME - UDYAM-GJ-22-0335197 State Code: 24 SURAT 395007 GUJARAT State Code: 24 prance: Phone: M-7878368000 :  a4 Invoice No. : V¥-35638 GST No. : 24AGDPVv7018G1zD TAX INVOICE avers | gefoea25 PAN No. : AGDPV7018G Tae  i ignee (Shipped to) : Details of Receiver (Billed to) : Details of Consignee (Shipp  SHED  29-30 SAMAYSAAR BUNGLOW NR NANDINI 3 VIP ROAD SURAT 395007  |'GUJARAT State Code: 24 /Phone: 9429331884 GST No.: 24AAAHY7933GiZY (PA No.: ASAHY7S336  -. i i Discount Tax @. Description Pcs Quantity Unit Rs. % Rs. Rate |  WATER PAPER PERFORMER 400 NO. 10 Pcs 200.00 15.25 -30.51 18.00% WATER PAPER PERFORMER150 NO. 10 Pcs 200.00 15.25 -30.51 18.00% WATER PAPER PERFORMER 1500 NO. 10 Pes 250.00 15.25 -38.14 18.00% WATER PAPER PERFORMER 2000 NO. 4 Pcs 120.00 15.25 -18.30 18.00%  Round off  Due Date : 06/08/2025 Rupees: SEVEN HUNDRED SEVENTY ONLY oats:  GST 18.00% Total Rs. | Bank Details ASHIRWAD PAINTS TAXABLE Rs. 652.54 652.54 Bank Name = : KOTAK MAHINDRA BANK LTD. CGST Rs. 58.72  58.72 | a, d SGST Rs. a saz | Ale No. 3812805412 Sranch : PIPLOD  | Total Rs. 77D. KKBKCOO0877  For ASHIRWAD PAINTS  Authorised Signatory  INESGST3GHRL</t>
@@ -2892,10 +2808,10 @@
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="n">
+      <c r="F77" t="n">
         <v>22.98</v>
       </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>TUNDELSOPAN  Aoyeubig pasuoyuyny ‘UONIIPSUNP LYYNS 01 Welgng (9) “S1eP anp ayy wo4) pabieys aq jeys ‘wd %S'2 10 aes ayy Aq epew aq jjeus ING SIU} JO jUaWAed su, (“s) ysl suang je Paynedsep ase spoos BY (‘p) 0 Awenb uw a6ueya Aue JO sjulejdus  WNleAesd pue spooB jo Ayjenb oy  SLINIVd GYMUIHSy 404  ZLB0000%2YY} 00°000'L ‘Sy 12101 |  dordid young | von apy | 22.98 1Z'9L 6Z"bL sy sos CL PSO8CL8E NOV | oc-06 1z'9L 6Z'bL ‘sy S99  ‘O17 YNVE VYGNIHVI MVLOM OWEN MURR | og gLb'L Sb Lb9 by LLs ‘SY FIGVXVL SLNIVd GVMXMIHSY SHRISG YURW | sy jeyoy %00'81 %00°S iso XING G3EGNNH XIS GNYSNOHL 3NO :saedny  . ‘ S 210 G0'008 } palit: ze S202/80/92 : 3a}2qG ang  ie pogiaaemn |  c0'0-  %00G  g9G°8¢- 92% 007009 00°02 Sod 0€ 802S( MWA LAMDVd ) TWWS HLOIO NYOM INVS 180299  %O0O8L EO Z- S@Si 00°0S 00°0S wun) Lt 0 60cE HQVHS (YANIVLS) YSN3aLS a FOOSE Le viL- S¢St 00°0S6 00°0S6 Sq | 0 VL8E 8110) YSNIHL 108 ON WAINSd bi  ] lun ARUeND so OVS uoRdioseq - xe) 1UNODSIG sa sith A) MEATS) ahs /NSH ‘ia - ‘@ - ; af |  SECSZANVVY ON Wd AZLOSEBZAHVV PZ “ON 199 LESLESSTHS -OU0UG Ve -8DND BIS LYNE 200568 ivans GVOU diA © INIGNYN UN MO TONAG YVVSAVAVS O€-6Z gays : (0} peddiyg) eaubisuog jo sjlejaq * (0) Paitig) sanisoay jo s1iajeq  SCOcBO/ST - seq S8LOZAdGOW : “oN Ng BESE-A &gt; “ON SoI0AKy SOIOAN! ¥w he G2+98102Adaoypz &gt; “ON iSS  “eles 00089¢E8282-;W :2U0Ud pz :@P09 ajeig ¥e *8P0D ayBI5 LVavrnd 2o0s6e LVuNsS  v5  tsseippy Auojoe4 ‘SSOIPPY SIO  fee Buin</t>
@@ -2908,29 +2824,25 @@
           <t>IMG_20260516_162846.jpg</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>URMIE SAL</t>
-        </is>
-      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G78" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>16/09/2025</t>
-        </is>
-      </c>
-      <c r="G78" t="n">
-        <v>4250.8</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -2946,7 +2858,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LSOHENI</t>
+          <t>WEL S2/BL/6 ASY 41S</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -2976,19 +2888,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>24/09/2025</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>900.02</v>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>24/09/2025</t>
-        </is>
-      </c>
-      <c r="G80" t="n">
-        <v>1050</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3004,7 +2916,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ASHIRWAD PAINTS  SHOP NO D</t>
+          <t>ASHIRWAD PAINTS SHOP</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3012,19 +2924,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>2500.01</v>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>24AGDPV7018G1ZD</t>
         </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>06/10/2025</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
-        <v>2500.01</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3038,29 +2950,25 @@
           <t>IMG_20260516_163157.jpg</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>SHED</t>
-        </is>
-      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>01-04-2025</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>30883</v>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>24AANFH9851K1Z2</t>
         </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>01-04-2025</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
-        <v>30883</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3076,7 +2984,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SURAT</t>
+          <t>SHED, SURAT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3084,20 +2992,20 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Due</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Due</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
           <t>23/03/2026</t>
         </is>
       </c>
-      <c r="G83" t="n">
+      <c r="F83" t="n">
         <v>67336</v>
       </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>To, SHED, SURAT  Dear Sir,  HVK ENTERPRISE  B/8, HARIOM MILL COMPUND, NR VED  ROAD POLICE CHOWKI SURAT  Mobile: 9925349542,9726265848.  Report Printing Date : 23/03/2026  With due respect, we have to inform you that in our books of account amount of Rs. 67,336.00 DB has been lying with you as on date 23/03/2026 Detail is as per following :  SDRC RE 9 de DS  Date Bill No Due Days Bill Amount Pending Amount 05/11/2025 € 5-26 139 7204.00 DB %3308'00 be 15/11/2025 GT, -26 129 3890.00 DB 3890100 DB 20/11/2025 Gill -26 124 2300.00 DB 2300.00 bs 12/12/2025 GT/ -26 102 6793.00 DB §6793,00 DE 12/12/2025 GT/7667/25-26 102 1050.00 DB @050100 De 13/12/2025 GT/7i27/25- 26 101 2400.00 DB .: DB 26/12/2025 GT/ 26 88 14875.00 DB 0 DB 21/01/2026 GT/ -26 62 16879.00 DB 6879.00 DB 09/02/2026 GT/9219/25-26 43 1699.00 DB 1699100 DB 18/03/2026 GT/10136/25-26 6 14142.00 DB 4142.00 DB  Kindly arrange to send above said amount as early as possible.  Your's Faithfully,  For, HVK ENTERPRISE  Pending Amount :  2@</t>
@@ -3112,7 +3020,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HVK ENTERPRISE  B</t>
+          <t>HVK ENTERPRISE B/8, HARIOM MILL COMPUND,</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3120,19 +3028,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>05/11/2025</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>7204</v>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>05/11/2025</t>
-        </is>
-      </c>
-      <c r="G84" t="n">
-        <v>7204</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3146,11 +3054,7 @@
           <t>IMG_20260516_163340.jpg</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>AL MATL</t>
-        </is>
-      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
@@ -3170,7 +3074,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DT P HVK ENTERPRISE</t>
+          <t>HVK ENTERPRISE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3178,19 +3082,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>20/11/2025</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1949</v>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>20/11/2025</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
-        <v>2299.82</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3206,7 +3110,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HVK ENTERPRISE  B</t>
+          <t>HVK ENTERPRISE B/8, HARIOM MILL COMPUND,</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3214,19 +3118,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>6792.76</v>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>12/12/2025</t>
-        </is>
-      </c>
-      <c r="G87" t="n">
-        <v>6792.76</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3242,23 +3146,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HVK ENTERPRISE  B</t>
+          <t>HVK ENTERPRISE B/8, HARIOM MILL COMPUND,</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr">
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1049.62</v>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>24AANFH9851K1ZS</t>
         </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>12/12/2025</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
-        <v>1049.62</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -3272,11 +3176,7 @@
           <t>IMG_20260516_163511.jpg</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>UIYIIM</t>
-        </is>
-      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
@@ -3294,11 +3194,7 @@
           <t>IMG_20260516_163542.jpg</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>YONG UAYD</t>
-        </is>
-      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
@@ -3318,7 +3214,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LONDIPSLING</t>
+          <t>LONDIPSLING,</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -3340,19 +3236,19 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HVK ENTERPRISE  B</t>
+          <t>HVK ENTERPRISE B/8,</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr">
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="n">
+        <v>1440</v>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="n">
-        <v>1440</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3368,7 +3264,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HVK ENTERPRISE  B</t>
+          <t>HVK ENTERPRISE B/8. HARIOM MILL COMPUND.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3377,15 +3273,15 @@
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="G93" t="n">
+      <c r="F93" t="n">
         <v>14142</v>
       </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>HVK ENTERPRISE  B/8. HARIOM MILL COMPUND. NR VEDROAD POLICE CHOWKI SURAT Mobile:9925349542,9726265848.  Debit Memo TAX INVOICE Duplicate NUso li SHED Invoice No. &gt; GT/10136/25-26  29-30. SAMAYSAAR BUNGLOW NR. NANDANI 3 Date &gt; 18/03/2026  VIP ROAD SURAT  SURAT - 395007 (M): 429331881 Salesman &gt; BUAUTIK GSTIN Now SYAVATIY7933G1ZY Place of Supply: 24-Gujarat IRN | 1 Sr. Produet Name USN NC Qty Rate SD. C.D. Taxable = GST Amount Net % %Q Amount %, CGS SGSI Amount 1 FINNOQ S3T) ALASRING TAPE- ASAD 2.00 R 103.39 206.78 18.0 18.6] 18.61 244.00 (I2N20 YARD) 2 FINNO 3311 MASKING TAPE- 48114100 3.00 R 103.39 310.17 18.0 Qin92 27.92 366.0] (Q4N20 YARD) 3 VINNO S311. MASKING TAPE- 48114100 3.00 R 103.39 310.17 18.0 27.92 27.92 366.01 (36X20 YARD) | FINNO 3311 MASKING TAPE- AS8T14100 3.00/R 103.39 | 310.17 18.0 27.92 27.92 366.01 (J8N20 YARD) r FINNO MASKING UAPE- 48114100 2.00 PCS 211.86 | 423.72, 18.0 38.13 38.13 499.98 | (60X20 YARD) | 6 FINNOCLR TAPE-~(36N40 39191000 3.00 PCS 122.88 368.64 18.0 PES al'8 33.18 435.00 YARD) 7 EDONOVC TLR TEN PRS) S919 1000 3.00 PCS 122.88 368.64 18.0 33.18 33.18 435.00 YARD) | 8 FIXNO BROWN EAPE-(18X40 39191000 3.09) PCS_, 122.88 368.64 18.0 33.18 33.18 435.00 YARD) \ is" 9 FIXXO BROWN PAPE“72N40 39191000 3.00 PCS 122.88 | | 368.64 18.0 33.18 33118 435.00 YARD) } b / 10) CUMI BABLU STEAREATED - OS8O52040) 200,00 PCS 13.56 2712.00), 18:0 244,08 Def 3200.16 | 320 GRII Ti CUMPEAPPL SURTIA PAPER- 68052040 150.00: PCS 5.93 889.50. 18.0 $0.06 $0.06 10:49.62 150 GRIT 12) CUMIWARIOR WATER PAPER 08052040 150.00 PCS 10.20 1530.00. 18.0 137,70 137.70 1805.40 - 100 GRU | [3 CUMI WARIOR WATER PAPER 68052040 150.00 PCS 11.02 1653.00 18.0 148.77 148.77 1950.54 - 600 GRII 9: CUM! WARTIOR WATER PAPER, — 68052040 150.00 PCS 14.43) 2164.50, 18.0 194.8] 194,81 25541,12 . - 1200 GRI|  GSTIN No 244A ANFI985TKIZS  Toll (1984.57  1078.64 1078.64 l4 141.85 Bank Name HDC BANK  Banh A/c. No. SOZUNOSYBR8362 RTGS/AFSC Code HDECOOOT708  (),00  0.00, Round OF OL15  Bill Amounts Paarteen Thousand One thindved lorty Tivo Only  Grand Total 14,142.00  Terms &amp; Condition :  !. Our rish and responsibility ceases as soon as the goods leave our premises, 2s diterest a\tStaip.a, will be charg  ed if pavmnent is notimade within 19 days. } 3. Caods once sd Will nor Ae taken\back Subject to SURAT! Jurisdiesion only  ee T  Beet ia cs</t>
@@ -3400,7 +3296,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HVK ENTERPRISE  URAT B</t>
+          <t>HVK ENTERPRISE URAT B/8. HARIOM MILL COMPUND,</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3408,19 +3304,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>31/25-26</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1699</v>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>24AAAHY7933GIZY</t>
         </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>31/25-26</t>
-        </is>
-      </c>
-      <c r="G94" t="n">
-        <v>1699.2</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -3434,29 +3330,25 @@
           <t>IMG_20260516_163920.jpg</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>HVK ENTERPRISE  B</t>
-        </is>
-      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>18/04/2025</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>24AAAHY7933GIZY</t>
         </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>18/04/2025</t>
-        </is>
-      </c>
-      <c r="G95" t="n">
-        <v>2950</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -3472,20 +3364,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>HVK ENTERPRISE  B</t>
+          <t>HVK ENTERPRISE B/8, HARIOM MILL COMPUND,</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>28/05/2025</t>
         </is>
       </c>
-      <c r="G96" t="n">
-        <v>1902.16</v>
-      </c>
+      <c r="F96" t="n">
+        <v>1902</v>
+      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>HVK ENTERPRISE  B/8, HARIOM MILL COMPUND, NR VEDROAD POLICE CH Mobile:9925349542,9726265848.  Debit Memo TAX INVOICE  SRD 29-21) SAMAYSAAR BUNGLOW NR. NANDANI 3  OWKI SURAT  Original  Invoice No. : GT/1761/25-26 Date + 28/05/2025  VIP KOAD SURAT : ; St AT - 395007 (M): 9429331881 Salesman + LIMANSIIU GSTIN No. AAATY7933GIZY Place of Supply: 24-Gujarat IRN : ) | sr.| PR TISN/SAC Qty . Rate BDH) CID) || iaable A GST | apni Net Gn | % Amount % CCS SGST Amount 1 |CUMI WARIOR WATER 68052040 we PCS 10.20, 510,00) 18.0 45.90 45.90 601.80 | PAPER - 400 GRIT ! 2 |CUMI WARIOR WATER 68052040 J 30.00 PCS 11.02 551.00} 18.0 49.59 49.59 650.18 ~~—}PAPER - 600 GRIT 3 | CUMI WARIOR WATER 68052040 50.00 PCS 11.02) 551.00} 18.0 49.59 49.59 650.18 PAPER - $00 GRIT  ) bet \ Mh | | GSTIN No.: 24AANFII9851K1ZS ‘Total 1612.00 145.08 145.08 1902.16 Bank Name + HDFC BANK : Branch : KATARGAM ‘ f Bank A/c. No. + $0200059888362 RTGS/IFSC Code: HDFC0001708 (),00 Round Off -0.16  Bill Amount: = One Thousand Nine Ilundred Two Only  Grand Total 1,902.00  RPRISE  Terms &amp; Condition: } forivk b "OM, y  1. Our risk and responsibili) ceases as soon as the goods leave our premises. e}  ‘ pa @18% p.a. will be charged if payment is not made within 45 days. | CE . Goods once sold will not be taken back. 4, "Subject to 'SURAT' Jurisdiction only. L.&amp;.O.1L" Rapp ee $$ TH</t>
@@ -3498,11 +3390,7 @@
           <t>IMG_20260516_164004.jpg</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>SD UOOS</t>
-        </is>
-      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
@@ -3520,11 +3408,7 @@
           <t>IMG_20260516_164017.jpg</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>DUO SPOOL</t>
-        </is>
-      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -3544,7 +3428,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HVK ENTERPRISE  B</t>
+          <t>HVK ENTERPRISE B/8, HARIOM MILL COMPUND,</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3552,19 +3436,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>12/07/2625</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>2069.96</v>
+      </c>
+      <c r="G99" t="inlineStr">
         <is>
           <t>24AAAHY7933GIZY</t>
         </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>12/07/2625</t>
-        </is>
-      </c>
-      <c r="G99" t="n">
-        <v>2069.96</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -3578,29 +3462,25 @@
           <t>IMG_20260516_164111.jpg</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>HVK ENTERPRISE  B</t>
-        </is>
-      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>3450</v>
+      </c>
+      <c r="G100" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>14/08/2025</t>
-        </is>
-      </c>
-      <c r="G100" t="n">
-        <v>3450</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -3614,26 +3494,22 @@
           <t>IMG_20260516_164157.jpg</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>CSD A</t>
-        </is>
-      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>10/09/2025</t>
         </is>
       </c>
-      <c r="G101" t="n">
+      <c r="F101" t="n">
         <v>6763.02</v>
       </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>t 4 of. on. &gt; &lt; - CSD A cgtaaS, Sys ots. Fait Meee aEO) Rea ENN sya fe On Gee Bt ee Reet ine pasa she Be ae A Sei oe clea eee oh PINES tt a - 7 d a Cy a ¢ Moreh ‘* a) - . CieX ¥ c ode ae ee RO , See ales of V7 tse SOE Be RS ie oar oe  B/8, HARIOM MILL COMPUND, NR VEDROAD POLICE CHOW  HVK ENTERPRISE  KI SURAT  Mobile:9925349542,9726265848.  Original  | Debit Memo - M/ TAX INVOICE NMOS. SHED Invoice No. + G1/5225/25-26 29-3 S / 7O 30. SAMAYSAAR BUNGLOW NR. NANDANI 3 Date 10/09/2025 ce nan” be! HIMANSIIU GSI SURAT - 395007 (M): 9429331881 Lite NNo.: 24 AAAWY 7933G17.Y Place of Supply: 24-Gujarat IRN ; | Ler Amount Net Sr. Product Name USN/SAC Qly Rate s.p. | C.D. ‘Vaxable || GST ‘ = Code 0% % Amount % CGS SGST AC t oe &amp; a &gt; IL » p Wer} aE oi }— ea — —/ - -* = ar G 69.1 69.12 906.24 1 | BONDONE UNITITE 1 - 39089090 1.60 KG 480.00 768.00) 18.0 69.12 5 (0.800KG) ¢ d 0 60.48 60.48 792.96 2 | BONDONE UNITITE R - (1 KG) 39073010 2.00 KG 336.00 672.00} 18 9 : “&lt; 510.00] 18.0 45.90 45,90 601.80 3 | CUMI WARIOR WATER PAPER 68052040 50.00 PCS 10.20 0 - 400 GRIT ss a S oS 51.00) 18.0 49.59 49.59 650.18 4 |CUMI WARIOR WATER PAPER 68052040 50.00 PCS 11.02 551.0 - $00 GRIT f 51.38 5 aS d 21.50} 18.0 64.94 64.94 851.3% @ 5 |CUMIWARIOR WATER PAPER | 68052040 50,00 PCS 14.43 7 - - 1200 GRIT - “C | ; 109.07 109.07 1430.00 6 |CUMI PAPER ROLL 4”- 60 68052040 1.00 PCS 1211.86 1211.86] 18.0 | GRIT (S0 MTR) 53() 46 Se) S 1297.00| 18.0 116.73 116.73 1530. 7 |CUMI CONCORD ROLL 4°X55__ | 68051010 1.00 PCS 1297.00 MTR- 80 GRIT d | | «@ aly GSTIN No. 24AANFH985IIKIZS Total $731.36 515.83 6763.02 Bank Name HDFC BANK Branch: 4 ATARGAM 0.00 Bank A/c. No. 50200059888362 I RTGS/AVSC Code LIDFC0001 708 0.00 : Round OU -().02 Bill Amount: Six Thousand Seven Ifundred Sixty Three Only Yerms &amp; Condition : 1, Our risk and responsibility ceases as soon as the goods leave our premises. 2. Interest @18% p.a. will be charged if payment 1s not made within 45 days.  KW &amp; OM"  3. Goods once sold will not be taken back. 4, "Subject to 'SURAT" Jurisdiction only.</t>
@@ -3657,15 +3533,15 @@
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>20/09/2025</t>
         </is>
       </c>
-      <c r="G102" t="n">
+      <c r="F102" t="n">
         <v>1867.5</v>
       </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>HVK ENTERPRISE Re  Yr : a ve B/8. i a ie io &gt;’, HARIOM MILL COMPUND, NR: VEDROAD POLICE CHOWK! SURAT es ns - £3 9 IAQ LP oo a al . § ’ Debit Memo Mobile:9925349542,9726265848. mia eae ; Ti Original baer, ORNS: 3 [Ms = SHED Tax Ga : Bae te &lt; ia Invoice No. : GT/5618/25-26 ie oe ae 29-30.S A " ey Se “a SAMAYSAAR BUNGLOW NR. NANDANI3 Date : 20/09/2025 ; wi tn Sed nea VIP ROAD Foo ORE xe. ae Ts Ue Gat OS 1 ‘ . ‘ x. S ; = SURAT - 395007 (M): 9429331881 Salesman &gt; TMMANSIIU Tae, Eee xf GSTIN No, : DVN NEN FRAC: : off A eh et nee pam -4AAAHY7933G1Z.Y Place of Supply: 24-Gujarat Send ges IRN : nee ok Be 7 a . a. ee ae, le Apap vlan \ { 1a in 7) Me Cy Sr. Product Name HISN/SAC Qty Rate S.D. C.D. Vaxable GST Amoun Net rete Caer Code % %, Amount % CGST SGST Amount ae = Ls tk 1 | CUM APPU SURTIA PAPER- 68052040 150.00 PCS 5.93 889.50) 18.0 80.06 80.06 1049.62 es vo wi Sse 150 GRIT ie SY 2 = aS ) } 1.02 61.02 800.04 ’ apie. " 2 |CUMIBABLU STEAREATED - | 68052040] $0.00 PCS 13,56 Te OR Oe BS a eS 320 GRIT ba pend see) JIN Pt = | ¥ or  GSTIN No.: 24AANFH985I1K1ZS Total 1867.50 141.08 141.08 1849.66  Bank Name [DFC BANK Branch ) kK ATARGAM 0.00 erthe OF Bank A/c, No. * — $0200059888362 252 RIGS/IFSC Code : J{DFC0O001708 es a Round Of ().34 : Tey Bill Amount: One Thousand Bight Ilundred Fifty Only i Sat, ap Grand 19) 1,850.00 Se Rn | p Y, uk ey rr 1 Terms &amp; Condition ; WV \ “or. er. ip ead 1, Our risk and responsibility ceases as soon as the goods leave aur premises. ( : “ae 2. Interest @18% p.a. will be charged if payment is not nade within 45 days is 3. Goods once sold will not be taken back. 4. "Subject to 'SURAT" Jurisdiction only, 1. OSE” toe ae Je«</t>
@@ -3688,19 +3564,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>3554</v>
+      </c>
+      <c r="G103" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>16/10/2025</t>
-        </is>
-      </c>
-      <c r="G103" t="n">
-        <v>3554</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -3725,15 +3601,15 @@
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>01-04-25</t>
         </is>
       </c>
-      <c r="G104" t="n">
+      <c r="F104" t="n">
         <v>164591</v>
       </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>wn  SHED STIN :- x Bs e933 zy GAI | ae METAL CORPORATION ge 2 4AAJFG9239012N Date  vVno BkCode 01-04-25 01-04-25 5007 PRCHA1 02-04-25 5019 PRCHAL 04-04-25 5038 PRCHA1 14-04-25 5092 PRCHAL 17-04-25 5108 PRCHAL 13-05-25 5248 PRCHA1 16-05-25 5280 PRCHA1 01-06-2aes AXISBA 14-06-25 5433 PRCHA1 16-06-25 5440 PRCHAL SY \oeoe 5469 PRCHAL 7-25 5566 PRCHA1 07-07-25 5584 PRCHA1 08-07-25 5586 PRCHAL 2 1207-25 Sear PRCHA1 30-07-25 5729 PRCHA1 04-08-25 5761 PRCHA1 14-08-25 5824 PRCHA1 14-08-25 5825 PRCHA1 10-09-25 6006 PRCHA1 15-09-25 6038 PRCHA1 20-09-25 6070 PRCHA1 22-09-25 4 AXISBA 04-10-25—6m69%  PRCHAIL 09-10-25q62000"  PRCHAL +3-11-2 PRCHA1 26-11-25 PRCHA1 23-12-2566ae PRCHAL 25-12-25 6625" PRCHAL 35-12-25 q6@neee PRCHAL * a Z 5, 6649” Eee @ i -26mo685™ | PRCHA 06201-26605" PRCHAL 07-01-26qemmi5m” PRCHAL 09-01-26 46926 PRCHAI 10-01-26m167349 PRCHAL oe PRCHA1 16-01-2 PRCHA1 miei PRCHAL 21-01-2 PRCHA1 22-01-26§ 68080 § PRCHA1 26-01-2686827' PRCHAL 29-01-26 €6839" PRCHA1  11720  uae: “Sn ** From 01-04-2025 to 31-03-2026  164591.00  85294.00  26422.00 CR OO) VOIR | PAB .00 CR PB 48255.00 CR PB 65632.00 CR PB 150741.00 CR PB 152741.00 CR PB 164115.00 CR PB 476.00 DB BP 2607.00 CR PB 10992.00 CR PB 12838.00 CR PB 3539.00 CR PB 24662.00 CR PB 30175. 49854. 56125. 13348.  85099.00 CR PB 100065.00 CR PB 106106.00 CR PB 106649.00 CR PB  91355.00 CR BP  21993.00 CR 2B  23680.00 CR PB  36800.00 CR PB  43370.00 CR PB  61461.00 CR PB  PB  69195.00 CR PB  74337.00 CR PB  98352.00 CR PB 107075.00 CR PB 109093.00 CR PB 121239.00 CR PB 122708.00 CR PB 125281.00 CR PB 126396.00 CR PB 129795.00 CR PB 133659.00 CR PB 136411.00 CR PB 146276.00 CR PB  Loo CR PB</t>
@@ -3748,7 +3624,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CP &amp;.</t>
+          <t>GAUTAM METAL CORPORATION -</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3758,10 +3634,10 @@
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="n">
-        <v>464591</v>
-      </c>
+      <c r="F105" t="n">
+        <v>26417</v>
+      </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>eee” cae: rates CP &amp;. To ee GAUTAM METAL CORPORATION - Fi oe p SHOP NO-7,8 , GAUTAM HOUSE Behe at B/S. DENA BANK,UDHNA MAIN ROAD ee UDHNA,SURAT. $ so E-Mail : gmcmetal@gmail.com ie: oR , GSTIN/UIN: 2AAAJFG9239Q1ZN wee ot State Name: , Code : _ hee s Lee SHED-7933 phere Ledger Account es E 99-30,SAMAYSAR BUNGLOW,NR.NANDINI-3 VIP oe ROAD ,SURAT. M-9429331881 ee 4-Apr-25 to 12-Feb-26 Fi = oe Page 1 Iv ae Date Particulars Vch Type Vch No. Debit Credit § {-Apr-25 To Opening Balance 26,417.00 pig x 4-Apr-25 To SALE GST-1 LECT ARNE 5007 3,360.00 ute 2-Apr-25 To SALE GST-1 SLL 5019 43,517.00 ae S 4-Apr-25 To SALE GST-1 SALE GSTTAXCASHIMNOCE 5038 4,956.00 pS ae 14-Apr-25 To SALE GST-1 HLEGSTIANCASHINORE 5092 17,377.00 FS = 47-Apr-25 To SALE GST-1 SESH 5108 85,109.00 a eo 13-May-25 To SALE GST-1 ALESTIA CHINE 5248 2,000.00 oe 46-May-25 To SALE GST-1 SLE AHO 5280 11,374.00 eee 14-Jun-25 To SALE GST-1 SHE STTACSHIVOLE 5A33 3,083.00 ae 4 Ss 46-Jun-25 To SALE GST-1 SECSHANCASHNNOCE 5440 8,385.00 eo 49-Jun-25 To SALE GST-1 SLEGSTIAXCASHINOGE 5469 4,846.00 E ¥ {-Jul25 By ICICI BANK Receipt 788 4,64,591.00 eee 3-Juk25 To SALE GST-1 SETHE 5566 10,701.00 ree 7-Jul-25 To SALE GST-1 SALEGSTTANCASHIAVOE: 5584 4,123.00 aa = 8-Jul-25 To SALE GST-1 SALE GST TEKCASHINVOLE 5586 551 3.00 = wi 21-JulL25 To SALE GST-1 SLE SIA 5671 49,679.00 2S 30-Jul-25 To SALE GST-1 SALE GSTTAL CASHIN 5729 6,271.00 aoa. 4-Aug-25 To SALE GST-1 SSMU 5761 17,218.00 ea: 14-Aug-25 To SALE GST-1 SLE GSTIAN ASHORE 5824 ‘5 898.00 ee 9 To SALE GST-1 SLCHI CHOC 5825 5 858.00 FS SS) J 10-Sep-25 To SALE GST-1 SLE NOL 6006 14,966.00 EN, 15-Sep-25 To SALE GST-1 SLES 6038 6,041.00 WERE 20-Sep-25 To SALE GST-1 se HN 6070 543.00 a 22-Sep-25 By ICICI BANK Receipt 1309 85,294.00 at 4-Oct25 To SALE GST-1 Ses eer quasst0e" aye 9-Oct-25 To SALE GST-1 SHLEGSTTALCASHIOCE que201i 687.00 Rowe e 13-Nov-25 To SALE GST-1 LECH i663" eas 26-Nov-25 To SALE GST-1 SHE GOTTA ASHOOCE @n4aein anon ends cs ; 23-Dec25 To SALE GST-1 SCH 6641" CRGISTOL00 bee 25-Dec-25 To SALE GST-1 SAEGSTIA ASHI 6625! wene : Bask To SALE GST-1 SLE SALAH 96626)" 03:769.00 as 27-Dec-25 To SALE GST-1 ALE GSTTALCASHIMNOCE aquec4oi . 3-Jan-26 To SALE GST-1 MES OBC HO 66685) or 5 eae 6-Jan-26 To SALE GST-1 SEG HOE penne oe 7-Jan-26 To SALE GST-1 ESTA CAMHIE = i a i 9-Jan-26 To SALE GST-1 SLES A CH ~ 6726" Len tig ae 10-Jan-26 To SALE GST-1 LEGS &gt; goon oan oe 12-Jan-26 To SALE GST-1 SALE GTINLCQHINORE 6734 “1,469.00. , i MeRA2 IY \yunn2eB73,00 ‘ » | i Wee ay) Raat 3,75,161.00 2,49,885.¢0 A Re ws  continued ...</t>
@@ -3786,10 +3662,10 @@
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="n">
+      <c r="F106" t="n">
         <v>397144</v>
       </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>GAUTAM METAL CORPORATION  Page 2 “ SHED-7933 Ledger Account _:_1-Apr-25 to 12-Feb-26 Vch No. Debit Credit Date Particulars Vch Type 3,75,161.00 2,49,885.00 Brought Forward 16-Jan-26 To SALE GST-1 none “6765 «3399.00 17-Jan-26 To SALE GST-1 pce ss 6782" 3864.60 21-Jan-26 To SALE GST-1 ead 8 6808" 2752.00 24-Jan-26 To SALE GST-1 eas 6817" 9,865.00" ‘ T-1 26-Jan-26 To SALE GS MONI equ" "98800 29-Jan-26 To SALE GST-1 3,97,144.00 2,49,885.00 i ce By Closing Balan 3,97,144.00 3,97,144.00  am ae  ee or a a ae bart: ME te ee ist ee Lo es  oO ey</t>
@@ -3802,20 +3678,16 @@
           <t>IMG_20260516_164449.jpg</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>M GST TAX INVO MSICS</t>
-        </is>
-      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>24AAJFG9239Q1ZN</t>
-        </is>
-      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>24AAJFG9239Q1ZN</t>
+        </is>
+      </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>th afl idlaae wadua e ul Original For Recipient Stockists &amp; Suppliers Of.:-  ™ : . » ICE Stainless Steel, Brass, Copper, Aluminium, 9 G&amp;G le| U I re M GST TAX INVO MSICS, Pipe, Sheet, Red, Plate, ve SORBORERG Ni Pipe Fittings &amp; Non-Ferrous Metals EIAL VV ‘3 = cside Bank of Baroda, Main Road, Udhna, SURAT-394 210,  W " Tf . © ona Housel shor 321, 2275164 Emall : gmemetal@gmall.com Visit us : www gautammetal.com  PARTICULARS ~ HSN CODE| QUANTITY  i  Wns OF  Se aA aN,  GSTNO: 24AAJFG9239Q1ZN  Declaration  (1) Interest @ 24% Will Be Charged On Payment Remain Unpaid After Due Date (2) Goods Once Sold Will No Be Taken Back (3) We Are Not Responsible For The Breakage Or Shortage |  Company’s PAN : AAJFG9239Q DAYS  PAYMENT DUE ON Material Receiver Sign.  For, Gautam Metal Corporation  Cpe. Authorised Signatory  A/c. No. : 183605501681 «Branch : KATARGAM IFC Code: ICIG0001836</t>
@@ -3828,11 +3700,7 @@
           <t>IMG_20260516_164507.jpg</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>INVOICE</t>
-        </is>
-      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
@@ -3850,11 +3718,7 @@
           <t>IMG_20260516_164535.jpg</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>VOICE</t>
-        </is>
-      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
@@ -3872,20 +3736,16 @@
           <t>IMG_20260516_164545.jpg</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>M GST TAX INVOIC MS</t>
-        </is>
-      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>24AAJFG9239Q1ZN</t>
-        </is>
-      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>24AAJFG9239Q1ZN</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>aa AH tl Original For Recipient Stockists &amp; Suppliers OF.:-  YY E ‘Stainless Steel, Brass, Copper, Aluminium, (5 |! a | M GST TAX INVOIC MS/CS, Pipe, Sheet, Rod, Plate, Pipe Fittings &amp; Non-Ferrous Metals  11 a eiveaz wed  METAL CORPORATION roda, Main Road, Udhna, SURAT-394 210, -8, Beside Bani. oF lemetal@gmall.com Visit us : www gautammetal.com  " Gautam House " Shop No. 7 © 98243 75434 Ph.: +91 261-2279321, 2275164  TRANSPORT: (yf, J - 5 - ol Sms  CONTACTNo.: G YOU? BIP FG  RATE PER| AMOUNT  | ee Lime  pp C27 [rerowrces| ico - im GSTNO: 24AAJFG9239Q1ZN core | sottie  /p bis A 4  : 24AAJ Declaration kaoftw ; SGST @ 9% Cael!  (1) Interest @ 24% Will Be Charged On Payment Remain Unpaid : After Due Date (2) Goods Once Sold Will No Be Taken Back (3) We ioe iii h | Are Not R . Or Short e Not Responsible For The Breakage Or Shortage ROUNDOFFWH)| | EY Company's PAN S—_Jorano toma | agente | pany's PAN : AAJFG9239Q (0. NS GRAND TOTAL | (60) 7 For, Gautam Metal Corporation  Material Receiver Sign. Bank Name : ICICI BANK A.lc. No. ; 183605501681 Branch : KATARGAM IFC Code _ : ICIC0001836  aS  Authorised Signatory</t>
@@ -3898,20 +3758,16 @@
           <t>IMG_20260516_164600.jpg</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>M GST TAX INVOICE MS</t>
-        </is>
-      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>24AAJFG9239Q1ZN</t>
-        </is>
-      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>24AAJFG9239Q1ZN</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>i afk aivaag wedereie ti Il Original For Recipient Stockists &amp; Suppliers Of.:-  T™ ‘Stainless Steel, Brass, Copper, Aluminium, | Gb 4 U T i M GST TAX INVOICE MS/CS, Pipe, Sheet, Rod, Plate, m =| ON Pipe Fittings &amp; Non-Ferrous Metals METAL CORPORATION |  a " Gautam House " Shop No. 7-8, Bescon @ 98243 75434 Ph.: +91 261-2279321, 2275  , Main Road, Udhna, SURAT-394 210, AK ; BRaMeaicomall.com Visit us : www gautammetal.com  TRANSPORT : CONTACT No.: 221E2-7 ee fren] ancuwr—| “ars  | P.&amp;.F.CHARGES RUPEES  eas) ted  GSTNO: 24AAJFG9239Q1ZN nek  a paren | sxe)" (1) Interest @ 24% Will Be Charged On Payment Remain Unpaid ; After Due Date (2) Goods Once Sold Will No Be Taken Back (3) We cot I iit Are Not Responsible For The Breakage Or Shortage  Company's PAN : AAJFG9239Q GRAND TOTAL oh perey pe: |  i&gt; &amp;Cacan! | PAYMENT DUE ON DAYS | Material Receiver Sign.  Eka  Bank Name : ICICIBANK For, Gautam Metal Corporation  A.lc. No. : 183605501681 Branch : KATARGAM | IFC Code _ : ICIC0001836  Authori ignatory</t>
@@ -3924,11 +3780,7 @@
           <t>IMG_20260516_164625.jpg</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>LUT FAM GST TAX INVOICE MSICS</t>
-        </is>
-      </c>
+      <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
@@ -3946,11 +3798,7 @@
           <t>IMG_20260516_164731.jpg</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>M GST TAX INVOICE MS</t>
-        </is>
-      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
@@ -3968,11 +3816,7 @@
           <t>IMG_20260516_164745.jpg</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>A M GST TAX INVOICE MS</t>
-        </is>
-      </c>
+      <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
@@ -3990,20 +3834,16 @@
           <t>IMG_20260516_164834.jpg</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>M GST TAXINVOICE</t>
-        </is>
-      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>24AAJFG9239Q1ZN</t>
-        </is>
-      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>24AAJFG9239Q1ZN</t>
+        </is>
+      </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>ee  11 aft eiaaz wataete ET Original For Recipient Stockists &amp; Suppliers Of.:-  c= Ks ‘Stainless Steel, Brass, Copper, Al tainless steel, Brass, Copper, Aluminium, m. bAU j iM GST TAXINVOICE = —Wisic, Pipe, Sheet, Red, Plate, Nal -— Pipe Fittings &amp; Non-Ferrous Metals  METAL CORPORATION _ k of Bar " Gautam House " Shop No. 7-8, Beside Banc ter  @ 98243 75434 Ph.: +91 261-2279321, 2275164  RUPEES  =!  i  GSTNO: 24AAJFG9239Q1ZN  Declaration (1) Interest @ 24% Will Be Charged On Payment Remain Unpaid After Due Date (2) Goods Once Sold Will No Be Taken Back (3) We ||GST @ 18 %  Are Not Responsible For The Breakage Or Shortage ROUND OFF(+/-) Bae aul  [TARR Company's PAN : AAJFG9239Q Sere 7 For, Gautam Metal Corpo  ration  Material Receiver Sign. Bank Name : ICICI BANK vf @ (pure Ly Authoris ignatory Ze  A.lc. No. : 183605501681 Branch : TARGAM IFC Code — : IC|C0001836</t>
@@ -4016,20 +3856,16 @@
           <t>IMG_20260516_164843.jpg</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>TRANSPORT</t>
-        </is>
-      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>24AAJFG9239Q1ZN</t>
-        </is>
-      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>24AAJFG9239Q1ZN</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>sap . &lt; pRex oY rego The BEE Oars pe eh seal Sie” S ate  et ‘  4 { a a  ot GFy  a ar  ee ne 2 NAA, ee HAS on ge  Seen. I  5  . Hal U1 afl aieae waded tH Original For Recipient  Stockists &amp; Suppliers Of.:- ‘Stainless Steel, Brass, Copper, Aluminium, mG i | A M- SIM = MS/CS, Pipe, Sheet, Rad, Pate, Pipe Fittings &amp; Non-Ferrous Metals  ; &gt; shame Tad k of Baroda, Main Road, Udhna, SURAT-394 210, © = auton Ouse roe, doen gmcmetal@gmail.com Visit us : WWW gautammetal.com  [nwocens: (mp6B5 | DATE : og. es  TRANSPORT :  a a ee CONTACT No.: OY 29 59 [X7  ee ee pe TE Lee pel Sie  Se pk A oe a  N  S  RUPEES  | GSTNO: 24AAJFG9239Q1ZN  Declaration | (1) Interest @ 24% Will Be Charged On Payment Remain Unpaid  After Due Date (2) Goods Once Sold Will No Be Taken Back (3) We Are Not Responsible For The Breakage Or Shg  P.&amp;.F.CHARGES  “i,  romp cl =o prem | Ral ade pesrem | 59) 21 Sia cs a  4.  GRAND Tota | Ys  0 lV,  Company’s PAN : AAJFG9239Q PAYMENT DUE ON DAYS  For, Gauta fetal Cor  Bank Name : ICICI BANK  AJjc.No. — : 183605501681  Branch : KATARGAM  IFC Code _ : ICIC0001836 Authorise Bry ot</t>
@@ -4042,11 +3878,7 @@
           <t>IMG_20260516_164855.jpg</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>BPR G T</t>
-        </is>
-      </c>
+      <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
@@ -4064,11 +3896,7 @@
           <t>IMG_20260516_164906.jpg</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>GST TAX INVOICE</t>
-        </is>
-      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
@@ -4088,7 +3916,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GST TAX INVOICE</t>
+          <t>GST TAX</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -4108,11 +3936,7 @@
           <t>IMG_20260516_164947.jpg</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>G U T M GST TAX INVOICE MSICS</t>
-        </is>
-      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
@@ -4130,11 +3954,7 @@
           <t>IMG_20260516_165004.jpg</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>GST TAXINVOICE</t>
-        </is>
-      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
@@ -4152,11 +3972,7 @@
           <t>IMG_20260516_165012.jpg</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>J J LI</t>
-        </is>
-      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
@@ -4176,7 +3992,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TRANSPORT</t>
+          <t>MS/CS,</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -4196,11 +4012,7 @@
           <t>IMG_20260516_165032.jpg</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>GST TAX INVOICE  TRANSPORT</t>
-        </is>
-      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
@@ -4218,20 +4030,16 @@
           <t>IMG_20260516_165039.jpg</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>GST TAX INVOICE MS</t>
-        </is>
-      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>24AAJFG9239Q1ZN</t>
-        </is>
-      </c>
+      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>24AAJFG9239Q1ZN</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr">
         <is>
           <t>: SOE TaN oe SEG: af yal!  - AVA &gt; on Sy ietice  meee 2 ba) ey es ened sie ee  Wa siege wsdeuea 44: Il  Original For Recipient er Fil | T | ™ Stockists &amp; Suppliers Of.:- M Stainless Steel, Brass, Copper, Aluminium, - GST TAX INVOICE MS/CS, Pipe, Sheet, Rod, Plate, Q Pipe Fittings &amp; Non-Ferrous Metals  “ Gautam House " Sho No 78 Beside Bank of Baroda, Main Road, Udhna, SURAT-394 210, 98243 75434 Ph.: +94 2612279321, 2275164 Email : gmcmetal@gmail.com Visit us : www gautammetal.com  a P.&amp;.F.CHARGES  GSTNO: 24AAJFG9239Q1ZN cest@ om |  CGST @ 9% Declaration p7. Paher— ie Ge SS: (or) 4 2€ 64 (1) Interest @ 24% Will Be Charged On Payment Remain Unpaid  After Due Date (2) Goods Once Sold Will No Be Taken Back (3) We |IGST @ 18 % Are Not Responsible For The Breakage Or Shortage  RUPEES  Bank Name : ICICI BANK  A/c. No. : 183605501681 Branch : KATARGAM j IFC Code =: ICIC0001836 Authorised Signatory</t>
@@ -4244,20 +4052,16 @@
           <t>IMG_20260516_165047.jpg</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>RR EEE</t>
-        </is>
-      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>24AAJFG9239Q1ZN</t>
-        </is>
-      </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>24AAJFG9239Q1ZN</t>
+        </is>
+      </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>a)  MOMS Ne RD  , 7 i RR EEE eae a ‘er RL Oa U Rett Original For Ree picnt 4] GA ITA} f i — Stockitts &amp; Supplies Of ‘Stainless Steel, Bross, Copper, Aluminium, METAL Bieteroine li GST TAX INVOICE MS/CS, Pipe, Sheet, Rod, Plate,  pin. CORPORATION" Pipe Fittings &amp; Non-Ferrous Metals  © gezgutam House ™ Shop No. 7-8, Beside Bank of Baroda, Maln Road, Udhna, SURAT-394 210, 3434 Ph. 494 261-2279321, 2275164 Email : gmcmotal@gmall.com Visit us : www gautammotal.com  INVOICE No.:  BT ei AUMAD hey cre  CONTACTING: LUr20°7 2979763 Ea eo lagu. cheer uxexann erslgnio| sot | erso!  | GSTNO: 24AAJFG9239Q1ZN 2  Declaration PYT— A/kufhsy, GJ-OS. TT UST: (1) Interest @ 24% Will Be Charged On Payment Remain Unpaid After Due Date (2) Goods Once Sold Will No Be Taken Back (3) We |IGST @ 18 %  Are Not Responsible For The Breakage Or Shortage Company's PAN : AAJFG92390 JaRano tora (wigs igs}  PAYMENT DUE ON DAYS Metal Corporation Bank Namo : ICICI BANK For, Gautam p  Alc, No + 163605501681 dh, Branc : KATARGAM ¢ Dae IFC Code: 1CiC 0001836 Autho alory</t>
@@ -4270,11 +4074,7 @@
           <t>IMG_20260516_165054.jpg</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>PAYMENT DUE ON DAYS</t>
-        </is>
-      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
@@ -4292,11 +4092,7 @@
           <t>IMG_20260516_165133.jpg</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Q UE ON  PAYMENT D</t>
-        </is>
-      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
@@ -4314,11 +4110,7 @@
           <t>IMG_20260516_165150.jpg</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>A U A M GST TAXINVOICE</t>
-        </is>
-      </c>
+      <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
@@ -4336,11 +4128,7 @@
           <t>IMG_20260516_165202.jpg</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>RUPEES  GSTNO</t>
-        </is>
-      </c>
+      <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
@@ -4364,14 +4152,14 @@
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>24AAJFG9239Q1ZN</t>
-        </is>
-      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>24AAJFG9239Q1ZN</t>
+        </is>
+      </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>1 af sear adam tH: Il  y GAUTAM ‘ GST TAX INVOICE Lp  "METAL CORPORATION : Gautam House «Shap No.7 8 Setds Seiko igunal cn vv ww satan 1,22 4 © 98243 75434 Ph: +91 261-2279321,  INVOICE No.:  Original For Recipient Stockists &amp; Suppliers Of.:-  Stainless Steel, Brass, Copper, Aluminium, MS/CS, Pipe, Sheet, Rod, Plate, Pipe Fittings &amp; Non-Ferrous Metals  EI PARTICULARS HSN CODE QUANTITY RATE ) pect Sau Kee Wome. | goeree| rot | 1992e9- | 3 i  RUPEES  GSTNO:24AAJFG9239Q1ZN —|ccst@% |  Declaration SGST @ 9%  (1) Interest @ 24% Will Be Charged On Payment Remain Unpaid  After Due Date (2) Goods Once Sold Will No Be Taken Back (3) We  Are Not Responsible For The Breakage Or Shortage Company's PAN : AAJFG9239Q |  PAYMENT DUE ON DAYS  Iss  mee aN dal  ww  7)  V\ mk  Wie  Materlal Receiver Sign. Bank Name : ICICI BANK For, Gautam Metal Corporation Alc.No. — : 183605501681 by ef Branch =: KATARGAM Ch+€: IFC Code  : 1C1C0001836  Authorised Signatory  Tee Gere wae er  ace  Be vhied</t>
@@ -4384,18 +4172,14 @@
           <t>IMG_20260516_165223.jpg</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>AM GST TAX INVOICE MS</t>
-        </is>
-      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>5108</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
@@ -4410,11 +4194,7 @@
           <t>IMG_20260516_165232.jpg</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>METAL CORPORA</t>
-        </is>
-      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
@@ -4432,11 +4212,7 @@
           <t>IMG_20260516_165242.jpg</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>M GST TAX INVO MS</t>
-        </is>
-      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
@@ -4454,11 +4230,7 @@
           <t>IMG_20260516_165304.jpg</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>IM GST TAX INVE MS</t>
-        </is>
-      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
@@ -4476,11 +4248,7 @@
           <t>IMG_20260516_165329.jpg</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>G AUTAM</t>
-        </is>
-      </c>
+      <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
@@ -4500,18 +4268,18 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PROMEGA RE NSE</t>
+          <t>PROMEGA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>24AAJFG9239Q1ZN</t>
-        </is>
-      </c>
+      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>24AAJFG9239Q1ZN</t>
+        </is>
+      </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>&gt; aie Re Nak Panene  y aS is thet eRe ae, ; PROMEGA RE NSE oe OS Raa LI ate APO Se . af edeae stu WH: Il Original For Recipient ™ Stockists &amp; Suppliers Of.:- é VOICE Stainless Steel, Brass, Copper, Aluminium, fa (5 [4 | | A M GST. TAX IN MS/CS, Pipe, Sheet, Rod, Plate, sg Pipe Fittings &amp; Non-Ferrous Metals  PORATION y METAL COR of Baroda, Main Road, Udhna, SURAT-394 210,  Ceram House Shop No To e104, ah gincmetal@gmall.com Visit us : www gautammetal.com  — on aa oo CeCe  pi ths mS Cm Ao ee  | | | re SS \ v 2 r » G 2 O iS S|  ae  a a GSTNO: 24AAJFG9239Q1ZN Jecst@ ox [|  /Yorlxe q SGST @ 9%  Declaration  Ps rr ‘7 ; * ED, Met ' 2 &lt;8! eye be Ps “4 . 2 4  (1) Interest @ 24% Will Be Charged On Payment Re nain Unpaid aa After Due Date (2) Goods Once Sold Will No Be Taken Back (3) We |IGST @ 18 % Ss Are Not Responsible For The Breakage Or Shortage | Sa ROUND OFF(+/-) US &lt;i  ’ rf : BE Company's PAN : AAJFG9239Q 1 Guod GRAND TOTAL y SUS &amp; [PAYMENT BUEN bAYSSdYS 7 i Material Receiver Sign. Bank Name : ICIGi BANK For, Gautam Metal Corporation | ES AJjc.No. — : 183605501681 f  Branch —_; KATARGAM : :  IFC Code _: ICIC0001836 Authorised Signatory x  oa 3 s  2 Py Agree, 0 we f \ Me Rabie) S  eR</t>
@@ -4524,18 +4292,14 @@
           <t>IMG_20260516_165413.jpg</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>IM GST TAX INVO</t>
-        </is>
-      </c>
+      <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
@@ -4550,11 +4314,7 @@
           <t>IMG_20260516_165424.jpg</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>U IM GST TAXINVOICE</t>
-        </is>
-      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
@@ -4572,11 +4332,7 @@
           <t>IMG_20260516_165435.jpg</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>GAUTAM</t>
-        </is>
-      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
@@ -4596,7 +4352,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>GST TAX INVOICE</t>
+          <t>GST TAX</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -4616,11 +4372,7 @@
           <t>IMG_20260516_165501.jpg</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>GST TAX INVOICE</t>
-        </is>
-      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
@@ -4638,20 +4390,16 @@
           <t>IMG_20260516_165529.jpg</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>REECE</t>
-        </is>
-      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>24AAJFG9239Q1ZN</t>
-        </is>
-      </c>
+      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>24AAJFG9239Q1ZN</t>
+        </is>
+      </c>
       <c r="H143" t="inlineStr">
         <is>
           <t>. f NES “ W: REECE aR gs Non vEs Wa siege wardens tH Il a ve Original For Recipient  ™ G “1 LI T i M Stockists &amp; Suppliers OF.:- = INVOICE Stainless Steel, Brass, Copper, Aluminium, SF Ll EE ee coy TAX MS/CS, Pipe, Sheet, Rod, Plate, . a METAL CORPORATION Pipe Fittings &amp; Non-Ferrous Metals " Gautam House " Shop No. 7-8, Beside Bank of Baroda, Main Road, Udhna, SURAT-394 210, @ 98243 75434 Ph.: +91 261-2279321, 2275164 Email : gmcmetal@gmail.com Visit us : www gautammetal.com  C4 = Sr  a EPARARMEMAAAMC  RUPEES  GSTNO: 24AAJFG9239Q1ZN _  Declaration Le SGST @ 9% (1) Interest @ 24% Will Be Charged On Payment Remain Unpaid  After Due Date (2) Goods Once Sold Will No Be Taken Back (3) We oo. Ol iii Are Not Responsible For The Breakage Or Shortage Company's PAN : AAJFG9239Q ; ] |eranv toTaL | 1GObK io"  PAYMENT DUE ON DAYS Material Receiver Sign. Bank Name : ICICI BANK For, Gautam Metal Corporation  Ajc.No. — : 183605501681 Branch : KATARGAM (WE IFC Code _ : ICIC0001836 . Author ignatory</t>
@@ -4666,7 +4414,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>FE  GRUTAM  NETAL CORPORATION</t>
+          <t>GRUTAM NETAL CORPORATION</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -4688,7 +4436,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>GST TAX INVOICE</t>
+          <t>GST TAX</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -4708,20 +4456,16 @@
           <t>IMG_20260516_165615_1.jpg</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>WEA DB</t>
-        </is>
-      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>24AAJFG9239Q1ZN</t>
-        </is>
-      </c>
+      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>24AAJFG9239Q1ZN</t>
+        </is>
+      </c>
       <c r="H146" t="inlineStr">
         <is>
           <t>‘ -  WA a2 WEA DB reyey faye . Original For Recipient  T™ T A M {" | Stockists &amp; Suppliers OF.:- | GST TAX INVOICE Stainless Steel, Brass, Copper, Aluminium 4 vine MS/CS, Pipe, Sheet, Rod, Plate, Pipe Fittings &amp; Non-Ferrous Metals  «Gautam House “ Shop No. 7-8, Beside Bank of Baroda, Main Road, Udhna, SURAT-394 210 9 98243 75434_Ph.: +91 261-2279321, 2275164 Email : gmcmetal@gmail.com Visit us : www gautammetal.com  4  Bee l ee ome DolW2S Lees = aa  = com: PY | Are ELIS VIET comncrnnspha I P| [| AIF Th f CONTACT No.: fh E S[vnmwne [ons sue [oe O Mena. Jan | ha Bar 8 6 6S SS eS eee | ie é D las 1 TAS a | 4 ra We lw | ea  —_  RUPEES  GSTNO: 24AAJFG9239Q1ZN |  Declaration (1) Interest @ 24% Will Be Charged On Payment Re iain Unpaid  After Due Date (2) Goods Once Sold Will No Be Takef Back (3) We Are Not Responsible For The Breakage Or Shortage  esrem | J] rosr@e |g) Sel Ee Boro) _ Sen  For, Gautam M orporation  Avithotised “nel  Company’s PAN : AAJFG9239Q  PAYMENT DUE ON DAYS Material Receiver Sign.  A.lc. No. Branch IFC Code</t>
@@ -4734,20 +4478,16 @@
           <t>IMG_20260516_165645.jpg</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>OSE ES</t>
-        </is>
-      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>24AQYPR3586Q1ZH</t>
-        </is>
-      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>24AQYPR3586Q1ZH</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr">
         <is>
           <t>rs) TE so -s,. a&gt; °, 2 ty oe - Boul fw ae « ip oF. pe OSE ES oe ages EE et pee Se a ee Sip SUP poe k Bia) ate  TAX INVOICE (GFIGINAI, FOR, FEGIRIEND) . 5 ey RIN MOISe  | , % Wat wanes aE Ut Lat aerratt 71: UL! V stasttraett TA: U Original For Recipient  q Mo. 99981 57057 DELIVERY CHALLAN 99740 48199  SHREE,CHANDRASLa meta CORPORATION  : ini S, Pipe, Sheet, --Stainles§ Steel, Brass, Copper, Aluminium, MSI/CS, , SC 7 Rod, Nets SP cania Ferrous|&amp; Non-Ferrous Metals, All Industrial Raw Materials  U  hla Bus Depot, Main Road, Udhna, Surat - 394 210 Noo Fe gmail.com Website : www.shreechandrajimetal.in  G-1/2, Manikan Complex,  M. 98256 57057 Ph. : + 91-261-  2270027,E-mail : : shreechandrajimetal@  TRANSPORT :  CONTACT No. eee ae QUANTITY | RATE  } a  be Tora ra |  RUPEES  GSTIN : 24AQYPR3586Q1ZH  (1) Please let us have your approval report within 5 days. I (2) Our risk and responsibility ceases on delivery of the goods from our premises. (3) Goods once sold will not be taken back.  u  Please return duplicate duly signed es Company's PAN : AQYPR3586Q Bea | PAYMENT. DUE ON | es | Bank Name : HDF Bank For, Shree Chandraji Metal Corporation Be Ajc.No. : 50200028513464 | Branch : Udhyog Nagar, Udhna | IFC Code : HDFC0003048 ‘as P DAS  I) oh  . SS ie pe ETO ME RITE Sa ;</t>
@@ -4760,18 +4500,18 @@
           <t>IMG_20260516_165715.jpg</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>NG SOY</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr"/>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>rences</t>
+        </is>
+      </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="n">
+      <c r="F148" t="n">
         <v>2936</v>
       </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>A i ot . te ti - Beha Wangs ,4 oa a Sn! “3 Se aoe Lice Pea NG SOY Pee RT —_  piled aan” ey a et 6 deb’. dads “Ss se A PSST SX ?  Te  TAX INVOICE (ORIGINAL FOR RECIPIENT) e-Invoice —= Dh caar eta x See esi Reagieaat ty IRN  eSb2cbe463e2726121be34322007¢5206a3144Gg?- ie er a1ff29cf696ae4c363c72e : Ack No. — : 162523053127571 Ack Date : 26-Dec-25 if i Dated Invo No. SHREE CHANDRAJI METAL CORPORATION -* a Me 26-Dec-25 G-1/2,Manikan Complex, Below Union Bank, eee 2eKale ieeerrarme of Payment Nr.Udhna Bus Depot,Main Road, Hdfc Online Udhna Surat. Le ANE Bas : UDYAM : UDYAM-GJ-22-0023965 (Micro) -Rifference No. &amp; Date. ilemizctorences GSTIN/UIN: 24AQYPR3586Q 12H 2663 dt. 26-Dec-25 ha 'Bilyer's Order No. Dated  Gujarat, Code : 24  State Name: 70027, +91-999815  Contact : 0261-22 7057/ 9974048199  ‘Delivery Note Date  E-Mail : shreechandrajimetal@gmail.com ‘Dispatch Doc No. www.shreechandrajimetal.in_ 2) USDA RRR UEC uve Seon nk De ee ee ami Des uyer (BI Dispatched through Destination SHE W, NR NANDINI By Hand Surat 29-30, SAMAYSAAR BUNGLOW, ) ey ea an $3 VIP ROAD, SURAT, Surat, Gujarat, 395007 ‘Terms of Delivery GSTIN/UIN - DAAAAHY7933G1ZY | State Name - Gujarat, Code : 24 Place of Supply : Gujarat Contact - 9558038546 | Sl Description of Goods “HSNISAC | Quantity | Rate | per | Disc. % Amount No. By | Jai | ai | + BRASS ROD BARS ( 74072120 ) 74072120 3.150kg) 790.00 kg 2,488.50 10x 10mm | CGST | | ! 222.97 SGST | 223.97 Less : ROUND OFF | | (-)0.44 =k | @ | | | | | eapey Bis “Tan Total ) 3.150 kg Gk Nak. &amp; 2,936.00 Amount Chargeable (in words) Ta: a MPO. &amp; O.£ INR Two Thousand Nine Hundred Thirty Six Only EGNISAC WC Taxable Wb, meGS Wt ju SGST/UTGST | Total Value Rate | Amount Rate Amount Tax Amount 74072120 2.488790 | 1) 9% | 223.97 [Wwo% 223.97 447.94 Ria Re He rotary 2:488.9R) ah mmua223197 |p 223.97 447.94 | Tax Amount (in words) : INR Four Hundred Forty Seven and Ninety Four paise Only Company's PAN : AQYPR3586Q Declaration Com } i Deciara OF CMO pany's Bank Details We declare that this invoice shows the actual price of the Bank Name : HDFC BANK-OD goods described and that all particulars are true and correct. A/c No. : 50200028513464 ‘Sranch &amp; IFS Code: Customer's Seal and Signature | for SHRESCHANGRAII UOHNA* HURCOUOSS RAJI METAL CORPORATION | Prepared b Verified by anak  SUBJECT TO SURAT JURISDICTION This is a Computeil Generated Invoice  }</t>
@@ -4784,11 +4524,7 @@
           <t>IMG_20260516_165736.jpg</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>SI INC</t>
-        </is>
-      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
@@ -4806,20 +4542,20 @@
           <t>IMG_20260516_165754.jpg</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>DELIVERY CHALLA</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>24AQYPR3586Q1ZH</t>
-        </is>
-      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ry RUPEES</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>24AQYPR3586Q1ZH</t>
+        </is>
+      </c>
       <c r="H150" t="inlineStr">
         <is>
           <t>A POs eat 2  5 ales se mo ee ab aasoee ge)  Vat Peng a: 1 ita =i 1 tect TH =U Original For Recipient werent N Mo. 99981 57057 DELIVERY CHALLA 99740 48199  S  SHREE CHANDRAJL 9 meTAL CORPORATION Brass, Copper, Aluminium, MSICS, Pipe, Sheet,  .:-Stainless Steel, Re Ne Rate Ferrous &amp; Non-Ferrous Metals, All Industrial Raw Materials G-1/2, Manikan Complex, Nr. Udhna Bus Depot, Main Road, Udhna, Surat - 394 210 } handrajimetal@gmall.com Website : www.shreechandrajimetal.in  M, 98258 57057 Ph. : + 91-261- 2270027 E-mail : shreec cHaianno: IOYY) Do25 /2¢4  TRANSPORT  em: [STA TAH 197 S131 3A0 2 bf conmorned [TT TTT TTT FED wsnnewans ——‘wahcone] auawrmmy[ ware |ren{ awounr |  UU SGU ay, Ute Z| Muniniun Pyaté UFO 13? 4 B3SKBYSKI2. Fr i 2, Bya SS GeavLxe GELS IBS OR ZS BXF  TOTAL {Yas Bo Ma, 5-O  scree TT  a  ROUND OFF(+/-  aranororan | 12974 [=  For, Shree Chandraji Metal Corporation  Authorised Signatory  RUPEES  GSTIN : 24AQYPR3586Q1ZH  (1) Please let us have your approval report within 5 days. (2) Our risk and responsibility ceases on delivery of the goods from our premises.  (3) Goods once sold will not be taken back. Subject to SURAT Jurisdiction  Please return duplicate duly signed Company’s PAN : AQYPR3586Q PAYMENT DUE ON Receiver's Signature  Bank Name : HDFC Bank A.lc. No. : 0200028513464 Branch : Udhyog Nagar, Udhna IFC Code :HDFC0003948</t>
@@ -4832,11 +4568,7 @@
           <t>IMG_20260516_165801.jpg</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>TAX INVOICE</t>
-        </is>
-      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
           <t>SHED</t>
@@ -4844,10 +4576,10 @@
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="n">
+      <c r="F151" t="n">
         <v>14257.25</v>
       </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
           <t>NN  8  TAX INVOICE (ORIGINAL FO IRN - edfd3da5fa84fcfc76b67013b9fcecd1fa1a257dec07- 207713d47ae264c871 35  Ack No. &gt; 162521327086782 Ack Date : 15-Jul-25  Invoice No.  CORPORATION " 1044-2025-26  w Union Bank,  SHREE CHANDRAJI META  G-1/2,Manikan Complex,Belo  Nr.Udhna Bus Depot,Main Road, Delivery Note  Udhna Surat.  UDYAM : UDYAM-GJ-22-002396 (Micro)  GSTIN/UIN: &gt;AAQYPRS586Q1 - —_— oe Pat  State Namen ulaieauoonS : SeEeaT BEY: Reference No. &amp; Date. ante 4044 dt. 15-Jul-25  Contact : 0261 -2270027,+91-  E-Mail : G2 echandraljimetal@esmMall-co  Buypr's ‘Order No.  R RECIPIENT)  (15-Jul-25  | Mode/Terms of Payment Immidate _  Other References  _|_——  ‘Dated  www_shreechandraimetel (0 _ sa ® Consignee (Ship to) OF ae SHED ‘Dispatch DocNo.. | Delivery Note Date 29-30, SAMAYSAAR BUNGLOW, NR NANDINI, | 3 VIP ROAD, SURAT, Surat, Gujarat, 395007 za aes) GSTIN/UIN_; 24AAAHY7933G12Y ep atch eee pea State Name - Gujarat, Code : 24 By Hand _ |Surat Contact : 9558038546 if Terms of Delivery Buyer (Bill to) | SHED | 29-30, SAMAYSAAR BUNGLOW, NR NANDINI, | 3 VIP ROAD, SURAT, Surat, Gujarat, 395007 | GSTIN/UIN - 2QAAAAHY7933G61ZY | State Name : Gujarat, Code : 24 ne aL Place of Supply : Gujarat Nae Contact : 9558038546 i AALS? SI Description of Goods THSN/SAC* Quantity | Rate! | per | Disc. % Amount No | hi ; ‘ | | \! ___| a ! 4 Brass Sheet ( 74092900 ) 74092900, 14.800 kg | 750.00| kg) 11,100.00 14"x 48"x 4mm ii | ARM | 2 ALUMINIUM PLATE/SHEET-76061200 76061200) 4:190 kg, 470.00. kg 1,927.00 335 x 345 x 12.7mm ni} ; fh 3 BRASS ROD BARS ( 74072120 ) 74072120 | 1.850 kg 665.00! kg| 4,230.25 8x 8mm | | ne | VamNu4a257-25 CGST 1,283.15 SGST | 1,283.15 S ROUND OFF (u 0.45 w i, | | Z Total '20.750 kg Rea ) — Amount Chargeable (in words) ' ! SL IS 25-09 INR Sixteen Thousand Eight Hundred Twenty Four Only HSN/SAC | ieee tL = PCS | SGST/UTGST | Total : ue | Rate mount Rate | Amount TaxA 74092900 j T | \Tax Amount 56061200 11,100.00 | 9% 999.00 9% | 999.00 1,998.00 7407212 1,927.00, | 9% 173.43) 9% 173.43 | 346 74072120 4230.25 6 | .86 : Total 14,257.25 Level Morey oe 110.72, 221.44 ee RB - otal (/\ 14,257:25|M)\) || 11,283.18 (4,283.15 2,566.30. &lt; Amount (in words) : INR Two Thousand Five Hundred Si i i i ho anne IRAN Be Wenssa6a Sixty Six and Thirty paise Only Declarati ration Company's Bank Details  We declare that this invoice shows the actual price of the Bank Name  : HDFC BANK-OD : 50200028513464  Customer's Seal and Signature  Prepared b SUBJECT TO SURAT JURISDICTION  This is a Computer Generated Invoice  Verified by  goods described and that all particulars are true and correct. A/c No. Branch &amp; IFS Code: UDHYOGNAGAR UDHNA &amp; HDFC0003948  for SHREE CHANDRAJI METAL CORPORATION  ae }</t>
@@ -4860,11 +4592,7 @@
           <t>IMG_20260516_165819.jpg</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>TAX INVOICE</t>
-        </is>
-      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
           <t>SHED</t>
@@ -4872,10 +4600,10 @@
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="n">
-        <v>5360</v>
-      </c>
+      <c r="F152" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
           <t>TAX INVOICE  (ORIGINAL FOR RECIPIENT)  IRN &gt; 9db3c166824448cf8cc5c0809ac1 bb071755c9a0da-  136947530fc36dd8481d59  Ack No. Ack Date  &gt; 162520921966179 &gt; 5Jun-25  Invoice No.  SHREE CHANDRAJI METAL  CORPORATION  G-1/2,Manikan Complex,Below Union Bank, Nr.Udhna Bus Depot,Main Road, Udhna Surat.  637-2025-  ‘Delivery Note  Reference No. &amp; Date.  26 | 5-Jun-25  Mode/terms of Payment  WING CUR tae OBIS Other References  GSTIN/UIN: 24AQYPR  3586Q1ZH  State Name : Gujarat, Code : 24 Contact : 0261-2270027,+91-9998157057/ 9974048199  E-Mail : shreechandrajimetal@gmail.com www.shreechandrajimetal.in  Buyer (Bill to)  SHED  29-30, SAMAYSAAR BUNGLOW, NR NANDINI, 3 VIP ROAD, SURAT, Surat, Gujarat, 395007 GSTIN/UIN - DAAAAHY7933G1ZY  State Name - Gujarat, Code : 24  Place of Supply : Gujarat  Contact : 9558038546  637 dt. S-Jun-25 0 “Buyer's Order No. Dated  -/Dispatch Doc No. | Delivery Note Date 637  Dispatched through By Hand  Terms of Delivery  | Destination | Surat  | Rate | per |Disc. % Amount  Sl Description of Goods No.  HSN/SAC | Quantity  |  4 ALU- FLAT BAR 175x 6mm  2 ALUMINIUM TUBE - 76082000 60 x 50 mm,  CGST SGST ROUND OFF  76042930  76082000 |  3.300 kg  9.100 kg 365.00! kg 3,321.50  370.00) kg. 4,221.00  4,542.50  408.83 408.83 (-)0.16  Total  12.400 kg  = 5,360.00  Amount Chargeable (in words)  INR Five Thousand Three Hundred Sixty Only  E.&amp; O.E  T  HSN/SAC  Taxable | Central Tax  State Tax | Total  Value | Rate Amount  Rate | Amount | Tax Amount  | "76042930 76082000 |  3,321.50) 9% 298.94 1,221.00| 9% 109.89  9% | 298.94| 597.88  9% | 109.89 219.78  Total |  4,542.50 408.83  i  Tax Amount (in words) : INR Eight Hundred Seventeen and Sixty Six paise Only  Company's PAN Declaration  : AQYPR3586Q  Company's Bank Details  408.83, 817.66.  ’ 1  wy? ¢ i. "  We declare that this invoice shows the actual pri i price of the Bank Name 3 goods described and that all particulars are true and correct. Alc No. : MeN a64 Customer's Seal and Signature Ta Ses NCES SOAS MION or HANDRAJI METAL COR  SUBJECT TO SURAT JURISDICTION  This is a Computer Generated Invoice</t>
@@ -4888,11 +4616,7 @@
           <t>IMG_20260516_165903.jpg</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>IRN  1df3996ab74ffffe8acc4 Ack</t>
-        </is>
-      </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
           <t>SHED</t>
@@ -4900,10 +4624,10 @@
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="n">
-        <v>14818.75</v>
-      </c>
+      <c r="F153" t="n">
+        <v>38.55</v>
+      </c>
+      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>IRN  1df3996ab74ffffe8acc4 Ack No. : 162520652748628 Ack Date: 9-May-25  &gt; 912460539bd8e35f02f57677c4526a735995e54e4a0-  SHREE CHANDRAJI METAL CORPORATION G-1/2,Manikan Complex,Below Union Bank, Nr.Udhna Bus Depot,Main Road,  Udhna Surat. }  GSTIN/UIN: 24AQYPR3586Q12ZH  State Name: Gujarat, Code: 24  Contact - 0261-2270027,+21-999R157057/ 9974048199  ‘Invoice No.  388-2025-26 Delivery Note  Capea f [98-May-25 | Mode/Terms of Payment \ByNeft | Other References  Reference No. &amp; Date.  388 dt,9-May-25 || | Buyer's Order No. \ ‘Dated  E-Mail : shreechandrajimetal@gmail.com www.shreechandrajimetal.in  Buyer (Bill to)  SHED  29-30, SAMAYSAAR BUNGLOW, NR NANDINI,  7] Delivery Note Date  Dispatch Doc No.  1 Dispatched through | Destination  3 VIP ROAD, SURAT, Surat, Gujarat, 395007 By Hand | Surat GSTIN/UIN : 2ZAAAAHY7933G1ZY Terms of Delivery | State Name : Gujarat, Code : 24 » Place of Supply : Gujarat ‘ Xe Contact : 9558038546 i { Sl Description of Goods HSN/SAC | Quantity Rate | per | Disc. % | Amount No. | | ‘ | | 1 GISTRIP FLATE / SQURE 73089090 73089090 | 38.550 kg 125.00 ) kg 4,818.75 25 X 6 MM | ; SGST | 433.69 asl f CGST. | a ~~433.62- Less: ROUND OFF | (-)0.13 | | i | | I | | f on | ha i L | 2 ) ho | | | YO VAY | , Total 38.550 kg | _ = 5,686.00 Amount Chargeable (in words) | E. &amp; O.E| INR Five Thousand Six Hundred Eighty Six Only HSN/SAC \ Taxable Central Tax | |! State Tax | Total _ | Value Rate, | Amount | Rate\), Amount | Tax Amount 73089090 zi | 14,818.75] 7)" 9%)" ~~ 483.69|" 3% ay 433.69 © $67 38 ¥ Total! 4,818.75 433.69 | 433.69| 867.38 ; : SA) ERO OO | Tax Amount (in words) : INR Eight Hundred Sixty Seven and Thirty Eight paise Only Company's PAN : AQYPR3586Q i  Declaration iW Company's Bank Details ; We declare that this invoice shows the actual price of the Bank Name : HDFC BANK-OD goods described and that all particulars are true and correct. A/c No. : 50200028513464  Branch &amp; IFS Code: UDHYOGNAGAR UDHNA &amp; HDFC0003948  Customer's Seal and Signature  SUBJECT TO SURAT JURISDICTION This is a Computer Generated Invoice ay</t>
@@ -4916,25 +4640,21 @@
           <t>IMG_20260516_165910.jpg</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>TAX INVOICE  IR</t>
-        </is>
-      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="n">
+        <v>7528</v>
+      </c>
+      <c r="G154" t="inlineStr">
         <is>
           <t>24AQYPR3586Q1ZH</t>
         </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="n">
-        <v>7528</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -4972,18 +4692,18 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PUNJAB NATIONAL BANK</t>
+          <t>24BKIPK7354Q1ZH</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>24BKIPK7354Q1ZH</t>
-        </is>
-      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>24BKIPK7354Q1ZH</t>
+        </is>
+      </c>
       <c r="H156" t="inlineStr">
         <is>
           <t>GSTIN : 24BKIPK7354Q1ZH State Code : 24 Gujarat  ~ &gt; |e  = Ls)  Bank Name PUNJAB NATIONAL BANK Account Number: 4535002100019578  IFSC Code PUNBO453500  Branch MAIN ROAD, UDHNA, SURAT 394210  ie 1. Subject to Surat Jurisdction.  2. Goods have been sold &amp; Despatched at the entire risk of Purchasér._ nel a sl 3. Payment must be paid within 7 days. 2 ear }) ) (i (See  eye 4. Complaints if any regarding this invoice must be informed in writing within 48 Hrs) Authorised Signature</t>
@@ -5000,10 +4720,10 @@
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="n">
+      <c r="F157" t="n">
         <v>2.09</v>
       </c>
+      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
           <t>ms  ~ _a-_ nn 2 ee “ a0! ~ ae ‘ Ma Ss ore. = 2 web kY * aft | &lt;  “Es Pe Swe  in 5)Pp| 26  [ Ramchod Chew v Ac i nick -  Fitting Jhangs = '620° | TE ise “Tht angel Miele @)  2.09.00|}2:  ngovo/z ©  \Ulgo/—= qo p- =  asggo% ©)  S4 peo 2 ()  maa3&amp; (©) \  &gt; &lt;"~ |e -zaee  pw) aa) Tame Toth = 163653 Dt  oN TA</t>
@@ -5016,11 +4736,7 @@
           <t>IMG_20260516_170058.jpg</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>ANA LAHG</t>
-        </is>
-      </c>
+      <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
@@ -5040,7 +4756,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ZI  TAX INVOICE</t>
+          <t>0O8SAAKFA9121G1ZI TAX</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -5060,20 +4776,16 @@
           <t>IMG_20260516_170120.jpg</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>ALL TYPE OF ENGINEERING REPAIRING &amp; JOB</t>
-        </is>
-      </c>
+      <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>24BJZPM1877Q1Z0</t>
-        </is>
-      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>24BJZPM1877Q1Z0</t>
+        </is>
+      </c>
       <c r="H160" t="inlineStr">
         <is>
           <t>a  ne ily Bd ag) Ne Ce |  D h | RN. Ul j MM. 8511397203 | aS i i | Dashamaa Engineering Works ALL TYPE OF ENGINEERING REPAIRING &amp; JOB WORKS Plot No. 8, Ground Floor, Shiv Nagar Ind. Estate, B/h. Petro! Pump, Udhna, Surst-scect Q State : Gujarat TAX INVOICE  State Code : 24 GSTIN : 24BJZPM1877Q1Z0  Qe Invoice Numter « hy %  Date : 2S- his (SET  Quantity  Th SICA  Ly pe G  ZNO 6S  ay rR, 2,4 ey  Toes *¢  us  cA) 1)  ~ oh! . 4 ee an ot ay es 48, ee: eS esy Fins v ~ eee 4G  Total Amourit Befcre tax| |  upees in 7 eee eae A y) EN.) i a  X n a add:cast KY, | A Zoytu 3ankName : The Surat People Co. Bank Ltd. Add: IGST NC. No. : 304008536854 San, FSC Code : SPCB0251007 ors abe "ERMS &amp; CON so( en |, This bill Is ills dolivered a3 per your order and in perfect condition. For, Dashamaa Eng 1, Goods Is handed over to carer's al buyer's risk and responsibiity only.  }, Broker Is responsible for buyers payment dues.  I. Interest will be charged @ 21% if payment is not made as per payment conciten. Sheet Che ew ean tees 5, Subject to Surat Jurisdiction Authorised Signa:on  oh  CE Scanned with OKEN Scanner  ry oT Seer nM Ses rie oa ht A ae e . AAS eae tape oy pa ie ee \s ast x ¥ « % A as , . . - \ ; he N . 4 ~ ‘ We. x ASS Y va : ~  Y</t>
@@ -5088,7 +4800,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>7,47 - 1 AQ cI1san</t>
+          <t>O8ABAPMB364)175</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -5108,11 +4820,7 @@
           <t>IMG_20260516_170358.jpg</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>YS EFRON</t>
-        </is>
-      </c>
+      <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
@@ -5132,7 +4840,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>T INVOICE</t>
+          <t>O8ABAPM8364)1ZB</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -5176,16 +4884,16 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>TERPRISE CRYSTAL ENT</t>
+          <t>O8ABAPM8364J1ZB</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>MRDeee</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
@@ -5202,7 +4910,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CRYSTALENTERPRISES</t>
+          <t>O8ABAPM8364J1ZB</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -5224,7 +4932,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>41-2567305</t>
+          <t>O8ABAPM8364J1ZB</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -5244,18 +4952,18 @@
           <t>IMG_20260516_170446.jpg</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>GST INVOICE</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr"/>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ol 9</t>
+        </is>
+      </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="n">
+      <c r="F168" t="n">
         <v>0.59</v>
       </c>
+      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
           <t>ne Gh 6 Xe &lt;e a  . 4 SRR og tag Re Na Oe ¢ MAIER,  Wey alle 5 GSTIN : O8ABAPM8364J1ZB [GST INVOICE] Phone : +91-141-256730  CRYSTAL ENTERPRISES  Grinding Wheel, Grinding Disk, Disk &amp; utting, Wheels, Saw etc.  State : Rajasthan Code : 08  Manufacturer &amp; Dealer of: Tools Polishing, Wheels Bricks C  HALDIY  903,  seeeRgecceoccec: Gee De COCOA SSSI ESA I asia ae wvvcenneccccncccsscsnenseceneee wervecencceececenccseeereee  Address :  State : -ceeeeee SUSAR rales. coco COE &amp; orsesssssceeeeeeees GSTIN CU ARAHXYAL 3B OLZY ae Way Bill No.  Yin } 8260 ISooR |b8ok  Am sw DSc  jae ‘an ( SS. - ra  2}BCal Saw Blade 8 0.59  \| eh  Ae ar 17 &amp;eimw y 4 fame r / Mag Ke | my kKenhor  si fol Ai — Crome pxide CLLrinn Parmley . (Gr, mht vf jack CV  Gouge “opm  Grin ing. Tool  9  Total In Words :  Bank Details :  ORIGINAL - PINK DUPLICATE - YELLOW TRIPLICATE - WHITE  Terms &amp; Conditions :  Certified that the particulars given above are true &amp; correct All Subject to Jaipur Jurisdiction only. E.&amp; O.E.  Receiver’s Signature</t>
@@ -5270,16 +4978,16 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ZB  CRYSTAL ENTERPRISES</t>
+          <t>O8ABAPM8364J1ZB</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="n">
+      <c r="F169" t="n">
         <v>3.12</v>
       </c>
+      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
           <t>Cache bv) wee ow wma ww’ yw yw wer  Phone : +91-141-2567305 GSTIN : O8ABAPM8364J1ZB  CRYSTAL ENTERPRISES = ___  ; |, Grinding Disk, Disk &amp; Manufacturer &amp; Dealer of : Grinding to CAN ae “4 mothe KS  Tools Polishing, Wheels Bricks Cutting,  wcccceccecssitHMMEREEEI rs tsseneocscseseesers MISES, all BIE 70d  ACICIeSS : wecesssssecceccerssssensesscesseneesnen® 7 a peat wala RENE 8 cccceccennocooococcang SuUbALO Place of Transport GSTIN Oh ABDAXY A432 3.12%. seneenannnrne PAA BilliNCOs ies ee a  Code  3)  TOTAL BEFORE TAX [JK 5Q0=bn OTHERS A | Total In Words : 7  |  Kumthr | 8904 = 4A  Bank Details : ROUND OFF ee ee GRAND TOTAL [5-4 78 UY-Lyp’  ORIGINAL - PINK  ae ae - j . DUPLICATE - YELLOW  ertifie: jat the particulars given above are true &amp; correct  All Subject to Jaipur hares only. E.&amp; O.E. f f PTAC NAAN Receiver’s Signature</t>
@@ -5294,10 +5002,14 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ZB  CRYSTAL EN TERPRISES</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr"/>
+          <t>O8ABAPM836431ZB CRYSTAL</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>TAL BEFORE TAX DEYevs a ous Paes.</t>
+        </is>
+      </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
@@ -5314,18 +5026,14 @@
           <t>IMG_20260516_170522.jpg</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>STALL</t>
-        </is>
-      </c>
+      <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="n">
+      <c r="F171" t="n">
         <v>907</v>
       </c>
+      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
           <t>~ryt STALL aianuiacivret &amp; Dealet of: Gil Tools rollehing, Wheels Arle  LOIYON KA RASTA,  CRY ndtinta V4  NE fee Cottle, JONARL BAZAR J  tas tinel,  Whealt  in wor  AIRUR-  Grindirie  Code: «  2 EEA  gare  DESCRIPTION OF GOOD Beyeran, DmeND DISC  Vag LGR:  Lyne. Loe.  /  yy poke  tre? Bok. |}  ds — ?  ssfnitla 7  RT Yon  Het sa lithonas  $hiial thie pris plesdeare ' al 4444 Laatyanay MPH is | Ue {sus &amp; conned  Tesetrs  ORIGINA  TRIPLICAT  Receiver’s Signature  OYA emer tm  DUPLICAT  L - PINK  £ - YELLOW E - WHITE  en) a7 yat PAYAL sated \ WITS RLS  wn Pajaihan haw ote.  “907.003 (RAS  Ee rere  | eit lc  Mode of Trans  Place of Tra</t>
@@ -5340,16 +5048,20 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>&lt;= co a LOSTINVOICK</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr"/>
+          <t>LOSTINVOICK</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>n a Oroni re tere No. PRON. ye</t>
+        </is>
+      </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="n">
+      <c r="F172" t="n">
         <v>1.52</v>
       </c>
+      <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
           <t>&lt;= co a LOSTINVOICK Phone 1 +91-1A1-2567905  CRYSTAL ENTERPRISES  Manvraciurer @ Ueaier of 1 Grinding Wheel, Grinding Olsk, Olsk &amp; Tools Pollahing, Wheels Bricks Cutting, Wheels, Suw ate.  903, HALDIYON KA RASTA, JOHAR! BAZAR, JAIPUR- 302 003 (RAJ  Name,zgiteneertntens S HER Mme seteaLbicsseadebuaasiand sutton a Oroni re tere No. PRON. ye Dates AJR) FO 2M seerercersssecreses  Herre syI dor sb esa  State 1 Rulawhan Code 108  | A chcdiess ta eerscoantteearsscs Resi Reathcisestrvbaa itis Utirestnislinatttieitees: Mode of Transport  Nar AV RS tiigatis Code tannins | oliey oF thanenor Esra DV SUN ON Gey aa hey NA WemBINGy el Ais : DESCRIPTION OF GOCD | CRYSTALD AM DAW DISC Crvimdy  (ae Ca CS 1 Cae  Fos  CIBCAP Qany Prlabe £1.52  | | 16 RE Try Kenber  Folin oti A132 | | Comme pxide fe lahing Pauler. | ern na} aie. ac”  Bout JoD mm \  3 _ &lt;r al ¢ eec\ &gt; Grainning Too A  ND  {, VINCKS  Total In Words :  Bank Detalls | | ROUND OFF 1 Dy Me GRAND TOTAL  ORIGINAL - PINK Terms &amp; Conditlons : Bhai ig DUPLICATE - YELLOW Certified thot the portiasans given above are trve &amp; correct TRIPLICATE - WHITE All Subjed to Jalpur Jurisdiction only. E.8 O-E Receiver's Signature</t>
@@ -5364,7 +5076,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>OITINVOICH</t>
+          <t>ORADAPM83643120</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -5384,11 +5096,7 @@
           <t>IMG_20260516_170709.jpg</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>MSME NO</t>
-        </is>
-      </c>
+      <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
           <t>SHED</t>
@@ -5396,21 +5104,21 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
+          <t>1453</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>09-03-2026</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>6290</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>1453</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>09-03-2026</t>
-        </is>
-      </c>
-      <c r="G174" t="n">
-        <v>6290</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -5424,11 +5132,7 @@
           <t>IMG_20260516_170719.jpg</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>TAX INVOICE</t>
-        </is>
-      </c>
+      <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
           <t>SHED</t>
@@ -5436,10 +5140,10 @@
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="n">
+      <c r="F175" t="n">
         <v>2780.5</v>
       </c>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
           <t>TAX INVOICE (ORIGINAL FOR RECIPIENT) e-Invoice  meee teesa se] rat crea Ee  IRN - 371b99052bc9888290e1 Aafg01da1f263d1 2c457590- 7de9a8490591 9dd7a6ba0  Ack No. : 162623678477382  Ack Date : 20-Feb-26  SHREE CHANDRAJ! METAL CORPORATION Invoice No.  G-1/2,Manikan Complex,Below Union Bank, |3260-2025-26 20-Feb-26  Nr.Udhna Bus Depot,Main Road, | Delivery Note /Mode/Terms of Payment | Hdfc Online _  Udhna Surat. URED) Maal UDYAM : UDYAM-GJ-22-0023965 (Micro) Reference No. &amp; Date. Other References GSTIN/UIN: 244QYPRSSSEO ST 3260 dt. 20-Feb-2600  Stare Name . Gujeias, Code : 24 Buyer's Order No. Dated  Contact : 0261-2270027,+91-9998157057/ 9974048199  E-Mail : shreechandrajimetal@gmail.com Benaich DoclNa! ——Seiwery Note Date  www.shreechandrajimetal.in 3260  Buyer (Bill to) | CN SHED Dispatched through | Destination | Surat  29-30, SAMAYSAAR BUNGLOW, NR NANDINI, By Hand  3 VIP ROAD, SURAT, Surat, Gujarat, 395007 'Terms of Delivery GSTIN/UIN - 2Q4AAAHY7933G1ZY State Name - Gujarat, Code : 24 Place of Supply : Gujarat  Contact : 9558038546 |  Sl Description of Goods ” THSN/SAC Quantity | Rate | per | Disc. % Amount No. | | |  Tuna 1 I i Wa  4 BRASS ROD BARS (74072120 ) |74072120 | 3.350 kg} 830.00' kg 25x 25mm | | ‘|  2,780.50  Total | 3.350 kg  Amount Chargeable (in words) INR Three Thousand Two Hundred Eighty One Only ~ HSN/SAC | Taxable | CGST _ WMsGsmUnGSim Total Value Rate | Amount | Rate | Amount | Tax Amount 74072120 TV 2,766.50) S| 250.25 | 9% | 250.25 Total | 2,780.50 | 1250.25)  Tax Amount (in words) : INR Five Hundred and Fifty paise Only  Company's PAN : AQYPR3586Q  Declaration Company's Bank Details  We declare that this invoice shows the actual price of the Bank Name : HDFC BANK-OD  goods described and that all particulars are true and correct. A/c No. - 50200028513464 Branch &amp; IFS Code: UDHYOGNAGAR UDHNA &amp; HDFC0003948  Customer's Seal and Signature for SHREE CHANDRAJI METAL _  Prepared by Verified by SUBJECT TO SURAT JURISDICTION  This is a Computer Generated Invoice  . ¢. tee , 4 lap dy aS, ave  Me aN eis aig has ee ok RP Gag De:</t>
@@ -5452,11 +5156,7 @@
           <t>IMG_20260516_170728.jpg</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>TAX INVOICE</t>
-        </is>
-      </c>
+      <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
         <is>
           <t>SHED</t>
@@ -5464,10 +5164,10 @@
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="n">
+      <c r="F176" t="n">
         <v>5590</v>
       </c>
+      <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
           <t>TAX INVOICE (ORIGINAL FOR RECIPIENT)  IRN &gt; ce9887f4b111 5b61f54359b0bb0ec9445ec087e7 1f5- 08c674782f7d2ffecaba8  Ack No. : 462623744921849  Ack Date : 26-Feb-26  SHREE CHANDRAJ! METAL CORPORATION G-1/2,Manikan Complex,Below Union Bank, 13342 a Nr.Udhna Bus Depot,Main Road, Delivery Note 4 ms of Pay Udhna Surat. . a bith (AY \Immidate _ ba UDYAM : UDYAM-GJ-22-0023965 (Micro) jReference No. &amp; Date. Other References GSTIN/UIN: 24AQYPR3586Q12H 3346. rt. 26-Feb-26 :  4) Order No. Dated  VInvoice No. 3346-2025-26 26-Feb-26  State Name : Guiaret, Gade. 24 aie Contact - 9961-227 0027 +9 1-9998157 057/ 9974048199  E-Mail : shreechandrajimetal@gmail.com ‘Dispatch Sean —Delivery Note Date www.shreechandrajimetal.in  Buyer (Bill to) SHED  59-30, SAMAYSAAR BUNGLOW, NR NANDINI, ByHand ‘Surat __ 3 VIP ROAD, SURAT, Surat, Gujarat, 395007 ‘Terms of Delivery  GSTIN/UIN - DANAAHY7933G61ZY  State Name - Gujarat, Code : 24  Place of Supply : Gujarat  Contact : 9558038546  'Dispatched through Destination  1 \ Sl Description of Goods | HSNISAC Quantity | Rate per | Disc. Amount No. lap. \ i  1 SS PIPE - 73064000 '73064000 (18.950 kg. 250.00; kg 4,737.50 75x 25mm, 25x 12mm |  | a  CGST  - #SGsT. ROUND OFF |  ey) 17  ae 3  Total "48.950 kg. = 5,590.00 =e OE  Amount Chargeable (in words) O.  INR Five Thousand Five Hundred Ninety Only  HSN/SAC | Taxable CGST SGST/UTGST_‘Total  : 2 | Value | Rate | Amount | Rate |. Amount | Tax Amount  73064000 4,737.50: 2p%! 426.381 9% 426.38 852.76 Total| 4,737.50; | 426.38 | 426.38 852.76  Tax Amount (in words) : INR Eight Hundred Fifty Two and Seventy Six paise Only  Company's PAN : AQYPR3586Q  Declaration Company's Bank Details  We declare that this invoice shows the actual price of the Bank Name - HDFC BANK-OD  goods described and that all particulars are true and correct. A/c No. : 50200028513464 Branch &amp; IFS Code: UDHYOGNAGAR UDHNA &amp; HDFC0003948  Customer's Seal and Signature for SHREE CHANDRAJI METAL C  Prepared by Verified by  SUBJECT TO SURAT JURISDICTION  This is a Computer Generated Invoice</t>
@@ -5482,7 +5182,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TUS  ESE ERE</t>
+          <t>TUS ESE ERE</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -5504,7 +5204,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PATEL BEARING CENTRE ESTD</t>
+          <t>PATEL BEARING CENTRE ESTD-1972</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5512,19 +5212,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>3304</v>
+      </c>
+      <c r="G178" t="inlineStr">
         <is>
           <t>24AADFP5289P1ZK</t>
         </is>
-      </c>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>25/02/2026</t>
-        </is>
-      </c>
-      <c r="G178" t="n">
-        <v>3304</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -5538,29 +5238,25 @@
           <t>IMG_20260516_170830.jpg</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>TAX INVOICE</t>
-        </is>
-      </c>
+      <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" t="inlineStr">
         <is>
           <t>24AAIFO7653D1Z9</t>
         </is>
-      </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>18/02/2026</t>
-        </is>
-      </c>
-      <c r="G179" t="n">
-        <v>7510</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -5574,25 +5270,21 @@
           <t>IMG_20260516_170841.jpg</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>ANGUS MONTGOMERY ART</t>
-        </is>
-      </c>
+      <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
         <is>
           <t>Yogesh Natwarlal Shah (HUF)</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G180" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="n">
-        <v>23600</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -5608,7 +5300,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>S.MOHANLAL KACHARABHAI MEHTA</t>
+          <t>M/S.MOHANLAL KACHARABHAI MEHTA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5616,19 +5308,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>27-01-2026</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>44545</v>
+      </c>
+      <c r="G181" t="inlineStr">
         <is>
           <t>24AAEFM0653M1ZA</t>
         </is>
-      </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>27-01-2026</t>
-        </is>
-      </c>
-      <c r="G181" t="n">
-        <v>44545</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -5644,7 +5336,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>AL KACHARABHAI MEHTA  M</t>
+          <t>KACHARABHAI MEHTA M/S.MOHANL</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5654,21 +5346,21 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
+          <t>9128</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>45-01-2026</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>370.01</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>9128</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>45-01-2026</t>
-        </is>
-      </c>
-      <c r="G182" t="n">
-        <v>370.01</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -5684,7 +5376,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ORIGINAL</t>
+          <t>M/S.MOHANLAL KACHARABHAI MEHTA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5694,21 +5386,21 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
+          <t>8518</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>25-12-2025</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>42.82</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
           <t>24AAEFM0653M1ZA</t>
         </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>8518</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>25-12-2025</t>
-        </is>
-      </c>
-      <c r="G183" t="n">
-        <v>4313</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -5724,7 +5416,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>S.MOHANLAL KACHARABHAI MEHTA</t>
+          <t>M/S.MOHANLAL KACHARABHAI MEHTA 3/231,GANCHI SHERI, OPP.CLOCK TOWER, NEAR BHAGAL, SURAT</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5732,19 +5424,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>19-12-2025</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>1419.96</v>
+      </c>
+      <c r="G184" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>19-12-2025</t>
-        </is>
-      </c>
-      <c r="G184" t="n">
-        <v>1419.96</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -5760,7 +5452,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ORIGINAL</t>
+          <t>M/S.MOHANLAL KACHARABHAIT MEHTA 3/231,GANCHI SHERI, OPP.CLOCK TOWER, NEAR BHAGAL, SURAT</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5770,21 +5462,21 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
+          <t>6541</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>46-10-2025</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>3750.02</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
           <t>24AAEFM0653M1ZA</t>
         </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>6541</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>46-10-2025</t>
-        </is>
-      </c>
-      <c r="G185" t="n">
-        <v>3750.02</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -5800,7 +5492,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ORIGINAL</t>
+          <t>M/S.MOHANLAL KACHARABHAI MEHTA 3/231,GANCHI SHERI, OPP.CILOCK TOWER, NEAR BHAGAL., SURAT</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5809,15 +5501,15 @@
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr">
+      <c r="E186" t="inlineStr">
         <is>
           <t>44-10-2025</t>
         </is>
       </c>
-      <c r="G186" t="n">
-        <v>12021.04</v>
-      </c>
+      <c r="F186" t="n">
+        <v>329</v>
+      </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
           <t>————————————  ORIGINAL  “Sthroo Ganoahay Nama”  M/S.MOHANLAL KACHARABHAI MEHTA  3/231,GANCHI SHERI, OPP.CILOCK TOWER, NEAR BHAGAL., SURAT Gujntnt 305 003  Phone : 9825469130 2425129,2417129 Emall « mkmontatsoegamyrnatl am  j GSTIN : 24AAEFMOGS3SMIZA TAX INVOICE  PAN &gt; AAEFMO0653M MSME_; GJ-22-0346448  invoica Ho: 6460 125-26  Details of Recelver(Bitled to) SHED Date : 44-10-2025 29-30, SAMAYSAAR BUNGLOW, 5 NR NANDINI -3 Challan No: 0  Date 44-40-2025  VIP ROAD 9558038546 SURAT 395 007  State : Gujarat Code : 24 GSTIN : 24AAARY7S33G1ZY Transpor:  sere = sates nn OF : RN :71001e492835d1 18923182976da63c7e330998049b9f8482cbf4f7e63ad25647 Ack No.: 1  “Marks ° °°: NO Vehicle No. : Destination: § 9 .. ».... + _Eway,Bill.No.: 62522326294152 Ack Date.: 2025-10-14 17:09:00  EPE FOAM 39211900} 70.00 | Mts 70,22 4915.40 9.00 442.39 3.00  12 MM 2 ROLL ape AC t 4 AIR BUBBLE FILM Ges Th toes ck 39201012 200.00. Mts, vit 7.63 1526.00 1 MTRX109 MIRX2 ROLL } Aa ' His ;  ¥ | CORRUGATED ROLL ES u 48191010 30.000 | Kgs 67.80 1 ROLL 1  Bs mit sts  Bank Detaiis :- THE SURAT PEOPLES CO-OP.BANK AJC.NO.104011526205 IFSC CODE : SPCB0251001 VAN ar Cn  Rs.: TWELVE THOUSAND TWENTY ONE Giily Total Rs.: 12,021.00  Terms: (1) We reserve the right right of recovery before due dale at any time. (2) The sale is understood to have been made after due consideration of the quality of goods and  Gate. (6) Subject to SURAT Jurisdiction.  E.2.0.E For: NUS. MOHANLAL KAGHARABRAI MEHTA  Received by Cm CI rake nme  \MCSIRINVBTEGENRLFRS  Prepared by  Value Yo Rs. j Y Rs_ ‘ ft 442.39 5200.12  9.00! 137.34 9.00- 137.34 1800.62  2034.00 | 9.00 . 183.06 | 9.00 183.06 2400.12  PAPER CUTTER 82111000 2 | Pcs 31.25 62.50 | 6.00 3.75 | 6.00 3.75 | 70.00 PAPER ane ony yy 7921490 2}pces | 17.86 35.72 | 9.00 3.21 | 9.00 3.21 42.14 BOPP TAPE ne 39191000 | 24 | Pcs 42.37 | 1016.88 | 9.00 91.52 | 9.00 91.52 i ae i : : : . 4 5 4199.92 be Has Yip nAY Bib AME La ", Ae if Ce i it ae : FRE! TEMPO RENT 996519 , 41 | Pes 600.00 600.00 | 9,00,-:. 54.06 | S.00 54.00 | 798.00  Total 329.000 10190.50 $15.27 915.27 12021.04  prevailing rates. (3) Report shall have to be Tidiscecteet cece at ec presented within 24 hours of delivery, where afier no complaints of any change in quality or shorta i yers risk. (5) The payment of this bili shail be made by the due date failing which interest @ the me of 2.5% Breushal GoGhargsa tram ine dos  Authorised Signatory  EY x  FS ITP) r  Wet  ae eae  &lt; at  2 SP SA ee Sy ee  Wort ta  ON  Q  Pe. &gt;  -  oe,  -  yr | Hien  eo ’  ar .°</t>
@@ -5832,7 +5524,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ORIGINAL  M</t>
+          <t>B-2 AE}</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5842,21 +5534,21 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
+          <t>6074</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>03-10-2025</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>434.58</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
           <t>24AAEFM0653M1ZA</t>
         </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>6074</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>03-10-2025</t>
-        </is>
-      </c>
-      <c r="G187" t="n">
-        <v>18219.02</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -5870,29 +5562,25 @@
           <t>IMG_20260516_171213_1.jpg</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>ORIGINAL  A</t>
-        </is>
-      </c>
+      <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>27-01-2026</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>996</v>
+      </c>
+      <c r="G188" t="inlineStr">
         <is>
           <t>24AAEFM0653M1ZA</t>
         </is>
-      </c>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>27-01-2026</t>
-        </is>
-      </c>
-      <c r="G188" t="n">
-        <v>44544.58</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -5908,20 +5596,20 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>LIONS TDD</t>
+          <t>L-109,</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr">
+      <c r="E189" t="inlineStr">
         <is>
           <t>23/02/2026</t>
         </is>
       </c>
-      <c r="G189" t="n">
+      <c r="F189" t="n">
         <v>4950</v>
       </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr">
         <is>
           <t>L-109, Kanchan Jan ga Co  Bhatar Surat: 394219,  Mob.: 9825160180 EmailiD : Navpadbuildchem@yahoo.com GSTIN : 24AHEPK4410B125  mplex, Bhatar Char Rasta,  Tax Invoic LIONS TDD ey Invoice Date: 23/02/2026, on eee a ake i BaN ie : i Transporter ee Bunglow, Nr. a Vee nih We ates a aaa LER ARR NO pe earn e Pe LEE UNS GUY LR/RR Date GSTIN : 24@AAAHY7933G1ZY ie VaHicle’ No: State: 24-GUJARATE U0 i i! Agent  Details of Receiver | Billed to:  OE TC ASN/SAG || GST: Amount ES &amp; | CT le LS UN Rate 1), 1 |Aloor P Tect 15 - ikg 3824990 fr  4950.00 445.50 445.50  Rupees Five Thousand Eight Hundred Forty One Only. Bank Details :-  Bank Name : Indian Overs A/c.No.: 1876020000003  @as Bank, Surat Branch (0112) 42, IFSC : 1OBA0000112  Terms &amp; Conditions :-  OS  ORIGINAL</t>
@@ -5934,25 +5622,21 @@
           <t>IMG_20260516_171249.jpg</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>PE LU AI OVROM REN EEL</t>
-        </is>
-      </c>
+      <c r="B190" t="inlineStr"/>
       <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr">
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>35061000118</v>
+      </c>
+      <c r="G190" t="inlineStr">
         <is>
           <t>24AHEPK4410B1Z5</t>
         </is>
-      </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>16/02/2026</t>
-        </is>
-      </c>
-      <c r="G190" t="n">
-        <v>35061000118</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -5966,29 +5650,25 @@
           <t>IMG_20260516_171257.jpg</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>EEE  L</t>
-        </is>
-      </c>
+      <c r="B191" t="inlineStr"/>
       <c r="C191" t="inlineStr">
         <is>
           <t>Invoice No. 240</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>6501</v>
+      </c>
+      <c r="G191" t="inlineStr">
         <is>
           <t>24AHEPK4410B1Z5</t>
         </is>
-      </c>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="G191" t="n">
-        <v>6501</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -6012,20 +5692,20 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Duplicate</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Duplicate</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
           <t>25/11/2025</t>
         </is>
       </c>
-      <c r="G192" t="n">
+      <c r="F192" t="n">
         <v>8933</v>
       </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
           <t>CLASSIC LES  }  PLOT NO 1/2 AMUL ESTATE NR KAPADIYA WADI ALTHAN ROAD SURAT GUJARAT GSTIN : 24AAOFC4949A12K State Code:24-GuJARAT PAN: AAOFC4949A Original for buyer # TAX INVOICE # Duplicate for Suppliez/Trans. : ee | a ip licateiforssupplier Details of Receiver/Billed To: atai i i : [Invoice No Detail SHED Invoice No: 235 29-30 SAMAYSAAR BUNGLOW! NR 29-30 : Date g25// ii / 202 NANDINI 3 VIP ROAD SURAT SURAT NANDINI 3 VIP) ROAD SURAT SURAT |Challan No: 235 R ; Supply Dt.:25/11/2025  SURAT-395007 SURAT-395007 Gstin : 24AAAHY7933G12Y PAN: AAAHY 7933G Gstin: 24AAAHY7933G12ZY State Cd:24 State: GUJARAT State Cd:24. State:GUJARAT Broker :1  Vehicle:TEMPO f  r  i e Sr1 |Description / |Hsn/Sac | HSN | QYANTITY| . Rate |uoc | Amount \ } y 7 Tena! SAND me cai N 2516 15.820 537.78 )SOM (OH. G2  15.820] | | 8507.62  4 ——_———  i CGST 2.50% BAL « OY) SGST 2.50% BAZ SE) } i  | Bill Amount 8933.00  Eight Thousand Nine Hundred Thirty Three Only  Terms and Conditions: , ls  [1] The goods: are despatched on your account and at your risk, &amp; responsibility,  [2] Shortage or leakage after delivery should be intimated in 24 hours.  [3] After due date interest will be charged 24.008 per annum,GST Applicable On \Interest, [4] Payment will be accepted only by A/c. Payee's Draft/Cheque.  [5] Subject to SURAT Jurisdiction, [6] £. 6 0. B. |  Bank Details Certified that the particular giving above are true § ci Our Bank :KOTAK MAHINDRA BANK  ) For C ss MARBLES A/ca.No. :4912976545 “wee Ifsc Code :KKBK0002848 7 Branch : ANAND MAHAL ROAD ADAJAN SURAT  Authorise Signatory  if  ems Lees</t>
@@ -6040,7 +5720,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>CLASSIC MARBLES  PLOT NO</t>
+          <t>CLASSIC MARBLES PLOT</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6050,21 +5730,21 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
+          <t>Duplicate</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>30/11/2025</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>10520</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Duplicate</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>30/11/2025</t>
-        </is>
-      </c>
-      <c r="G193" t="n">
-        <v>10520</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -6080,10 +5760,14 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>RKS  INTERNATIONAL  TAX INVOICE</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr"/>
+          <t>THE W@RKS INTERNATIONAL TAX</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Micro and a eaea reales have to be made within 15 days of</t>
+        </is>
+      </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
@@ -6102,16 +5786,20 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>RKS  INTERNATIONAL  TAX INVOICE</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr"/>
+          <t>THE W®RKS INTERNATIONAL TAX</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>be made within 15 days of</t>
+        </is>
+      </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="n">
+      <c r="F195" t="n">
         <v>450805.93</v>
       </c>
+      <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
           <t>THE W®RKS  INTERNATIONAL  TAX INVOICE  : ecbfceabfd565653e7¢5276b553"1 aG1 73b333380dc624-  #2357 288dfc9c66c408 : 432625581 273407 : 2-Feb-26  IRN  Ack No. Ack Date  lane | Dated  pee RL Pe 2: rade: O07"  ECTS PVT. LTD.  Village Anangpur dabad, Delhi  BRENNUS PROJ Khasra No. 1436/7,  Near Mount Kailash, Fari Haryana - 421003, India UDYAM : UDYAM-HR-03-0045756 (Small/Services)  GSTIN/UIN: OGAABCE7 127Q1ZA State Name - Haryana, Code : 06 CIN: 92413DL2006PTC1 54988  E-Mail : john @theworksintemnational-com sww.theworksinternational.com  Buyer (Bill to)  Shed  29-30, Samaysaar Bunglow, Nr Nandini  a Surat, Surat Gujarat - 395007, India 9 2AAAAHY7933G61 ZY  S AAAHY7933G : Gujarat, Code : 24 : Gujarat  NCR 121003  3 Vip  GSTIN/UIN PAN/IT No State Name  Place of Supply Particulars  998596-Interstate Sales @ 18% Events, Exhibitions, Conventions and tra Ref: Additional Orders of Your Stand India Art Fair 2026, New Delhi, IN  de shows assista  Exhibition Service  OUTPUT IGST [Integrated Goods &amp; Se  |2-Feb-26 Mode/Terms of RECEIVED TOther References 2602-0101 [IAF26] Dated  Invoice No. 348  ce No. &amp; Date.  Payment  Referen  Buyer's Order No.  L  Terms of Delivery PROJECT: India Art Fair 2026 Dates: February 5-8, 2026  Venue: NSIC Grounds, Okhla, New Delhi, IN  Amount  998596 4,50,805.93  nce services  rvice Tax @ 18%] 27,145.07  |  +——  = 1,77,951.00  Amount Chargeable (in words)  INR One Lakh Seventy Seven One Only  Thousand Nine Hundred Fifty  Remarks: |AF 2026 ADDITIONAL ORDERS  Company's PAN - AABCE7127Q  Declaration  - Payable to Brennus Projects Pvt. Ltd., Payable at Delhi  ; Any querie(s) on this bill should be reported within 7 days of issuance date as above  - As per Section 15 of MSMED Act 2006, Small Enterprises have to be made within 15 days of date of delivery of service or as per terms of agreement, failing which  payments to Micro and  E. &amp; O.E  Company's Bank Details  Alc Holder's Name : Brennus Projects Pvt. Ltd. Bank Name - Kotak Mahindra Bank Ltd. Alc No. - 92052180000595  Branch &amp; IFS Code: Okhla Phase 2, De  SWIFT Code KKBKINBBCPC  provisions of Section 43B(h) of Income Tax Act would be applicable to the buyer of services. - All disputes subject to Delhi jurisdiction only  ROJE Farinas $ (peini-vc®  S, \e  for BRENNUS  &lt;&lt;  d Signatory  (eas  5 authorise  EXHIBITION CONTRACTING SERVICES | EVENTS | INTERIORS |  Regd. Address: C-4/1  SPECIAL PROJECTS | DISPLAYS | NATIONAL PAVILIONS  40, SDA, Hauz Khas, New Delhi, India 410016 | www.theworksinternational.com</t>
@@ -6126,7 +5814,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>INIOS</t>
+          <t>*SUO}INIOS</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -6148,16 +5836,16 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>UONSIPSIENL LYUNS</t>
+          <t>‘UONSIPSIENL LYUNS</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="n">
+      <c r="F197" t="n">
         <v>114.91</v>
       </c>
+      <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr">
         <is>
           <t>ainyeuBbis SJ8Alad~  : ‘UONSIPSIENL LYUNS oO} 39e!Gn AL dae JO 4Deq UBHB} eg jOU j|IM PjOSs GDUO nooes 4 qug.s oe ep eu3 Woy skep ses} UIWWM BUM Ul PERO mae me IBEWUS eq II! WEP ON (Z) ‘eIEP ONP ulUy 114.91 ‘peBseuo ea 11M %bT D seoseu (L) : SHY,  *duOO ILNYVIN SSYHS UOI}ONSU| |BI9adg 04 SWHYAL LNAWAVd  2) TWLOL |-@ bil? Itibes OW fren 1oyons % [3t0 Ile ZikeHe  nbeeeemenseneoneneresnnceens, Pa ee ee oes erence enn: een esenennersnscesavecesen Perret Se Perit) Lite sseeessennacsanenessenesssevessssessansseasseses eres  UlVd MVHSYOTMOLAW  RGU Sr OL Debreenscensssnveeeseneacanssssesnsscevansscssnssessnesaees maeeteses sees stneseesssevenbecevsnectesenecehsareressscsconeressess  JOUVHO ONILLIS TIOHY diNNd JOINUSS  ST Oe eC) OLR TAIT) SY He eo ssenscenecascaassebtccsessssescesncesionencsscaesensssees  a enananeneecceccenaensvareens seevseccsacconscsscassosessssccsesosepbonssccccesenecesveesecsssnsessarsacesanecscnseons: ata bensessceesesseasecesnecseescscceasssasssansees:  aa SNe son Hla  cccanuecuesusansanveconsvessseqnonsenusenscnsoesefpensenecescutenccecocces Cocca Gcos scissile Ilias ssenusacauseas eolsesstehTOPRTORETTTREDTr cs osccssuocehsnoceccuncccnssccccao[pcwsscesaneesES==S0 zetia a acssesececsesssecacscsosccecapeccseseses sees senscarsesoscrne es:  seccocoovenccnsecevecccepanovenocccavonncneuseer®  “oo (es ew EEE Hsng Old) Ts conecceessacsesensensonenseeerssoserevecssveseipeesesss mod en pa : shih SS ————— SS SS See | eae SSRESeL ue fen TO) ee ee So once Ene poe ---=— = SS See en ee ae — 4 i (oS ee eee mene hy | Seat! RS “ens ener ere el aa ei. ae ae Sn rr ret eerie RIES Sen “cies © rears es Hse enn, Sree aero j1e30d SHed fon’s| Spooy jo suejnsved © ae, NILSS  gq  —WrGo  eee MON SS pe ter SM | ON UeIIEUD  LY8 .  ; ; 2 06 woo yeuB@ dwayne : Wades M6 AV) 6ujddous seq jebuew ala “oueuAd ‘9S aujbu3  49 ‘uy WSEMS 8 yexsOuly  6 9820 OZs6 : OW  a2uajja2x%2 yaam ja suoah  Q  ‘Iwuns ‘peod WN TW yyeuly  Spon Bunledoy 9 Bus0g MON 0} “8 '.9 ‘uv GO1NES B SajeS-1eHEIS JOIOW 22 Buuajemag ‘yesdwnd YOO\qOUuOW esduind |la=M-4UedO yesdwind aiqissaWwans  4409 IIA Ad aauHs iii  eas ele Falletnic yew  14Odau dOHSHHOA _ NWTIWHO Ada ALA  EE"</t>
@@ -6170,25 +5858,21 @@
           <t>IMG_20260516_171438.jpg</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>S  TAX INVOICE</t>
-        </is>
-      </c>
+      <c r="B198" t="inlineStr"/>
       <c r="C198" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="n">
+        <v>11095</v>
+      </c>
+      <c r="G198" t="inlineStr">
         <is>
           <t>24BKDPC3008E2ZZ</t>
         </is>
-      </c>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="n">
-        <v>11095</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -6202,11 +5886,7 @@
           <t>IMG_20260516_171450.jpg</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>NDRA STEEL</t>
-        </is>
-      </c>
+      <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr"/>
@@ -6224,25 +5904,21 @@
           <t>IMG_20260516_171459.jpg</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>EVERSHINE MARBLE INDUSTRIES</t>
-        </is>
-      </c>
+      <c r="B200" t="inlineStr"/>
       <c r="C200" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="n">
+        <v>22240</v>
+      </c>
+      <c r="G200" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="n">
-        <v>22240</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -6256,29 +5932,25 @@
           <t>IMG_20260516_171508.jpg</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>SABU BHAVAN</t>
-        </is>
-      </c>
+      <c r="B201" t="inlineStr"/>
       <c r="C201" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>06-08-2025</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>122</v>
+      </c>
+      <c r="G201" t="inlineStr">
         <is>
           <t>24AAKFS7386R1Z4</t>
         </is>
-      </c>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>06-08-2025</t>
-        </is>
-      </c>
-      <c r="G201" t="n">
-        <v>122</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -6294,23 +5966,23 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>SUBJECT TO SURAT JURISDICTION</t>
+          <t>SUBJECT</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr">
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>03-01-2026</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>475</v>
+      </c>
+      <c r="G202" t="inlineStr">
         <is>
           <t>24AAKFS7386R1Z4</t>
         </is>
-      </c>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>03-01-2026</t>
-        </is>
-      </c>
-      <c r="G202" t="n">
-        <v>487</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -6326,7 +5998,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ORIGINAL FOR RECIPIENT</t>
+          <t>FOR RECIPIENT) NANDI TRADERS OPP. INDIAN OIL PETROL PUMP,NR.GOTA LAKE,</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6334,15 +6006,15 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="n">
+        <v>4900</v>
+      </c>
+      <c r="G203" t="inlineStr">
         <is>
           <t>24ABOPC4962A1Z0</t>
         </is>
-      </c>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="n">
-        <v>4900</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -6380,7 +6052,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>STOCKIST OF BRASS SHEETS</t>
+          <t>STOCKIST</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -6402,7 +6074,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>BABULAL AND CO.  ALAND COMPANY</t>
+          <t>BABULAL AND CO. ALAND COMPANY</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6410,15 +6082,15 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="n">
+        <v>950</v>
+      </c>
+      <c r="G206" t="inlineStr">
         <is>
           <t>24AUAPM9396F1ZD</t>
         </is>
-      </c>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="n">
-        <v>1121</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -6434,7 +6106,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>A BABULAL AND CO.</t>
+          <t>BABULAL AND CO.</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6442,15 +6114,15 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="n">
+        <v>950</v>
+      </c>
+      <c r="G207" t="inlineStr">
         <is>
           <t>24AUAPM9396F1ZD</t>
         </is>
-      </c>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="n">
-        <v>1121</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -6464,26 +6136,22 @@
           <t>IMG_20260516_171802.jpg</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Aaa  SHED</t>
-        </is>
-      </c>
+      <c r="B208" t="inlineStr"/>
       <c r="C208" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr">
+      <c r="E208" t="inlineStr">
         <is>
           <t>01-04-2025</t>
         </is>
       </c>
-      <c r="G208" t="n">
+      <c r="F208" t="n">
         <v>13110</v>
       </c>
+      <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
           <t>Aaa  SHED  GSTIN :- 24AAAHY7933G12Y ** Ledger [MID:1375] ** From 01-04-2025 to 31-03-2026  PATEL BEARING CENTRE SURAT GSTIN : 24AADFP5289P12K  19-05-25 986 PRCHA1 8496.00 05-06-25 1350 PRCHA1 1322.00 25-06-25 1699 PRCHA1 885.00 01-07-25 1863 PRCHA1 1168.00 14-07-25 2079 PRCHA1 708.00 12579.00 SI-OP—2S_| BSA PRCHA1 531.00 13110.00</t>
@@ -6496,29 +6164,25 @@
           <t>IMG_20260516_171810.jpg</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>N A RD</t>
-        </is>
-      </c>
+      <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>19/05/2025</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>8496</v>
+      </c>
+      <c r="G209" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>19/05/2025</t>
-        </is>
-      </c>
-      <c r="G209" t="n">
-        <v>8496</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -6532,29 +6196,25 @@
           <t>IMG_20260516_171819.jpg</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>A NRE ACN BF ST</t>
-        </is>
-      </c>
+      <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>05/06/2025</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>4322</v>
+      </c>
+      <c r="G210" t="inlineStr">
         <is>
           <t>24AADFP5289P1ZK</t>
         </is>
-      </c>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>05/06/2025</t>
-        </is>
-      </c>
-      <c r="G210" t="n">
-        <v>4322</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -6568,29 +6228,25 @@
           <t>IMG_20260516_171829.jpg</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>TAX INVOICE K ORIGINAL</t>
-        </is>
-      </c>
+      <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>25/06/2025</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>885</v>
+      </c>
+      <c r="G211" t="inlineStr">
         <is>
           <t>24AADFP5289P1ZK</t>
         </is>
-      </c>
-      <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>25/06/2025</t>
-        </is>
-      </c>
-      <c r="G211" t="n">
-        <v>885</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -6604,29 +6260,25 @@
           <t>IMG_20260516_171835.jpg</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>TAX INVOICE  DUPLICATE  PATEL BEARING</t>
-        </is>
-      </c>
+      <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>1168</v>
+      </c>
+      <c r="G212" t="inlineStr">
         <is>
           <t>24AADFP5289P1ZK</t>
         </is>
-      </c>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>01/07/2025</t>
-        </is>
-      </c>
-      <c r="G212" t="n">
-        <v>1168</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -6642,7 +6294,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>GSTIN</t>
+          <t>‘DARADFPSRRGPTER</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6651,15 +6303,15 @@
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr">
+      <c r="E213" t="inlineStr">
         <is>
           <t>14/07/2025</t>
         </is>
       </c>
-      <c r="G213" t="n">
+      <c r="F213" t="n">
         <v>708</v>
       </c>
+      <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
         <is>
           <t>uthorians f ee t. Stoekise : 2  GSTIN No. : ‘DARADFPSRRGPTER  everse Invoice No.  &gt; PBC2079 Invoice Dat : ee = &gt; 14/07/2025  &gt; Gujarat  : SHED : 28-30, SAMAYSAAR BUNGLOW, NR. NANDINI 3, VIP ROAD,  % SURAT State &gt; Gujarat State Code = 24 gee No. - 24AAAHYTS33GIZY PH. No. - AAAHY7933G Mob. No. : 9429331881  Sub Total  Invoice Value {In Words) : Seven Hundred Ei  Receiver's Sign.:  TERMS &amp; CONDITIONS Subject to SURAT jurisdiction. (1) Goods once sold will not be taken back or replaced. (2) Intrest @18% p.a. will be charaed.if payment not made within 7 days.  A Our responsibility cease after goods leave our premises. sO}, 1S  L BLARING CENTRES  4/905, Tulsd Falla, Begumpura, Sural-395 003. Ph.: (0261) 2429543, 2436640 Mob: +91 38665 57648 E- malt: patelhearing1972@pmall.com  wma {i [ po cass t eee Re || oe | eae" | Rie |  PAN No. : AADFP5289P  Agtails of Consiqnes/Shinned to  Name : SHED Address : 29-30, SAMAYSAAR BUNGLOW, NR. NANDINI 3, VIP ROAD,  SURAT : | State 7 Gujarat Siate Code : GSTINNo. +: 24AA4HY7933GiZY¥ PAN No. - AAAHY7933G  { CGST 9.00 % SGST 9.00 %  708.00  -Bank Detail :  Bank Name : INDIAN BANK  Alc No. : CIA 477334633  Branch : RESHAMWALA MARKET NEFT/IFS CODE : IDIB000S039  For, PATEL BEARING CENTRE  Authorised Signatory  Certified that the particulars give  Ee ne</t>
@@ -6672,29 +6324,25 @@
           <t>IMG_20260516_171855.jpg</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>TAX INVOICE  PATEL BEARING CENTRE</t>
-        </is>
-      </c>
+      <c r="B214" t="inlineStr"/>
       <c r="C214" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>31/07/2025</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>531</v>
+      </c>
+      <c r="G214" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>31/07/2025</t>
-        </is>
-      </c>
-      <c r="G214" t="n">
-        <v>531</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -6710,7 +6358,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>RADHIKA TIMBERS  PLOT</t>
+          <t>RADHIKA TIMBERS PLOT NO.</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6718,19 +6366,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>30/05/2025</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>52109</v>
+      </c>
+      <c r="G215" t="inlineStr">
         <is>
           <t>24ABKFR8779A1ZV</t>
         </is>
-      </c>
-      <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>30/05/2025</t>
-        </is>
-      </c>
-      <c r="G215" t="n">
-        <v>145742.57</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -6744,29 +6392,25 @@
           <t>IMG_20260516_171924.jpg</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>SS SS  .</t>
-        </is>
-      </c>
+      <c r="B216" t="inlineStr"/>
       <c r="C216" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>09/06/2025</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>48860</v>
+      </c>
+      <c r="G216" t="inlineStr">
         <is>
           <t>24ABKFR8779A1ZV</t>
         </is>
-      </c>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>09/06/2025</t>
-        </is>
-      </c>
-      <c r="G216" t="n">
-        <v>154396.89</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -6782,7 +6426,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>RADHIKA TIMBERS  PLOT</t>
+          <t>RADHIKA TIMBERS PLOT NO.</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6790,19 +6434,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>27/06/2025</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>93814</v>
+      </c>
+      <c r="G217" t="inlineStr">
         <is>
           <t>24ABKFR8779A1ZV</t>
         </is>
-      </c>
-      <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>27/06/2025</t>
-        </is>
-      </c>
-      <c r="G217" t="n">
-        <v>135671.31</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -6818,7 +6462,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>RADHIKA TIMBERS  \ i PLOT</t>
+          <t>RADHIKA TIMBERS</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6826,19 +6470,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>29/07/2025</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>85427.28</v>
+      </c>
+      <c r="G218" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>29/07/2025</t>
-        </is>
-      </c>
-      <c r="G218" t="n">
-        <v>154381.16</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -6852,25 +6496,21 @@
           <t>IMG_20260516_171953.jpg</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>VENUS LIGHTS</t>
-        </is>
-      </c>
+      <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr">
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>25-26/084</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>1440</v>
+      </c>
+      <c r="G219" t="inlineStr">
         <is>
           <t>27CJAPS3474H1ZY</t>
         </is>
-      </c>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>25-26/084</t>
-        </is>
-      </c>
-      <c r="G219" t="n">
-        <v>1440</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -6890,19 +6530,19 @@
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
-      <c r="D220" t="inlineStr">
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>25-26/099</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>3304</v>
+      </c>
+      <c r="G220" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>25-26/099</t>
-        </is>
-      </c>
-      <c r="G220" t="n">
-        <v>3304</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -6940,7 +6580,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>STOTT AG</t>
+          <t>STOTT AG:</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -6960,11 +6600,7 @@
           <t>IMG_20260516_172039.jpg</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>a 93145 12534  MSME</t>
-        </is>
-      </c>
+      <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr"/>
@@ -6982,11 +6618,7 @@
           <t>IMG_20260516_172046.jpg</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Q G M</t>
-        </is>
-      </c>
+      <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr"/>
@@ -7004,11 +6636,7 @@
           <t>IMG_20260516_172057.jpg</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>A SAABRR RY MA</t>
-        </is>
-      </c>
+      <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr"/>
@@ -7026,11 +6654,7 @@
           <t>IMG_20260516_172121.jpg</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>MUA TY ES</t>
-        </is>
-      </c>
+      <c r="B226" t="inlineStr"/>
       <c r="C226" t="inlineStr">
         <is>
           <t>SHED</t>
@@ -7038,10 +6662,10 @@
       </c>
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="n">
-        <v>60125</v>
-      </c>
+      <c r="F226" t="n">
+        <v>125</v>
+      </c>
+      <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr">
         <is>
           <t>4 ¥ 2m a ar ‘ senha ret * reek tae rie ae } aoe WSs Pads vO a - +e etret MUA TY ES y a a re “Sh me Ts se. 2 ary. Ne Oe Os SE aS So iy Lica os oe ah  m™ Tax Invoice  a}  cae, Gems Invoice No. Dated mi = i Fae Agra Road, Near Wireless, 310 13-Aug-25 olice Line, Jaipur -302003 Delivery Note Mode/Terms of Payment  GSTIN/UIN: O8AAYPY6446J1Z1 State Name : Rajasthan, Code : 08 E-Mail : ajayyadav061@gmail.com  Consignee (Ship to)  Other References  Reference No. &amp; Date.  Dated  Buyer's Order No.  SHED  29-30, Samaysaar Bunglow, Surat Dispatch Doc No; Delivery Note Date GSTIN/UIN - DPAAAAHY7933G1ZY  State Name : Gujarat, Code : 24 Dispatched through Destination  Terms of Delivery  Buyer (Bill to) \ SHED | 29-30, Samaysaatr Bunglow, Surat ' GSTIN/UIN 2 2D4AAAHY7933G1ZY  State Name - Gujarat, Code : 24  Amount  Description of Goods HSN/SAC: | ‘Quantity  ) J} = 71049900 | 1,000.000 kg 50.00| kg 60,000.00  ® Synthetic Rough Stone 425.00  Total] __|#4000.000 kg NY tr Z 60,125.00)  a [Amour Chargeable (in words) Indian Rupees Fifty Thousand One Hundred Twenty Five Only  HSN/SAC  Integrated Tax Total  Amount Tax Amount 125.00 :  71049900  Tax Amount (inwords) : Indian Rupees One Hundred Twenty Five Only  Company's Bank Details  Bank Name : IDBI Bank Alc No. ; 0884102000002080 Company's PAN : AAYPY6446J Branch &amp; IFS Code: Rajapark, Jaipur &amp; iBKLO000884 | y ‘for Yadav Gems  Declaration We declare that this invoice shows the actual price of the  goods described and that all particulars are true and correct.  Authorised Signatory  This is a Computer Generated Invoice</t>
@@ -7054,11 +6678,7 @@
           <t>IMG_20260516_172127.jpg</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>SHED</t>
-        </is>
-      </c>
+      <c r="B227" t="inlineStr"/>
       <c r="C227" t="inlineStr">
         <is>
           <t>SHED</t>
@@ -7066,10 +6686,10 @@
       </c>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="n">
-        <v>40100</v>
-      </c>
+      <c r="F227" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr">
         <is>
           <t>Tax Invoice  Yadav Gems  Plot No, -7, Agra Road, Near Wireless, Police Line, Jaipur -302003 GSTIN/UIN: O8AAYPY6446J1Z1  State Name : Rajasthan, Code : 08  E-Mait : ajayyadavO6t @gmail.com  Consignee (Ship to)  SHED  29-30, Samaysaar Bunglow, Surat GSTIN/UIN : DAAAAHY7933G1ZY State Name : Gujarat, Code : 24  Invoice No.  Dated  17-Dec-25  360 Delivery Note  Mode/Terms of Payment  Reference No. &amp; Date. aR A Buyer's Order No. Dispatch Doc No.  Dispatched through  Other References  ‘ Dated  Delivery Note Date  Destination  Terms of Delivery  |Buyer (Bill to)  SHED  29-30, Samaysaar Bunglow, Surat GSTIN/UIN : PAAAAHY7933G1 TANG |State Name : Gujarat, Code : 24  — }Sl} Description of Goods  / HSN/SAG Quantity  Rate  per  Amount  Im 1 Mix Semi Precious Rough Stone | |  7103 200.000 kg  KG  200.00  kg 40,000.00  +28  100.00  | Total 200.000 kg Z 40,100.00 | Amount Chargeable (in words) E£.&amp; OF Indian Rupees Forty Thousand One Hundred Only HSN/SAC, Taxable Integrated Tax Total Value Rate Amount Tax Amount 7103 | “40.000.00|/ 0.25% | 100.00 400.00 Total 40,000.00 100.00 100.00  Tax Amount (in words) :  Company’s PAN Declaration  indian Rupees One Hundred Only  - AAYPY6446J  Company's Bank Deiails. Bank Name Alc No.  : IDBI Bank - 0884102000002080 Branch &amp; IFS Code: Rajapark, Jalpur &amp; IBKL0000884  We declare that this invoice shows the actual price of the goods described and that all particulars are true and  r Yadav Gems  Authorised Signatory  |  Jor [2 ©  This ls a Computer Generated Invoice  Or) ig: ) 0 Va  y W\/O pre  t</t>
@@ -7082,28 +6702,24 @@
           <t>IMG_20260516_172139.jpg</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>CNC GSTIN</t>
-        </is>
-      </c>
+      <c r="B228" t="inlineStr"/>
       <c r="C228" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
         <is>
           <t>24EQNPM9158Q1ZP</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>17/11/2025</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr">
         <is>
           <t>MK CoreCNC  605-606 shukan palace , B/h kasanagar lake guarden Khan faliya, Katargam Surat , Gujarat 395004,  Co India. re CNC GSTIN - 24EQNPM9158Q1ZP Udyam No - UDYAM-GJ-22-0463975 No sasesten TAX INVOICE Email - mkcorecnc@gmail.com No. &gt;MKCCA0 | Place Of Supply : Gujarat (24) Invoice Date 217/11/2025 Terms : Due on Receipt Due Date 2 17/11/2025 Bill To Sn eae Riana SHED 29-30, SAMAYSAAR BUNGLOW, 29-30, SAMAYSAAR BUNGLOW, NR NANDINI 3 VIP ROAD, | NR NANDINI 3 VIP ROAD, SURAT \ SURAT 395007 Gujarat | 395007 Gujarat India | | India GSTIN 24AAAHY7933G1ZY | a aa BRU RMEUIMIANUNOAMIAVEU ANNALARA TA ete et len me AN | i i | S6sT || i ns i # | Item &amp; Description % Amt | Amount | 7 | 9 TEETH GEAR | 9% | 2,925 | 32,500 | | aan TT TATE TUTTE TANT j it Sub Total 32,500 Total In Words ! (iii i iG Indian Rupee Thirty-Eight Thousand Three Hundred Fifty Only) 4 CGEST9 (2%) 2,925 SGST9 (9%) 2,925 Bank Name: Yes Bank LTD. Hi ‘ , \ 238,350 Account Number : 040061900019510 Total 2 | IFSC Code: YESB0000400 Balance Bue $38,359 Account Name: MK CORECNC x mG; et): 7  Branch At:  Terms &amp; Conditions  required, will be charged extra.  Varacha road , Surat ( Guj.)  — Payment to be made by A/C or Cheque only. ) | — After machining of during machining , if there would be any extraiwork  — Subject to’ Surat ‘jurisdiction only E.&amp;.0.E  oar  i  oy  \) y ; Zoho Crafted with easé using )))-  } Invoice</t>
@@ -7118,20 +6734,20 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>ZD TAX INVOICE  SA GAR CIIEEL</t>
+          <t>24BY1PA6096H1ZD TAX</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr">
+      <c r="E229" t="inlineStr">
         <is>
           <t>10-06-2025</t>
         </is>
       </c>
-      <c r="G229" t="n">
-        <v>89513</v>
-      </c>
+      <c r="F229" t="n">
+        <v>360.25</v>
+      </c>
+      <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr">
         <is>
           <t>24BY1PA6096H1ZD TAX INVOICE  SA GAR CIIEEL  51 , ROAD NO:-6, BESIDE LUNAR PLASTC, NEW ESTATE UDHNA SURAT  Tel - 9913832004  Os  Original Copy  }  | 3. Subject to ‘Gujarat’ Jurisdiction only. |  oo |  Authorised Signatory  $$$ - $$$ —_—_-— — 4 1 \ : ace suljarat (24 Invoice No. ey | Place of Supply . aL at (24) 4 vat 2A a\ (C = \ Date of Invoice 10-06-2025 Reverse Charge Hae A Ma a Billed to Shipped iy, | oes FHC IGAWIAV RAR BUNGLOW | = = A\IO an U ia SK \\ S KN fi ve \ | 29-30 , SAMAYSAAR BUNGLOW , 29-30 ean (SAM Bove 1 NQ_NANDINI 3 VIP ROAD , [ NR. VANDINT 3 VIP ROAD , | SURAT SUKAI ¢ ~ . MOA LISS FOZINITY | GSTIN / UIN . 2A AMMHY7S33G6 1ZY GSTIN / UIN  QADRDAHY79S3G1Z" t wa een - = : eal ‘A i ( + rar hi Saale ad fo | S.N. | Description of Goods HSN/SAC aty. [Unit Price ArOUNLK ) | j vi Coue | | { C= | 1 + | y 26 4S 4 +) =I AOE (910 | @ accoy see 7298 360.25 | Kas. 140.00 50,425.00 | | { i \ 1 1 ! | | | | i | | | i | t | | | | j t | | | | i | : | | | | | | | | | | Liab | | Hig | Rit {OVE OvA | SY) 5 SR EAS AAA bY) NOX UG LAY lay (VvA\, 2 /\ (=i2Xa = SVU - Ue (ee Jey (as) \ Pues 1) Add - SGST @ OOO" % A 520 15 Less : Rounded Off (-) 0.30 io : | Grand Total 360.25 Kgs. st 89,513.00 | L 4 | Tax Rate Taxabie Am CGST SGST_ Total Tax / 5 50,438.00 4,539.15 14,589.15 078,50 { | | Rupees Fifty Nine Thousand Five Hundred Thirteen Only BANK Details Bank name; - HDFC BANK AC/NO = 502000651905 | 52 ,mnewoees 46 PERANC! 1, UDI NOG NAGAR UDUNA | Lei’ COMP RIEDS Receiver's Signature | = (OLS 1. Goods once sold will not be taken hack - - " a! VANS: Ny Ba ty 2. interest @ 18% pd. will be charaed if the paymer | ® 16 ia! fe Will be charged if the payment EOMSAGAR STEEL iS NOL made with in the stipulated tirne 7  a  — =</t>
@@ -7146,7 +6762,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>TAX INVOICE</t>
+          <t>24BY1PA6096H1ZD</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7155,15 +6771,15 @@
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr">
+      <c r="E230" t="inlineStr">
         <is>
           <t>27-06-2025</t>
         </is>
       </c>
-      <c r="G230" t="n">
-        <v>59120</v>
-      </c>
+      <c r="F230" t="n">
+        <v>357.87</v>
+      </c>
+      <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr">
         <is>
           <t>a ay) GSTIN © 24BY1PA6096H1ZD Original Copy | | TAX INVOICE | 51 ROAD NO:-6, BESIDE LUNAR PLASTC, NEW ESTATE | UDHNA SURAT Tel : 9972832004 No 947 | Place of Supply Guiarat (24) | | o VV Ic : Ly i | Date of Invoice 27-06-2025 Reverse Charge N Shipped to: BD) ty oun yi, SHED 3 SLOW 99-30 . SAMAYSAAR BUNGLOW , 29-30 , SAMAYSAAR BUNGLOW , 29°30) SANIAY SHAS DLN | me aie ae VIP ROAD NR. NANDINT 8 VIP ROAD , | see hit V&lt; SURA | | |GSTIN / UIN DAP AAHY 793361 ZY HSN/SAC Oty.| Unit PARAS Arnount{” ) HESS A | | | 7228 357.87| Kgs. 140.00 | 50,191.80 | i { | | : | see, | | | | \ \ I f | ; { | | | { | | | | / | | | | | : 1 Sh y J, i 1 | | | | | : | | | = i Hl | | { | awa @ ars @) VU, U O Prac pen OSS, GN NN D.EO | NSCS ie Add SGST @ 900 % | 4599 14 Less : Rounded Off (-) 0.12 .? va : | - Grand Total 357.87 Kas. | 59,120.00 PEI EUAN L A { Tex Rete Taxable Amt CGSif SGST Total Tax iS 50,101.20 4508.16 4508.16 § 8,016:62  |  } J  Vad wlan hw 5  IIDEONANNND 49 bib UUUI at  Thousand One Hundred Twenty Only  BANK Details  Bank namie; - HDIC BANK AC/NO =! S0 200085190519  FAUT SRI FLIED INES NISSEN LISSA UD  DINAMO 7,  LAL PY CAG INU S OU ur,  at) eee ie rerms &amp; Congitions  Ea OE  1. Goods once sold will not be taken back 2 interest @ 18% pa. will be charged if the payment iS Nol rade with in the stipulated tirne  3. Subject 10 ‘Gujerat’ Jurisdiction only  Rece  iver's Signature |  For SAGAR STEEL  Authorised Signatory  wey  vy  a  ———S i rs</t>
@@ -7176,20 +6792,16 @@
           <t>IMG_20260516_172215.jpg</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>TAX INVOICE</t>
-        </is>
-      </c>
+      <c r="B231" t="inlineStr"/>
       <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>24BIJPJ2549D1ZH</t>
-        </is>
-      </c>
+      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>24BIJPJ2549D1ZH</t>
+        </is>
+      </c>
       <c r="H231" t="inlineStr">
         <is>
           <t>|; Whit \ state Code : 24 TAX INVOICE eth ‘Valew \  VALLABH TRADING |  NON-FERROUS METAL MERCHANT Hanuman Faliya Corner, Yakutpura, Vadodara - 390 006. (Guj.) M.: 9898307809  Dt. of Supply :  Place of Supply :  State Code :  Buyer (Billed to) ors) Add: 99-20 SAMAYSAAR BONGLOW  USL x.) SURAT Pin n Code : 24S oo 4 GSTIN No.: Ze Pin Code:  QUANTITY  AMOUNT  ‘i  Paring  TOTAL Before Tax ot Jo6 |  | HSN/ SAC] ee PARTICULARS CODE |  Orin No.: 24BIJPJ2549D1ZH |  Bank : IDBI BANK LTD. Add.: JUBILEEBAUG, RAOPURA, VADODARA.  AIC. No.: 1910102000004985. -. | IFSC : IBKLO001910 .  Round Off Add / Less eu | Uz  + Taxes will be charged extra as applicable. For, VALLABH TRADING + All rates are net &amp; ex-godown Vadodara i.e. packing &amp; forwarding extra as cost. « Goods once sold will not be taken back.  * Interest at 24% p.a. will be charged for payment after due date  * Subject to Vadodara Jurisdiction.  oe) &amp; OVE: | Authorised Signator MENHAM AY NIM RAARI eg)</t>
@@ -7202,11 +6814,7 @@
           <t>IMG_20260516_172232.jpg</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>TAX INVOICE</t>
-        </is>
-      </c>
+      <c r="B232" t="inlineStr"/>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr"/>
@@ -7224,20 +6832,16 @@
           <t>IMG_20260516_172246.jpg</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>KIMRAY BEARING CENTRE GSTIN</t>
-        </is>
-      </c>
+      <c r="B233" t="inlineStr"/>
       <c r="C233" t="inlineStr"/>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>24AANPP3672J1ZA</t>
-        </is>
-      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr"/>
-      <c r="G233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>24AANPP3672J1ZA</t>
+        </is>
+      </c>
       <c r="H233" t="inlineStr">
         <is>
           <t>aft ona\aitet ota7: 1 ener ft a1 Mien Off. : 95106 09481 E-mail : kbc2772 @ gmail.com Mob. : 94288 68817  -GJ-22-0361727 wowcizeonry  KIMRAY BEARING CENTRE GSTIN: 24AANPP3672J1ZA _4/907, Tulsi FallySECUN rarer  State : Gujarat, Code : 24  ue Y IC  ie 4 0  +E UA  a  pes NUH. igi  Bank Detalls: HDFC BANK BRANCH : Mahidharpura, Surat. Ale. No. 50200048542602 RTGS/NEFT IFSC CODE : HDFC0006022  Bank Detalls: BANK OF BARODA BRANCH :'Sagrampura, Surat. Alc. No. 02600200001167 RTGS/NEFT IFSC CODE ; BARBOSAGRAM  TERMS : (1) Payment within ..‘....... days from the date of our invoice. i B Interest of 24 % per annum will be charged after due date. For, KIMRAJ BEARING CENTRE 3) The amount due under this bill should be paid to this firm by means of An \e A/c. payee's cheque of A/c. payee's draft only. % - a . ee ON,  (4) Subject to Surat Jurisdiction.  E.&amp;0O.E. Authorised Signatory  Ye aig Pape po ee ¥ 27 2tSeis Pipes ye: “ys teh Fe J ies A  Bre 0 eee se  Yr N PERT.  46</t>
@@ -7252,19 +6856,23 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>TAX INVOICE  PYRAMID GLASS AND ALUMINIUM</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr"/>
-      <c r="D234" t="inlineStr">
-        <is>
           <t>24GMVPS6203Q1Z1</t>
         </is>
       </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>tal 2.0000 Samt CGST Amt. SGST Amt.</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
-      <c r="G234" t="n">
-        <v>2220</v>
+      <c r="F234" t="n">
+        <v>2</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>24GMVPS6203Q1Z1</t>
+        </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -7280,16 +6888,16 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>er CG men Ch. OE a on 4</t>
+          <t>24GMVPS620301Z1</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
-      <c r="G235" t="n">
-        <v>4897</v>
-      </c>
+      <c r="F235" t="n">
+        <v>9</v>
+      </c>
+      <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr">
         <is>
           <t>er CG men Ch. OE a on 4  GSTIN 24GMVPS620301Z1 Wii Oriainal Copy | TAX INVOICE Gaui GROUND FLOOR, DEVCHAND NAGAR IND. SOC, UDHNA, Surat } a PAN - i MANGIGE (NC 19/9995 406 j oe Re oii SUD Gujal al (24) | pie ees 57_NA-9025 Ravyarca Charge mreN| { ‘Hod Shipped to ae ae Shed | ' | aay OW 29-20, Samaysaar Bunglow, Nr a ee SMELT Bunglow, Nr ‘let a) Wie, Abe | Mandini 2 win Roo, 1 S{Ale Bei alh) seas ! Ie rat taliceat SBBO7 | Surat Guiarat 395007 ijarat (24) | tat Gujarat (24) State Gujarat ( a a / UIN SA AAMY 79331 2Y GSTIN / UIN DARAAHY 7/9336 1ZY | tly wou my | ISN | Description ot Goods HSN/SAC Qty. | Unit Price) Arnount(Rs. | Code fa g loa MM TOUGHEN GLASS 70071900} 9.0000 ae 461.15 4,150.25 | [ | { § i) r | | | i i | i | 4,150.35 | | Add: CGST | @ &gt; 9.00 % 373.53 | Add : SGST @ 9.00 % 373.58 | | ey Less: Rounded Off (-) spr L | x Grand Total 9.0000 Samt | 4,897.00 |  ne  By Reale TaxabieAmt. CGSTAmt. SGST Amt. Total Tax | 18% 4,150.35 373.53 273.53 747.06 Rupees  Four Thousand Eight Hundred Ninety Seven Only  =  Bank Details  HDrC BANK , A/C NO:- 0200085239401, IFSC CODE:-HUDFCUU0UY 4  Terms &amp; Concitiors  jRecelver’s Signatur  é | E&amp;OE.  Goods once sold will not be taken back. ; TT Scan 4. imerest @ 16% 9.2. will 5e energea sf ine payment = HO Mace wil wn the stipulated time  hor PYRAMID GLASS  AND ALUMIN  3. Subject to ‘Gujarat’ Jurisdictian only  UM |  Authorised Signator  ze  Ae eS AES Mal ORD i</t>
@@ -7304,7 +6912,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>J IA LA</t>
+          <t>A—\LZS</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -7326,18 +6934,18 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>ALL TYPE GF ENGINEERING REPAIRING &amp; JOB</t>
+          <t>ALL TYPE</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>24BJZPM1877Q1Z9</t>
-        </is>
-      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr"/>
-      <c r="G237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>24BJZPM1877Q1Z9</t>
+        </is>
+      </c>
       <c r="H237" t="inlineStr">
         <is>
           <t>a  La — ‘ i )  Dashamaa Engineering Works  ALL TYPE GF ENGINEERING REPAIRING &amp; JOB WORKS Plot No 8, Ground Floor, Shiv Nagar Ind Estate, B/h Petrol Pump. Udhna, Surat-394210  State Gujaral TAX INVOICE State Code 24 GSTIN : 24BJZPM1877Q1Z90  Name S lf é y Invoice Number | address ZA-3D SarVyasay BunGinrs Date n jae i. :  a  S|  |  | Party GSTIN No. HAH LN ee eS  No Description | eee | Quantity Rs  Hh GAyak sk MS WH?)  | Emm AVE MO a2}  ‘o CANA wren hy “wae |  Jemes tees Wn way  Le hom}  | lsonrvel (900 +0 b . | \ = | .  au WY |  ny | Total Amount Betore Tax Ss S Ow- OH E  Betis et) 4 wih w  Aupees in words ot Ae creel a lms 24 &lt; AB age) ae fit? | Ads ScST al 7. 1S Oe ~ &gt; ol rs  | Aca CGST f VAN Sg _— =O) te £.eer DD BRS Ee a es ee Om.h!”!]lUlUCé&lt;(‘ C*#:CiCC Lk !!Llt!tC dK lCULDL lee  | Gabe ee et) CaN  aes  = mew H ~~  5  &gt;  "  3  $  i  R  ;  :  3  :  3  :  i  i  ;  5  3  t  Bank Name esvvh  | AIC. No, SvnvvBs3baCY |  } | FSC Cede RS a “at TERMS &amp; CONDITION :- | 1 Ties b&amp; © for goods delivered as per your order and in perfect conaition For, Dashamaa Bagine ering g Works 2 Goods ® handed over to catners a! buyer's nsk and responsibdity only ‘ : roca @ Feeponsible for buyers payment dues ; nterest w#i be charged @ 21% 4 payment Ss NOt Made as per payment condition ; J 8, Sebyect to Surat Junsdachon sin Authohsed ignatory  QE Scanned with OKEN Scanner</t>
@@ -7352,18 +6960,18 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>ALL TYPE OF ENGINEERING REPAIRING &amp; JOB</t>
+          <t>ALL TYPE</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>24BJZPM1877Q1Z0</t>
-        </is>
-      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>24BJZPM1877Q1Z0</t>
+        </is>
+      </c>
       <c r="H238" t="inlineStr">
         <is>
           <t>N2 8780703108 ll Shree Ganeshay Namah Il M. 8511397233  Dashamaa Engineering Works  ALL TYPE OF ENGINEERING REPAIRING &amp; JOB WORKS Plot No. 8, Ground Floor, Shiv Nagar Ind. Estate, B/h. Petrol Pump, Udhna, Surat-394210  State : Gujarat TAX INVOICE State Code : 24 GSTIN : 24BJZPM1877Q1Z0  Date : [tice G alos  Ch. No. : a  —*  DEQ 2) ee  Description  Q\$SK100 MS. HV. VO |pr00 CW FESO DHA LVRS BNL) 3988 YO  (224 ee 5 ree®) \ ' |  S -G. Zone SUR:  CNG ae SKY FHYZI2 ie  (eye (Drone Ohwrer che  =X see  Bank Name AIC. No.  IFSC Code TERMS &amp; CONDITION :-  1. This bill is for goods delivered as per your order and in perfect condition. For, Dashamaa Engineering Works 2. Goods is handed over to carrier's at buyer's risk and responsibility only.  3. Broker is responsible for buyer's payment dues. f 4. Interest will be charged @ 21% if paymenit is not made as per payment condition. ; =e 5. Subject to Surat Jurisdiction Authorised signatory</t>
@@ -7378,7 +6986,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>ALL TYPE OF ENGINEERING REPAIRING &amp; JOB</t>
+          <t>ALL TYPE</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -7400,7 +7008,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>SHREE GANESHAY NAMAH</t>
+          <t>"SHREE GANESHAY NAMAH:"</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7408,19 +7016,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>24-09-2025</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G240" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>24-09-2025</t>
-        </is>
-      </c>
-      <c r="G240" t="n">
-        <v>1400</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -7434,28 +7042,24 @@
           <t>IMG_20260516_172448.jpg</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>STAR INDIA TEXTILES</t>
-        </is>
-      </c>
+      <c r="B241" t="inlineStr"/>
       <c r="C241" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>09-09-2025</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr"/>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>09-09-2025</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr">
         <is>
           <t>ak $ 4 &lt;y oe tajes Cheah  Oe I LR ee  on \!Shree Ganeshay Nam  sd  STAR INDIA TEXTILES  Sales Office : 109, 1st floor, Muri textile Tower, Pur Road Bhilwara-311001  State : Rajasthan (08 ), India Phone : 8233590008, 9413861915 EMAIL : starindiatex@gmail.com GSTIN : OSBMZPD4968E1ZG  Date 09-09-2025  Invoice No. ; $1/4326  Challan No.  SHED 29-30, SAMAYSAAR BUNGALOW OPPOSITE EMPIRE REGENCY APARTMENTS, NEAR NANDINI 3 VIP ROAD, VESU, SURAT-395007 STATION -VESU,SURAT STATE -GUJARAT-395007  GSTN -24AAAHY7933G1ZY  SAME AS CONSIGNEE  ;  CONTACT __ 9265334140, 63573831 50  &amp;  C ere  Rede  BAMBOO FIBER 5305| 2 BAGS | 32 KGS 605  2BAGS 32 kgs TOTAL 19360 Less Discount  Punjab National Bank Add, Packing AIC No. 4667002100017161 Freight IFSC PUNB0466700  Pur Road,Bhilwara 19360 7a SAFEXPRESS PVT LTD Lr Date Lr No. 968  ASS  TOTAL TAX  E WAY BILL 7215 6013 2241 Vehical No.  |__NETT AMOUNT  i TWENTY THOUSAND THREE HUNDRED TWENTY EIGHT RS ONLY  Condition |  1.Payment should be made by A/c payee cheque only. For STAR INDIA TEXTILES  2.Intrest @18% p.a. will be charged if the payment is not made With in stipulated time. |  3.Subject to "BHILWARA" Jurisdiction only.  4.Goods once sold will not be taken back,  Prepared B</t>
@@ -7468,11 +7072,7 @@
           <t>IMG_20260516_172506.jpg</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>UT UY</t>
-        </is>
-      </c>
+      <c r="B242" t="inlineStr"/>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
@@ -7492,7 +7092,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>NOJEUIS PYSUOUNY AG</t>
+          <t>NOJEUIS PYSUOUNY</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -7514,7 +7114,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>ZOODDEEDOZLO</t>
+          <t>9L1L00008S3A</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -7552,11 +7152,7 @@
           <t>IMG_20260516_172554.jpg</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>TAX INVOICE</t>
-        </is>
-      </c>
+      <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr"/>
@@ -7574,18 +7170,14 @@
           <t>IMG_20260516_172604.jpg</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>S H A N  B</t>
-        </is>
-      </c>
+      <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr"/>
-      <c r="G247" t="n">
+      <c r="F247" t="n">
         <v>13983</v>
       </c>
+      <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr">
         <is>
           <t>i)  Ishan Netsol Private Limited Registered Office. abad Gujarat 380054 eo | S H A N  B-L{. Privilon, Iskcon Cross Road, AmbIi - Bopal Road. Ahmed } DEIN $91 O2KL G4 7426 &amp; 9909047426 TEC  antechnologies.com Phone : hantechnologies.com  CIN : U74900GI2007PTCO0S 1929  TAX INVOICE  Original for Recipient  Customer Name &amp; Billing Address :  Priyanka Yogesh Shah Samaysaat Bunglow, Nr Saavathi Bunglow,  opp empire Regency Vesu, Surat, Ta: Surat, Dist: Surat - 395007.  State : Gujarat , State Code &gt; 24  Invoice Date: 11-Oct-2625  Invoice No.: §R24/25-26/27870  Date: 01-Feb-2021  Customer Order No.:  Tess (Pleo AF anes) + Vid im Address (Place of supply} : SO No.: 2896355  Yogesh Shah |  v= Bunglow, Nr Saavathi Bunglow,  opp empire Regency Vesu, Surat, Ta: Surat, Dist: Surat -  395007. Customer ID: 855379 Service ID: 249669  state: pan State Cede : 24 S500 09&gt; e—c—_"—"$®_$&gt;»—rmn ce \ Ilcategory of Service : Internet iN Lin Mien: 280 | | | | | Lelecommunication S Services i” on erheroen j  Summary of Current Ch  i i i 1 SAC | Particulars | IK Period | Amount (INR) y|  Internet Connectivity Recurring Charge i z 29 f 13983 998422 [Plan: ISHAN UNL 300Mb_ i8N] | 10-Oct-2025 To 10-Apr-2027 13983.0 | | : : : | | | | | Total current charges excluding taxes | 13983.00  | SGST @ 9% ( Gujarat ) | | |CGST @ 9% ( Guiarat )  | | I Total Taxes | a | Rounding Off  oe  1258.47  Total Current Charges including taxes  Amount in words (INR) : Rupees Sixteen Thousands Five Hundred Only</t>
@@ -7598,11 +7190,7 @@
           <t>IMG_20260516_172634.jpg</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>H  VHVSNV</t>
-        </is>
-      </c>
+      <c r="B248" t="inlineStr"/>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr"/>
@@ -7622,7 +7210,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>SHED OS</t>
+          <t>24CRPPS6314F1ZK</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -7630,15 +7218,15 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="n">
+        <v>9830.52</v>
+      </c>
+      <c r="G249" t="inlineStr">
         <is>
           <t>24CRPPS6314F1ZK</t>
         </is>
-      </c>
-      <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr"/>
-      <c r="G249" t="n">
-        <v>11600</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -7654,31 +7242,31 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>OO TN</t>
+          <t>VIVA COMPOSITE PANEL PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Sales Quotation</t>
+          <t>SHED</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
+          <t>4201627</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>30/07/2025</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>39700</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>4201627</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>30/07/2025</t>
-        </is>
-      </c>
-      <c r="G250" t="n">
-        <v>39700</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -7694,7 +7282,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>VIVA COMPOSITE PANEL PRIVATE LIMITED TY</t>
+          <t>VIVA COMPOSITE PANEL PRIVATE LIMITED TY,OPP. GOVALUCK TELEPHONE EXCHANGE,NR. PRACHI</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7704,21 +7292,21 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
+          <t>Sr</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>18/07/2025</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>6728.88</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>Sr</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>18/07/2025</t>
-        </is>
-      </c>
-      <c r="G251" t="n">
-        <v>7606.11</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -7734,7 +7322,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>VIVA COMPOSITE PANEL PRIVATE LIMITED  y -</t>
+          <t>VIVA COMPOSITE PANEL PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7744,21 +7332,21 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
+          <t>GJO2AR25/1200178</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>16/04/2025</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>15880</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
           <t>24AABCV9909K1ZX</t>
         </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>GJO2AR25/1200178</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>16/04/2025</t>
-        </is>
-      </c>
-      <c r="G252" t="n">
-        <v>15880</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -7774,7 +7362,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>J ea ls  VIVA COMPOSITE PANEL PRIVATE LIMITED</t>
+          <t>VIVA COMPOSITE PANEL PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -7782,19 +7370,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>16/04/2025</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>7606.11</v>
+      </c>
+      <c r="G253" t="inlineStr">
         <is>
           <t>24AABCV9909K1ZX</t>
         </is>
-      </c>
-      <c r="E253" t="inlineStr"/>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>16/04/2025</t>
-        </is>
-      </c>
-      <c r="G253" t="n">
-        <v>7606.11</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -7818,19 +7406,19 @@
           <t>SHED</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>18/07/2025</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>7606.11</v>
+      </c>
+      <c r="G254" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E254" t="inlineStr"/>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>18/07/2025</t>
-        </is>
-      </c>
-      <c r="G254" t="n">
-        <v>7606.11</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -7846,7 +7434,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>WHVSNY TWIAVHSS SVONIDYN</t>
+          <t>WHVSNY TWIAVHSS SVONIDYN ‘HOS</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -7868,7 +7456,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>QOIONU</t>
+          <t>QOIONU]</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -7890,7 +7478,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>QOIOAU</t>
+          <t>QOIOAU]</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -7910,26 +7498,22 @@
           <t>IMG_20260516_172853.jpg</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>ON AE</t>
-        </is>
-      </c>
+      <c r="B258" t="inlineStr"/>
       <c r="C258" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr">
+      <c r="D258" t="inlineStr">
         <is>
           <t>Te</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr"/>
-      <c r="G258" t="n">
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="n">
         <v>4665</v>
       </c>
+      <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr">
         <is>
           <t>Do Tae ON AE ie A Os RD SS SD ST ae an OS Te ee See  TAX INVOICE (ORIGINAL FOR RECIPIENT)  ist OW invoice No Te iy dy abe  ss re t ee ERTEAARAEE GPC ITEOL ATH ADVANCE  7  Roferance No. &amp; Data ~~ Gthor Rafarances 2B1I207K-2K At 1BBen-26 | RAE  BEOMENGII Oe MA fuyer's Order No Oatad  | . MANGA 3 NO. 2, vl Be lie  BSE OAR. Aca AS VERBAL BY MR. NILES 16-Sep-25  MUMBAI - 400 O02 Dispatch Doc No Nelivary ote Date  ITEL. NG. : 88207 soe27  MER TINANNE S7 aakenny cosh TZ! Dispatched through Doutinavan  State Name : Maharashtra, Code : 27  Contact : +91-38207 58627 ARAM |  Guyer (Oil 60), Aen Pir Terns af Oolivery  QUT OF THE SHED 28-30, SAMAYSAAR BUNGLOW, NEAR NANDINI - 3  Oe ee ee ee i } Wat Aa) - SSR A Vir Rivsaw, sane |e 3 x PA, e ee SS ee &gt; RRB ices gh MOB NG PRTSAR AGES 7 SUSST, Gsscs  GSTINAUIN - PARAAHYTS33SG1ZY State Name - Gujarat, Code : 24 ! Piace of Supply | Gujarat RUAN  Sy pikcreninonaane tetera nse rican res} TONE Ng y igralniteneih prcaacrped tal ryt “p — SI Oeeciplion |} Goods PES RMO Ae feo USSLaRty “4 ~ \ ; 4 iw { | Ree | Ww ka Re eee oe eS red Sat teint wig eR RE ARM pt (bit rear i 7 caSsem fomseong { oneec! Bee ws | TESe ac Kc | 3,255.55 * —* eee ~ f. t /} © y we eS Wty A ep We see SR t i : { TXSKGS CNE PLASTIC SAG j ‘ | | | P=) MATERIAL PKD IN ONE CARTOON | EO ee 8 Se et Y i Bs A ‘ PROS EE TTA RTE BE ETP REO ¢ j 4 { } { } he d if | { 5 ON TOPAY BASIS TO SURAT é 5 i 4 i" ¥ ¥ } H : : | ; ; i . , Pe ae, sy 4 i: t ey Rae i 4 ne Ne 5 esr OM SALE = +e Ae : 3 2 a oe ery } § 5S see i 4 j { i ; ‘ i 4 . j ik : ; j e : E i i { } be } é ‘ $ 1 u t ‘ oe | - a =v Us ii Aiky edt to pm ese eat so \s Sh dep td Sr NS . : F pers 4 (ttm Aare ARN Pare | } ; (X 8N, I 1O.UU ee ee ee NARI Peni « Jo, SLSR we by ose iets old 6 OURO RE IST go TICES RAE aL) BPO KE CEE SP A EAI he WIRE Font “afl an J — Asnoura Crnrosabie ta weordea =P2OE indian Russses Tan Thousand Nie Hind ted Fifties iy rome a AT ROR CR a I es i ( L SST Tota} Bi. Th Wale | Rate | Amount | Tax Amount  SSS000) 8%) 4,665.00! 1,665.00  rw eres merrenroprceemenlipeapepees eheymelnctteesntey se Berm GA e eae rt pe Spat nhc  “Feta 9.260.00) “| 4,685-00) 1,665.00)  Taz Amount (in words) Indian Rupees One Thousand Six Hund  red Sixty Five Only  Conpany s Back Gerails FM eet Tb oe ee ? Onl cog 4 on 1) NOT FOR MIEDICINAL UGE 2) FOR INTHISD TRIAL &amp; LAE Afc Holder's Name SANATAN CHEMICALS LIFE OA (STIS RG ET AT AR RL FD BM ABD FAK ATA CODES Sv 8 twos de be bomevs on . En aaits ees EIEN Ait. ACCOUNT UNPAID UATHIN 7 OAYS 4) GOOOCS ONCE Tape Tare ea Ra eRe Se, GOLD WALL MOT GE TAKEN GacK elias Age Ne. » 0404020600141769 k oe  i i din ve Oe Dectaruteon ¢ Saree ert earve pod “ ' “i i ‘ HT a Roe es. (  : iCALS 2018 - 24 42  (PET We nerapy cantly (net by J Our Raoinimtian Cariticete under ; eS - . 2S g pow! 5; wo IE ee RO he ne Bee Li. joomt ah Ne  BI 805 WW ARE ARK CISL Am I FH ote We “tertee Srey SHH T4 Gites eshiay &lt;3?  the godds a@pectoed in rus Lax invoices 1c marta try Me / (ia mined tht  Da Be eR EAA Cees CoH member Pom enrieyt be Oot he mend owe mene Mime bie te ow : &lt;1 Sait ret Cmte Se A We Tee Sess Site Cas  MPa srks Dry PAS Lie mtd it hal Ue acwountad fad im the tirnaems OF  Ye. 5 | cites nthe ing cf ctu ard jr Ove tas any, Crete CA Rhee Cote Bae Ones DAIS! Ghat ime peed | ‘xithe ‘ ~ et Mane ee ee Fi CI a lh ng hyn ah F ti MAS ee ei o.. We fee oe IF nn Oe amen alot ee OB omic sine Sos in Ke. pci &amp; ©, herperliree eabanpbargen tates prep eris 4 4 f ‘+A | i we it 5 . N ad Pt w! »e« +</t>
@@ -7942,11 +7526,7 @@
           <t>IMG_20260516_172931.jpg</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>NNSA NE</t>
-        </is>
-      </c>
+      <c r="B259" t="inlineStr"/>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr"/>
@@ -7964,25 +7544,21 @@
           <t>IMG_20260516_172939.jpg</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>TAX INVOICE ORIGINAL FOR RECIPIENT  RV</t>
-        </is>
-      </c>
+      <c r="B260" t="inlineStr"/>
       <c r="C260" t="inlineStr"/>
-      <c r="D260" t="inlineStr">
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>03-07-2025</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>235200</v>
+      </c>
+      <c r="G260" t="inlineStr">
         <is>
           <t>24AAUFR3458H1ZR</t>
         </is>
-      </c>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>03-07-2025</t>
-        </is>
-      </c>
-      <c r="G260" t="n">
-        <v>235200</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -7998,23 +7574,23 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>OPO OS NS</t>
+          <t>L-109,</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
-      <c r="D261" t="inlineStr">
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>35069190118</v>
+      </c>
+      <c r="G261" t="inlineStr">
         <is>
           <t>24AHEPK4410B1Z5</t>
         </is>
-      </c>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>17/10/2025</t>
-        </is>
-      </c>
-      <c r="G261" t="n">
-        <v>35069190118</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -8030,23 +7606,23 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>JAAHEDVAAINRIZE</t>
+          <t>L-109,</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
-      <c r="D262" t="inlineStr">
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>18/09/2025</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>25052</v>
+      </c>
+      <c r="G262" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>18/09/2025</t>
-        </is>
-      </c>
-      <c r="G262" t="n">
-        <v>25052</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -8062,23 +7638,23 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>ORIGINAL</t>
+          <t>L-109,</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
-      <c r="D263" t="inlineStr">
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>27/05/2025</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>135069190118</v>
+      </c>
+      <c r="G263" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>27/05/2025</t>
-        </is>
-      </c>
-      <c r="G263" t="n">
-        <v>135069190118</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -8094,23 +7670,23 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>TS NS</t>
+          <t>L-109,</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
-      <c r="D264" t="inlineStr">
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
+        <v>35069190118</v>
+      </c>
+      <c r="G264" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>02/07/2025</t>
-        </is>
-      </c>
-      <c r="G264" t="n">
-        <v>35069190118</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -8124,25 +7700,21 @@
           <t>IMG_20260516_173037.jpg</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>REA NS</t>
-        </is>
-      </c>
+      <c r="B265" t="inlineStr"/>
       <c r="C265" t="inlineStr"/>
-      <c r="D265" t="inlineStr">
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>10/07/2025</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>919086</v>
+      </c>
+      <c r="G265" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E265" t="inlineStr"/>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>10/07/2025</t>
-        </is>
-      </c>
-      <c r="G265" t="n">
-        <v>919086</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -8156,25 +7728,21 @@
           <t>IMG_20260516_173044.jpg</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>ORIGINAL</t>
-        </is>
-      </c>
+      <c r="B266" t="inlineStr"/>
       <c r="C266" t="inlineStr"/>
-      <c r="D266" t="inlineStr">
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>23/07/2025</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>35069190118</v>
+      </c>
+      <c r="G266" t="inlineStr">
         <is>
           <t>24AHEPK4410B1Z5</t>
         </is>
-      </c>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>23/07/2025</t>
-        </is>
-      </c>
-      <c r="G266" t="n">
-        <v>35069190118</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -8188,25 +7756,21 @@
           <t>IMG_20260516_173050.jpg</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>ORIGINAL</t>
-        </is>
-      </c>
+      <c r="B267" t="inlineStr"/>
       <c r="C267" t="inlineStr"/>
-      <c r="D267" t="inlineStr">
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>01/08/2025</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>20952</v>
+      </c>
+      <c r="G267" t="inlineStr">
         <is>
           <t>24AHEPK4410B1Z5</t>
         </is>
-      </c>
-      <c r="E267" t="inlineStr"/>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>01/08/2025</t>
-        </is>
-      </c>
-      <c r="G267" t="n">
-        <v>20952</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -8220,25 +7784,21 @@
           <t>IMG_20260516_173100.jpg</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>ORIGINAL  GSTIN</t>
-        </is>
-      </c>
+      <c r="B268" t="inlineStr"/>
       <c r="C268" t="inlineStr"/>
-      <c r="D268" t="inlineStr">
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>1388.34</v>
+      </c>
+      <c r="G268" t="inlineStr">
         <is>
           <t>24AHEPK4410B1Z5</t>
         </is>
-      </c>
-      <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>03/09/2025</t>
-        </is>
-      </c>
-      <c r="G268" t="n">
-        <v>1388.34</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -8262,14 +7822,14 @@
           <t>29-30,SAMAYSAAR BUNGLOW, NR NAMDINI 3 VIP ROAD, SURAT GUJARAT-395007</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>24AAAHY7933G1ZY</t>
-        </is>
-      </c>
+      <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr"/>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>24AAAHY7933G1ZY</t>
+        </is>
+      </c>
       <c r="H269" t="inlineStr">
         <is>
           <t>MOULDING POINT  71, JAY JALARAM INDUSTRIAL SOSCIETY,  NEAR. NAVJIVAN CIRCLE, U. M. ROAD SURAT:- 395007  PHONE:-  GSTIN ;- 24AAKFM1385L12Z TAX INVOICE  0261-2235409,9376611800  (U/S - 31(1)CGST Act, 2017 read with rule )  Original for Recipient  Detail of Recipent/Billed To  29-30,SAMAYSAAR BUNGLOW, NR NAMDINI 3 VIP ROAD, SURAT GUJARAT-395007  Address  24AAAHY7933G1ZY  GUJRAT  44119219|18MM 44119219|11MM  FER  rs pry ay wo N ray te)  4411921  THE  Total Invoice Amount in Words :  Remarks : Notification number availed if any  eBank Name : BANK OF BARODA eBank Account Number :25260200000452 eRTGS/IFSC Code : BARBOSURBHA  PANNo. | AAKFIM1385L  Terms And Conditions :  (Commom Seals)  MOULDING POINT AAG E-Mail : mouldingpoint118@gmail.com  \  Add IGST'@ Tax Amount :  % onT.V GST  GST payable on Reverse Charges  For:- MOULDING POINT Authorise Respresentative</t>
@@ -8282,7 +7842,11 @@
           <t>IMG_20260516_173152.jpg</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr"/>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>CNC GST18%</t>
+        </is>
+      </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr"/>
@@ -8389,17 +7953,21 @@
           <t>MOULDING POINT</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr"/>
-      <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr">
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>tal</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
         <is>
           <t>0841/25/26</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr"/>
-      <c r="G277" t="n">
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="n">
         <v>225005.48</v>
       </c>
+      <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr">
         <is>
           <t>fi MOULDING POINT  71, JAY JALARAM INDUSTRIAL SOSCIETY, NEAR. NAVJIVAN CIRCLE, U. M. ROAD SURAT:- 395007 PHONE:- 026 1-2235409,9376611800  GSTIN ;- 24AAKFM1385L122 TAX INVOICE (U/S - 31(1)CGST Act, 2017 read with rule )  invoice NO 0841/25/26 un cea RUTTUNLVW [QWURAT  Detail of Recipent/Billed To  29-30,SAMAYSAAR BUNGLOW, VIP ROAD, SURAT GUJARAT-395007  Veo Pe  Discription ofGoods = Services Fe ani909 @  woodn growing teak  Ron sheet { 2  fe) Total Invoice Amount in Words : Total Before Tax 225005.48 s  | Add CGST9%onT.V. | 20250.49 e  Remarks : Notification number availed if any Add SGST 9% onT.V. 20250.49 é  bet hoy |  Add IGST @ % onT.V.  a  eBank Name : BANK OF BARODA eBank Account Number :25260200000452 eRTGS/IFSC Code : BARBOSURBHA  PANNo. | AAKFIM1385L | :  Terms And Conditions :  wy  For:- MOULDING POINT Authorise Respresentative  (Commom Seals)  MOULDING POINT</t>
@@ -8412,18 +7980,18 @@
           <t>IMG_20260516_173302.jpg</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>MOULDING POINT</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr"/>
+      <c r="B278" t="inlineStr"/>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>tal</t>
+        </is>
+      </c>
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr"/>
-      <c r="F278" t="inlineStr"/>
-      <c r="G278" t="n">
+      <c r="F278" t="n">
         <v>90220</v>
       </c>
+      <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr">
         <is>
           <t>Morey CWO eS &lt;j MOULDING POINT  71, JAY JALARAM INDUSTRIAL SOSCIETY, NEAR. NAVJIVAN CIRCLE, U. M. ROAD SURAT:- 395067 PHONE:- 0261-2235409,9376611800  GSTIN ;- 2A4AAKFM1385L12Z TAX INVOICE (u/S - 21(1)CGST Act, 2017 read with rule ) Original for Recipient  29-30,SAMAYSAAR BUNGLOW, NR NAMDINI 3 vip ROAD, SURAT GUJARAT-395007  . 24lctate. HSN/CODE|THICKNESS Taxable  an ADHESIVES . 7anno  swwwvevw wie ew  44119219/12h4M  Add Packing/ Transportation Charges Total Invoice Amount in Words : Total Before Tax 90220.00  Add CGST9 % on T.V. Aad SG57 SF % On T.V. Add IGST @ % oan T.V.  Tax Amount : GST  @o~w_ __ tt ss amet — a ~~  _ _  yPRemar4ns - wULINCAauOn numer avaiiea it any i  l  eBank Name : BANK OF BARODA eBank Account Number :25260200000452  leRTGS/FSC Code : BARBOSURBHA |  PANNo. | AAKFIM13851  Terms And Conditions :  t payanie Git NeveErse Unarges  Pee RAT Mia DOA  ic See FUR eee eben © rte 6  ! |(Commom Seals) |Authorise Respresentative Ry | E-Mail : mouldingpoint118@gmail.com  | | |  MOULDING POINT</t>
@@ -8436,25 +8004,21 @@
           <t>IMG_20260516_173313.jpg</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>WA GSTIN</t>
-        </is>
-      </c>
+      <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr">
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="n">
+        <v>41933</v>
+      </c>
+      <c r="G279" t="inlineStr">
         <is>
           <t>24AAAHY7933G1ZY</t>
         </is>
-      </c>
-      <c r="E279" t="inlineStr"/>
-      <c r="F279" t="inlineStr"/>
-      <c r="G279" t="n">
-        <v>42038</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -8470,7 +8034,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Y  RFF</t>
+          <t>O8AAYPY6446J51Z1</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8480,10 +8044,10 @@
       </c>
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr"/>
-      <c r="F280" t="inlineStr"/>
-      <c r="G280" t="n">
-        <v>50125</v>
-      </c>
+      <c r="F280" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr">
         <is>
           <t>Tax Invoice  plot No, Police Line, Jaipur -302003  GSTIN/UIN: O8AAYPY6446J51Z1 State Name : Rajasthan, Code : 08 E-Mail : ajayyadav061 @gmail.com  dav Gems Invoice No. Dated va i 310 OEE Sa 13-Aug-25 Nea ee Delivery Note Mode/Terms of Payment  Reference No. &amp; Date.  Other References  Buyer's Order No.  Dated  Dispatch Doc No.  Dispatched through  Destination  Delivery Note Date  Terms of Delivery  Consignee (Ship to) SHED 29-30, Samaysaar Bunglow, Surat GSTIN/UIN : 2AAAAHY7933G1ZY State Name : Gujarat, Code : 24 Buyer (Bill to) SHED 29-30, Samaysaar Bunglow, Surat GSTIN/UIN : 2Q4AAAHY7933G1ZY State Name : Gujarat, Code : 24  Description of Goods  HSN/SAC Quantity  Rate per  Amount  Company's PAN : AAYPY6446J  | Deciaration  No. om k 50,000.00 1 ‘Synthetic Rough Stone |71049900 1,000.00 kg Li | | | IGST 125.00 | | | | | | : by | j oe | hs i Total | 1,000.00 kg | &lt;= 50,125.00 Amount Chargeable (in words) 2, &amp; QYs Indian Rupees Fifty Thousand One Hundred Twenty Five Only HSN/SAC Taxable LX Integrated Tax | _—‘Total Vale Rate | Amount | Fax Armount 71049900 50,000.00 | 0.25% |_ 125.00 125.00 Total 50,000.00 125.00 125.00 Tax Amount (in words): Indian Rupees One Hundred Twenty Five Only Company’s Bank Details Bank Name : IDBI Bank A/c No. : 0884102000002080  Branch &amp; IFS Code: Rajapark, Jaipur &amp; IBKL0000884  -—  We declare that this invoice shows the actual price of the |  goods described and that all particulars are true and  {or Yadav Geis  Authorised Signatory  This is a Computer Generated Invoice  Y  RFF hy  A  a:</t>
@@ -8496,25 +8060,21 @@
           <t>IMG_20260516_173326.jpg</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>MS SR</t>
-        </is>
-      </c>
+      <c r="B281" t="inlineStr"/>
       <c r="C281" t="inlineStr">
         <is>
           <t>SHED</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr">
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="n">
+        <v>3356</v>
+      </c>
+      <c r="G281" t="inlineStr">
         <is>
           <t>24AACAK4386L1ZC</t>
         </is>
-      </c>
-      <c r="E281" t="inlineStr"/>
-      <c r="F281" t="inlineStr"/>
-      <c r="G281" t="n">
-        <v>3524</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -8530,23 +8090,23 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>LS  SUNDARAM</t>
+          <t>SUNDARAM (CHEMICA</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
-      <c r="D282" t="inlineStr">
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>5050.36</v>
+      </c>
+      <c r="G282" t="inlineStr">
         <is>
           <t>24AAAHY7933GIZY</t>
         </is>
-      </c>
-      <c r="E282" t="inlineStr"/>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>15/07/2025</t>
-        </is>
-      </c>
-      <c r="G282" t="n">
-        <v>5050.36</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -8560,11 +8120,7 @@
           <t>IMG_20260516_173350.jpg</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>GSTIN</t>
-        </is>
-      </c>
+      <c r="B283" t="inlineStr"/>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr"/>
@@ -8582,25 +8138,25 @@
           <t>IMG_20260516_173400.jpg</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>PARA TRADING</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr"/>
-      <c r="D284" t="inlineStr">
+      <c r="B284" t="inlineStr"/>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>SURAT Jurisdiction.</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>49/07/2025</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>2850.06</v>
+      </c>
+      <c r="G284" t="inlineStr">
         <is>
           <t>24AFSPS3533D1ZD</t>
         </is>
-      </c>
-      <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>49/07/2025</t>
-        </is>
-      </c>
-      <c r="G284" t="n">
-        <v>3170</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
